--- a/artfynd/A 6153-2024 artfynd.xlsx
+++ b/artfynd/A 6153-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY47"/>
+  <dimension ref="A1:AY48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2281,45 +2281,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128835465</v>
+        <v>128833063</v>
       </c>
       <c r="B17" t="n">
-        <v>86954</v>
+        <v>86780</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Follingsbo Rosendal, Gtl</t>
+          <t>Follingbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>700869</v>
+        <v>700953</v>
       </c>
       <c r="R17" t="n">
-        <v>6388563</v>
+        <v>6388454</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2349,40 +2349,29 @@
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>16:25</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>16:25</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2502,45 +2491,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128833063</v>
+        <v>128835465</v>
       </c>
       <c r="B19" t="n">
-        <v>86780</v>
+        <v>86954</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Follingbo Rosendal, Gtl</t>
+          <t>Follingsbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>700953</v>
+        <v>700869</v>
       </c>
       <c r="R19" t="n">
-        <v>6388454</v>
+        <v>6388563</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2570,29 +2559,40 @@
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2813,45 +2813,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128833068</v>
+        <v>128835490</v>
       </c>
       <c r="B22" t="n">
-        <v>86917</v>
+        <v>86802</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3674</v>
+        <v>424</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Follingbo Rosendal, Gtl</t>
+          <t>Follingsbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>700938</v>
+        <v>700954</v>
       </c>
       <c r="R22" t="n">
-        <v>6388454</v>
+        <v>6388606</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2881,9 +2881,19 @@
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2898,12 +2908,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3017,32 +3027,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128835490</v>
+        <v>128835464</v>
       </c>
       <c r="B24" t="n">
-        <v>86802</v>
+        <v>86930</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>424</v>
+        <v>1988</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3052,10 +3062,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>700954</v>
+        <v>700940</v>
       </c>
       <c r="R24" t="n">
-        <v>6388606</v>
+        <v>6388612</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3087,7 +3097,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3097,7 +3107,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3124,10 +3134,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128835464</v>
+        <v>128833068</v>
       </c>
       <c r="B25" t="n">
-        <v>86930</v>
+        <v>86917</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3135,34 +3145,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1988</v>
+        <v>3674</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Follingsbo Rosendal, Gtl</t>
+          <t>Follingbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>700940</v>
+        <v>700938</v>
       </c>
       <c r="R25" t="n">
-        <v>6388612</v>
+        <v>6388454</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3192,19 +3202,9 @@
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>15:01</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>15:01</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3219,22 +3219,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128835444</v>
+        <v>128835473</v>
       </c>
       <c r="B26" t="n">
-        <v>86999</v>
+        <v>86754</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3242,21 +3242,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3767</v>
+        <v>1985</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3266,10 +3266,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>700957</v>
+        <v>700804</v>
       </c>
       <c r="R26" t="n">
-        <v>6388621</v>
+        <v>6388505</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3301,7 +3301,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3311,7 +3311,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3338,10 +3338,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128835470</v>
+        <v>128835444</v>
       </c>
       <c r="B27" t="n">
-        <v>86941</v>
+        <v>86999</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3349,21 +3349,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3599</v>
+        <v>3767</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3373,10 +3373,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>700910</v>
+        <v>700957</v>
       </c>
       <c r="R27" t="n">
-        <v>6388586</v>
+        <v>6388621</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3408,7 +3408,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3445,10 +3445,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128835473</v>
+        <v>128835470</v>
       </c>
       <c r="B28" t="n">
-        <v>86754</v>
+        <v>86941</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3456,21 +3456,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1985</v>
+        <v>3599</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3480,10 +3480,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>700804</v>
+        <v>700910</v>
       </c>
       <c r="R28" t="n">
-        <v>6388505</v>
+        <v>6388586</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3515,7 +3515,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3766,10 +3766,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128833061</v>
+        <v>128835471</v>
       </c>
       <c r="B31" t="n">
-        <v>86870</v>
+        <v>86754</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3777,34 +3777,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>248956</v>
+        <v>1985</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Follingbo Rosendal, Gtl</t>
+          <t>Follingsbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>700935</v>
+        <v>700792</v>
       </c>
       <c r="R31" t="n">
-        <v>6388458</v>
+        <v>6388508</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3834,9 +3834,19 @@
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>17:02</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3851,57 +3861,57 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128835455</v>
+        <v>128833061</v>
       </c>
       <c r="B32" t="n">
-        <v>90976</v>
+        <v>86870</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5735</v>
+        <v>248956</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Svartnande fingersvamp</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phaeoclavulina macrospora</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Brinkmann</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Follingsbo Rosendal, Gtl</t>
+          <t>Follingbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>700897</v>
+        <v>700935</v>
       </c>
       <c r="R32" t="n">
-        <v>6388579</v>
+        <v>6388458</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3931,72 +3941,61 @@
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>15:54</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>15:54</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128835471</v>
+        <v>128835455</v>
       </c>
       <c r="B33" t="n">
-        <v>86754</v>
+        <v>90976</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1985</v>
+        <v>5735</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Svartnande fingersvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Phaeoclavulina macrospora</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Brinkmann</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4006,10 +4005,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>700792</v>
+        <v>700897</v>
       </c>
       <c r="R33" t="n">
-        <v>6388508</v>
+        <v>6388579</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4041,7 +4040,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4051,7 +4050,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4060,6 +4059,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4078,45 +4078,48 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128833054</v>
+        <v>128835461</v>
       </c>
       <c r="B34" t="n">
-        <v>86954</v>
+        <v>91029</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6003295</v>
+        <v>5747</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Follingbo Rosendal, Gtl</t>
+          <t>Follingsbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>700966</v>
+        <v>700816</v>
       </c>
       <c r="R34" t="n">
-        <v>6388444</v>
+        <v>6388491</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4146,9 +4149,19 @@
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>16:59</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4164,19 +4177,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128833053</v>
+        <v>128833054</v>
       </c>
       <c r="B35" t="n">
         <v>86954</v>
@@ -4211,10 +4224,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>700979</v>
+        <v>700966</v>
       </c>
       <c r="R35" t="n">
-        <v>6388550</v>
+        <v>6388444</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4274,32 +4287,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128833066</v>
+        <v>128833053</v>
       </c>
       <c r="B36" t="n">
-        <v>86917</v>
+        <v>86954</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4309,10 +4322,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>701012</v>
+        <v>700979</v>
       </c>
       <c r="R36" t="n">
-        <v>6388573</v>
+        <v>6388550</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4353,6 +4366,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4371,32 +4385,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128833052</v>
+        <v>128833066</v>
       </c>
       <c r="B37" t="n">
-        <v>86954</v>
+        <v>86917</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4406,10 +4420,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>701151</v>
+        <v>701012</v>
       </c>
       <c r="R37" t="n">
-        <v>6388524</v>
+        <v>6388573</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4450,7 +4464,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4580,7 +4593,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128833057</v>
+        <v>128833052</v>
       </c>
       <c r="B39" t="n">
         <v>86954</v>
@@ -4615,10 +4628,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>701053</v>
+        <v>701151</v>
       </c>
       <c r="R39" t="n">
-        <v>6388488</v>
+        <v>6388524</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4678,7 +4691,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128833055</v>
+        <v>128833057</v>
       </c>
       <c r="B40" t="n">
         <v>86954</v>
@@ -4713,10 +4726,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>700996</v>
+        <v>701053</v>
       </c>
       <c r="R40" t="n">
-        <v>6388473</v>
+        <v>6388488</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4873,7 +4886,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128833056</v>
+        <v>128833055</v>
       </c>
       <c r="B42" t="n">
         <v>86954</v>
@@ -4908,10 +4921,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>701017</v>
+        <v>700996</v>
       </c>
       <c r="R42" t="n">
-        <v>6388485</v>
+        <v>6388473</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4971,32 +4984,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128833069</v>
+        <v>128833056</v>
       </c>
       <c r="B43" t="n">
-        <v>86917</v>
+        <v>86954</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5006,10 +5019,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>700967</v>
+        <v>701017</v>
       </c>
       <c r="R43" t="n">
-        <v>6388445</v>
+        <v>6388485</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5050,6 +5063,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5068,10 +5082,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128833065</v>
+        <v>128833069</v>
       </c>
       <c r="B44" t="n">
-        <v>86780</v>
+        <v>86917</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5079,21 +5093,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>3712</v>
+        <v>3674</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5103,10 +5117,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>701142</v>
+        <v>700967</v>
       </c>
       <c r="R44" t="n">
-        <v>6388527</v>
+        <v>6388445</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5165,7 +5179,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128833064</v>
+        <v>128833065</v>
       </c>
       <c r="B45" t="n">
         <v>86780</v>
@@ -5200,10 +5214,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>701018</v>
+        <v>701142</v>
       </c>
       <c r="R45" t="n">
-        <v>6388486</v>
+        <v>6388527</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5262,10 +5276,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128833071</v>
+        <v>128833064</v>
       </c>
       <c r="B46" t="n">
-        <v>86917</v>
+        <v>86780</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5273,21 +5287,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>3674</v>
+        <v>3712</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5297,10 +5311,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>701130</v>
+        <v>701018</v>
       </c>
       <c r="R46" t="n">
-        <v>6388509</v>
+        <v>6388486</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5359,7 +5373,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128833067</v>
+        <v>128833071</v>
       </c>
       <c r="B47" t="n">
         <v>86917</v>
@@ -5394,10 +5408,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>700982</v>
+        <v>701130</v>
       </c>
       <c r="R47" t="n">
-        <v>6388557</v>
+        <v>6388509</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5453,6 +5467,103 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>128833067</v>
+      </c>
+      <c r="B48" t="n">
+        <v>86917</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>3674</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Anisspindling</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Follingbo Rosendal, Gtl</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>700982</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6388557</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Follingbo</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 6153-2024 artfynd.xlsx
+++ b/artfynd/A 6153-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128835463</v>
       </c>
       <c r="B2" t="n">
-        <v>86930</v>
+        <v>86934</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>128835469</v>
       </c>
       <c r="B4" t="n">
-        <v>86941</v>
+        <v>86945</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>128835449</v>
       </c>
       <c r="B5" t="n">
-        <v>86756</v>
+        <v>86760</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>128835480</v>
       </c>
       <c r="B6" t="n">
-        <v>92248</v>
+        <v>92253</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1205,32 +1205,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128835466</v>
+        <v>128835494</v>
       </c>
       <c r="B7" t="n">
-        <v>86954</v>
+        <v>86921</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>700824</v>
+        <v>700929</v>
       </c>
       <c r="R7" t="n">
-        <v>6388554</v>
+        <v>6388692</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1275,7 +1275,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1294,7 +1294,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1313,32 +1312,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128835494</v>
+        <v>128835466</v>
       </c>
       <c r="B8" t="n">
-        <v>86917</v>
+        <v>86958</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1348,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>700929</v>
+        <v>700824</v>
       </c>
       <c r="R8" t="n">
-        <v>6388692</v>
+        <v>6388554</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1383,7 +1382,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1393,7 +1392,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1402,6 +1401,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1423,7 +1423,7 @@
         <v>128835475</v>
       </c>
       <c r="B9" t="n">
-        <v>86754</v>
+        <v>86758</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>128835492</v>
       </c>
       <c r="B10" t="n">
-        <v>106244</v>
+        <v>106250</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>128835493</v>
       </c>
       <c r="B11" t="n">
-        <v>86917</v>
+        <v>86921</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         <v>128835443</v>
       </c>
       <c r="B12" t="n">
-        <v>86999</v>
+        <v>87003</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>128835441</v>
       </c>
       <c r="B13" t="n">
-        <v>86999</v>
+        <v>87003</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>128835450</v>
       </c>
       <c r="B14" t="n">
-        <v>86756</v>
+        <v>86760</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>128835462</v>
       </c>
       <c r="B15" t="n">
-        <v>86930</v>
+        <v>86934</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>128835499</v>
       </c>
       <c r="B16" t="n">
-        <v>86917</v>
+        <v>86921</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         <v>128833063</v>
       </c>
       <c r="B17" t="n">
-        <v>86780</v>
+        <v>86784</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         <v>128835454</v>
       </c>
       <c r="B18" t="n">
-        <v>90976</v>
+        <v>90981</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
         <v>128835465</v>
       </c>
       <c r="B19" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2602,7 +2602,7 @@
         <v>128835498</v>
       </c>
       <c r="B20" t="n">
-        <v>86917</v>
+        <v>86921</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>128835497</v>
       </c>
       <c r="B21" t="n">
-        <v>86917</v>
+        <v>86921</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2813,45 +2813,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128835490</v>
+        <v>128833068</v>
       </c>
       <c r="B22" t="n">
-        <v>86802</v>
+        <v>86921</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>424</v>
+        <v>3674</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Follingsbo Rosendal, Gtl</t>
+          <t>Follingbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>700954</v>
+        <v>700938</v>
       </c>
       <c r="R22" t="n">
-        <v>6388606</v>
+        <v>6388454</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2881,19 +2881,9 @@
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>14:56</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>14:56</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2908,12 +2898,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -2923,7 +2913,7 @@
         <v>128835472</v>
       </c>
       <c r="B23" t="n">
-        <v>86754</v>
+        <v>86758</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3030,7 +3020,7 @@
         <v>128835464</v>
       </c>
       <c r="B24" t="n">
-        <v>86930</v>
+        <v>86934</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3134,45 +3124,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128833068</v>
+        <v>128835490</v>
       </c>
       <c r="B25" t="n">
-        <v>86917</v>
+        <v>86806</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3674</v>
+        <v>424</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Follingbo Rosendal, Gtl</t>
+          <t>Follingsbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>700938</v>
+        <v>700954</v>
       </c>
       <c r="R25" t="n">
-        <v>6388454</v>
+        <v>6388606</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3202,9 +3192,19 @@
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3219,22 +3219,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128835473</v>
+        <v>128835444</v>
       </c>
       <c r="B26" t="n">
-        <v>86754</v>
+        <v>87003</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3242,21 +3242,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1985</v>
+        <v>3767</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3266,10 +3266,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>700804</v>
+        <v>700957</v>
       </c>
       <c r="R26" t="n">
-        <v>6388505</v>
+        <v>6388621</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3301,7 +3301,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3311,7 +3311,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3338,10 +3338,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128835444</v>
+        <v>128835470</v>
       </c>
       <c r="B27" t="n">
-        <v>86999</v>
+        <v>86945</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3349,21 +3349,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3767</v>
+        <v>3599</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3373,10 +3373,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>700957</v>
+        <v>700910</v>
       </c>
       <c r="R27" t="n">
-        <v>6388621</v>
+        <v>6388586</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3408,7 +3408,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3445,10 +3445,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128835470</v>
+        <v>128835473</v>
       </c>
       <c r="B28" t="n">
-        <v>86941</v>
+        <v>86758</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3456,21 +3456,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3599</v>
+        <v>1985</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3480,10 +3480,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>700910</v>
+        <v>700804</v>
       </c>
       <c r="R28" t="n">
-        <v>6388586</v>
+        <v>6388505</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3515,7 +3515,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3555,7 +3555,7 @@
         <v>128835448</v>
       </c>
       <c r="B29" t="n">
-        <v>86756</v>
+        <v>86760</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3662,7 +3662,7 @@
         <v>128835442</v>
       </c>
       <c r="B30" t="n">
-        <v>86999</v>
+        <v>87003</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3766,10 +3766,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128835471</v>
+        <v>128833061</v>
       </c>
       <c r="B31" t="n">
-        <v>86754</v>
+        <v>86874</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3777,34 +3777,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1985</v>
+        <v>248956</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Follingsbo Rosendal, Gtl</t>
+          <t>Follingbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>700792</v>
+        <v>700935</v>
       </c>
       <c r="R31" t="n">
-        <v>6388508</v>
+        <v>6388458</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3834,19 +3834,9 @@
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>17:02</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>17:02</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3861,22 +3851,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128833061</v>
+        <v>128835471</v>
       </c>
       <c r="B32" t="n">
-        <v>86870</v>
+        <v>86758</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3884,34 +3874,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>248956</v>
+        <v>1985</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Follingbo Rosendal, Gtl</t>
+          <t>Follingsbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>700935</v>
+        <v>700792</v>
       </c>
       <c r="R32" t="n">
-        <v>6388458</v>
+        <v>6388508</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3941,9 +3931,19 @@
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>17:02</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3958,12 +3958,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -3973,7 +3973,7 @@
         <v>128835455</v>
       </c>
       <c r="B33" t="n">
-        <v>90976</v>
+        <v>90981</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4081,7 +4081,7 @@
         <v>128835461</v>
       </c>
       <c r="B34" t="n">
-        <v>91029</v>
+        <v>91034</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4192,7 +4192,7 @@
         <v>128833054</v>
       </c>
       <c r="B35" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4287,32 +4287,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128833053</v>
+        <v>128833066</v>
       </c>
       <c r="B36" t="n">
-        <v>86954</v>
+        <v>86921</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4322,10 +4322,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>700979</v>
+        <v>701012</v>
       </c>
       <c r="R36" t="n">
-        <v>6388550</v>
+        <v>6388573</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4366,7 +4366,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4385,32 +4384,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128833066</v>
+        <v>128833053</v>
       </c>
       <c r="B37" t="n">
-        <v>86917</v>
+        <v>86958</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4420,10 +4419,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>701012</v>
+        <v>700979</v>
       </c>
       <c r="R37" t="n">
-        <v>6388573</v>
+        <v>6388550</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4464,6 +4463,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4485,7 +4485,7 @@
         <v>128835474</v>
       </c>
       <c r="B38" t="n">
-        <v>86754</v>
+        <v>86758</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4596,7 +4596,7 @@
         <v>128833052</v>
       </c>
       <c r="B39" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4694,7 +4694,7 @@
         <v>128833057</v>
       </c>
       <c r="B40" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4792,7 +4792,7 @@
         <v>128833070</v>
       </c>
       <c r="B41" t="n">
-        <v>86917</v>
+        <v>86921</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4889,7 +4889,7 @@
         <v>128833055</v>
       </c>
       <c r="B42" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4987,7 +4987,7 @@
         <v>128833056</v>
       </c>
       <c r="B43" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         <v>128833069</v>
       </c>
       <c r="B44" t="n">
-        <v>86917</v>
+        <v>86921</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5182,7 +5182,7 @@
         <v>128833065</v>
       </c>
       <c r="B45" t="n">
-        <v>86780</v>
+        <v>86784</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5279,7 +5279,7 @@
         <v>128833064</v>
       </c>
       <c r="B46" t="n">
-        <v>86780</v>
+        <v>86784</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5376,7 +5376,7 @@
         <v>128833071</v>
       </c>
       <c r="B47" t="n">
-        <v>86917</v>
+        <v>86921</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5473,7 +5473,7 @@
         <v>128833067</v>
       </c>
       <c r="B48" t="n">
-        <v>86917</v>
+        <v>86921</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 6153-2024 artfynd.xlsx
+++ b/artfynd/A 6153-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY48"/>
+  <dimension ref="A1:AY49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>128835463</v>
       </c>
       <c r="B2" t="n">
-        <v>86934</v>
+        <v>86935</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,45 +782,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128833059</v>
+        <v>128835469</v>
       </c>
       <c r="B3" t="n">
-        <v>8450</v>
+        <v>86946</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>3599</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Follingbo Rosendal, Gtl</t>
+          <t>Follingsbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>700942</v>
+        <v>700915</v>
       </c>
       <c r="R3" t="n">
-        <v>6388538</v>
+        <v>6388581</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -850,9 +850,24 @@
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>1 fk</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,57 +882,57 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128835469</v>
+        <v>128833059</v>
       </c>
       <c r="B4" t="n">
-        <v>86945</v>
+        <v>8450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3599</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Follingsbo Rosendal, Gtl</t>
+          <t>Follingbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>700915</v>
+        <v>700942</v>
       </c>
       <c r="R4" t="n">
-        <v>6388581</v>
+        <v>6388538</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -947,24 +962,9 @@
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>15:23</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>15:23</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>1 fk</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,44 +979,44 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128835449</v>
+        <v>128835480</v>
       </c>
       <c r="B5" t="n">
-        <v>86760</v>
+        <v>92258</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3762</v>
+        <v>232138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Gul lammticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Albatrellus citrinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Ryman</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>700916</v>
+        <v>700814</v>
       </c>
       <c r="R5" t="n">
-        <v>6388577</v>
+        <v>6388491</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,32 +1098,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128835480</v>
+        <v>128835449</v>
       </c>
       <c r="B6" t="n">
-        <v>92253</v>
+        <v>86760</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>232138</v>
+        <v>3762</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gul lammticka</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Albatrellus citrinus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Ryman</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>700814</v>
+        <v>700916</v>
       </c>
       <c r="R6" t="n">
-        <v>6388491</v>
+        <v>6388577</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1208,7 +1208,7 @@
         <v>128835494</v>
       </c>
       <c r="B7" t="n">
-        <v>86921</v>
+        <v>86922</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>128835466</v>
       </c>
       <c r="B8" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>128835492</v>
       </c>
       <c r="B10" t="n">
-        <v>106250</v>
+        <v>106257</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>128835493</v>
       </c>
       <c r="B11" t="n">
-        <v>86921</v>
+        <v>86922</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         <v>128835443</v>
       </c>
       <c r="B12" t="n">
-        <v>87003</v>
+        <v>87004</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>128835441</v>
       </c>
       <c r="B13" t="n">
-        <v>87003</v>
+        <v>87004</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>128835462</v>
       </c>
       <c r="B15" t="n">
-        <v>86934</v>
+        <v>86935</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>128835499</v>
       </c>
       <c r="B16" t="n">
-        <v>86921</v>
+        <v>86922</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         <v>128835454</v>
       </c>
       <c r="B18" t="n">
-        <v>90981</v>
+        <v>90986</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
         <v>128835465</v>
       </c>
       <c r="B19" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2602,7 +2602,7 @@
         <v>128835498</v>
       </c>
       <c r="B20" t="n">
-        <v>86921</v>
+        <v>86922</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>128835497</v>
       </c>
       <c r="B21" t="n">
-        <v>86921</v>
+        <v>86922</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2813,45 +2813,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128833068</v>
+        <v>128835490</v>
       </c>
       <c r="B22" t="n">
-        <v>86921</v>
+        <v>86806</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3674</v>
+        <v>424</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Follingbo Rosendal, Gtl</t>
+          <t>Follingsbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>700938</v>
+        <v>700954</v>
       </c>
       <c r="R22" t="n">
-        <v>6388454</v>
+        <v>6388606</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2881,9 +2881,19 @@
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2898,57 +2908,57 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128835472</v>
+        <v>128833068</v>
       </c>
       <c r="B23" t="n">
-        <v>86758</v>
+        <v>86922</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1985</v>
+        <v>3674</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Follingsbo Rosendal, Gtl</t>
+          <t>Follingbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>700957</v>
+        <v>700938</v>
       </c>
       <c r="R23" t="n">
-        <v>6388630</v>
+        <v>6388454</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2978,19 +2988,9 @@
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>14:39</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>14:39</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3005,44 +3005,44 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128835464</v>
+        <v>128835472</v>
       </c>
       <c r="B24" t="n">
-        <v>86934</v>
+        <v>86758</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1988</v>
+        <v>1985</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3052,10 +3052,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>700940</v>
+        <v>700957</v>
       </c>
       <c r="R24" t="n">
-        <v>6388612</v>
+        <v>6388630</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3087,7 +3087,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3124,32 +3124,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128835490</v>
+        <v>128835464</v>
       </c>
       <c r="B25" t="n">
-        <v>86806</v>
+        <v>86935</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>424</v>
+        <v>1988</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3159,10 +3159,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>700954</v>
+        <v>700940</v>
       </c>
       <c r="R25" t="n">
-        <v>6388606</v>
+        <v>6388612</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3194,7 +3194,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3204,7 +3204,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3234,7 +3234,7 @@
         <v>128835444</v>
       </c>
       <c r="B26" t="n">
-        <v>87003</v>
+        <v>87004</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3338,10 +3338,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128835470</v>
+        <v>128835473</v>
       </c>
       <c r="B27" t="n">
-        <v>86945</v>
+        <v>86758</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3349,21 +3349,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3599</v>
+        <v>1985</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3373,10 +3373,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>700910</v>
+        <v>700804</v>
       </c>
       <c r="R27" t="n">
-        <v>6388586</v>
+        <v>6388505</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3408,7 +3408,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3445,10 +3445,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128835473</v>
+        <v>128835470</v>
       </c>
       <c r="B28" t="n">
-        <v>86758</v>
+        <v>86946</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3456,21 +3456,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1985</v>
+        <v>3599</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3480,10 +3480,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>700804</v>
+        <v>700910</v>
       </c>
       <c r="R28" t="n">
-        <v>6388505</v>
+        <v>6388586</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3515,7 +3515,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3662,7 +3662,7 @@
         <v>128835442</v>
       </c>
       <c r="B30" t="n">
-        <v>87003</v>
+        <v>87004</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3766,10 +3766,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128833061</v>
+        <v>128835471</v>
       </c>
       <c r="B31" t="n">
-        <v>86874</v>
+        <v>86758</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3777,34 +3777,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>248956</v>
+        <v>1985</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Follingbo Rosendal, Gtl</t>
+          <t>Follingsbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>700935</v>
+        <v>700792</v>
       </c>
       <c r="R31" t="n">
-        <v>6388458</v>
+        <v>6388508</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3834,9 +3834,19 @@
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>17:02</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3851,44 +3861,44 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128835471</v>
+        <v>128835455</v>
       </c>
       <c r="B32" t="n">
-        <v>86758</v>
+        <v>90986</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1985</v>
+        <v>5735</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Svartnande fingersvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Phaeoclavulina macrospora</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Brinkmann</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3898,10 +3908,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>700792</v>
+        <v>700897</v>
       </c>
       <c r="R32" t="n">
-        <v>6388508</v>
+        <v>6388579</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3933,7 +3943,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3943,7 +3953,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3952,6 +3962,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3970,45 +3981,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128835455</v>
+        <v>128833061</v>
       </c>
       <c r="B33" t="n">
-        <v>90981</v>
+        <v>86875</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5735</v>
+        <v>248956</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svartnande fingersvamp</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phaeoclavulina macrospora</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Brinkmann</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Follingsbo Rosendal, Gtl</t>
+          <t>Follingbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>700897</v>
+        <v>700935</v>
       </c>
       <c r="R33" t="n">
-        <v>6388579</v>
+        <v>6388458</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4038,40 +4049,29 @@
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>15:54</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>15:54</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4081,7 +4081,7 @@
         <v>128835461</v>
       </c>
       <c r="B34" t="n">
-        <v>91034</v>
+        <v>91039</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4189,45 +4189,48 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128833054</v>
+        <v>128835476</v>
       </c>
       <c r="B35" t="n">
-        <v>86958</v>
+        <v>87153</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6003295</v>
+        <v>451</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Sotbandad spindling</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius fuscoperonatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kühner</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Follingbo Rosendal, Gtl</t>
+          <t>Follingsbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>700966</v>
+        <v>700801</v>
       </c>
       <c r="R35" t="n">
-        <v>6388444</v>
+        <v>6388492</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4257,9 +4260,24 @@
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>16:53</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>16:53</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Kollekt.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4275,44 +4293,44 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128833066</v>
+        <v>128833054</v>
       </c>
       <c r="B36" t="n">
-        <v>86921</v>
+        <v>86959</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4322,10 +4340,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>701012</v>
+        <v>700966</v>
       </c>
       <c r="R36" t="n">
-        <v>6388573</v>
+        <v>6388444</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4366,6 +4384,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4384,32 +4403,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128833053</v>
+        <v>128833066</v>
       </c>
       <c r="B37" t="n">
-        <v>86958</v>
+        <v>86922</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4419,10 +4438,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>700979</v>
+        <v>701012</v>
       </c>
       <c r="R37" t="n">
-        <v>6388550</v>
+        <v>6388573</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4463,7 +4482,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4482,48 +4500,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128835474</v>
+        <v>128833053</v>
       </c>
       <c r="B38" t="n">
-        <v>86758</v>
+        <v>86959</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1985</v>
+        <v>6003295</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Follingsbo Rosendal, Gtl</t>
+          <t>Follingbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>700966</v>
+        <v>700979</v>
       </c>
       <c r="R38" t="n">
-        <v>6388635</v>
+        <v>6388550</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4553,19 +4568,9 @@
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>14:32</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>14:32</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4581,57 +4586,60 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128833052</v>
+        <v>128835474</v>
       </c>
       <c r="B39" t="n">
-        <v>86958</v>
+        <v>86758</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6003295</v>
+        <v>1985</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Follingbo Rosendal, Gtl</t>
+          <t>Follingsbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>701151</v>
+        <v>700966</v>
       </c>
       <c r="R39" t="n">
-        <v>6388524</v>
+        <v>6388635</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4661,9 +4669,19 @@
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4679,22 +4697,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128833057</v>
+        <v>128833052</v>
       </c>
       <c r="B40" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4726,10 +4744,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>701053</v>
+        <v>701151</v>
       </c>
       <c r="R40" t="n">
-        <v>6388488</v>
+        <v>6388524</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4789,32 +4807,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128833070</v>
+        <v>128833057</v>
       </c>
       <c r="B41" t="n">
-        <v>86921</v>
+        <v>86959</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4824,10 +4842,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>701026</v>
+        <v>701053</v>
       </c>
       <c r="R41" t="n">
-        <v>6388477</v>
+        <v>6388488</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4868,6 +4886,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4886,10 +4905,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128833055</v>
+        <v>128833056</v>
       </c>
       <c r="B42" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4921,10 +4940,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>700996</v>
+        <v>701017</v>
       </c>
       <c r="R42" t="n">
-        <v>6388473</v>
+        <v>6388485</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4984,10 +5003,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128833056</v>
+        <v>128833055</v>
       </c>
       <c r="B43" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5019,10 +5038,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>701017</v>
+        <v>700996</v>
       </c>
       <c r="R43" t="n">
-        <v>6388485</v>
+        <v>6388473</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5082,10 +5101,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128833069</v>
+        <v>128833070</v>
       </c>
       <c r="B44" t="n">
-        <v>86921</v>
+        <v>86922</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5117,10 +5136,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>700967</v>
+        <v>701026</v>
       </c>
       <c r="R44" t="n">
-        <v>6388445</v>
+        <v>6388477</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5179,10 +5198,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128833065</v>
+        <v>128833069</v>
       </c>
       <c r="B45" t="n">
-        <v>86784</v>
+        <v>86922</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5190,21 +5209,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>3712</v>
+        <v>3674</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5214,10 +5233,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>701142</v>
+        <v>700967</v>
       </c>
       <c r="R45" t="n">
-        <v>6388527</v>
+        <v>6388445</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5276,7 +5295,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128833064</v>
+        <v>128833065</v>
       </c>
       <c r="B46" t="n">
         <v>86784</v>
@@ -5311,10 +5330,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>701018</v>
+        <v>701142</v>
       </c>
       <c r="R46" t="n">
-        <v>6388486</v>
+        <v>6388527</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5373,10 +5392,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128833071</v>
+        <v>128833064</v>
       </c>
       <c r="B47" t="n">
-        <v>86921</v>
+        <v>86784</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5384,21 +5403,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>3674</v>
+        <v>3712</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5408,10 +5427,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>701130</v>
+        <v>701018</v>
       </c>
       <c r="R47" t="n">
-        <v>6388509</v>
+        <v>6388486</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5470,10 +5489,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128833067</v>
+        <v>128833071</v>
       </c>
       <c r="B48" t="n">
-        <v>86921</v>
+        <v>86922</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5505,10 +5524,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>700982</v>
+        <v>701130</v>
       </c>
       <c r="R48" t="n">
-        <v>6388557</v>
+        <v>6388509</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5564,6 +5583,103 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>128833067</v>
+      </c>
+      <c r="B49" t="n">
+        <v>86922</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>3674</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Anisspindling</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Follingbo Rosendal, Gtl</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>700982</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6388557</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Follingbo</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 6153-2024 artfynd.xlsx
+++ b/artfynd/A 6153-2024 artfynd.xlsx
@@ -991,32 +991,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128835480</v>
+        <v>128835449</v>
       </c>
       <c r="B5" t="n">
-        <v>92258</v>
+        <v>86760</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>232138</v>
+        <v>3762</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gul lammticka</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Albatrellus citrinus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Ryman</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>700814</v>
+        <v>700916</v>
       </c>
       <c r="R5" t="n">
-        <v>6388491</v>
+        <v>6388577</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,32 +1098,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128835449</v>
+        <v>128835480</v>
       </c>
       <c r="B6" t="n">
-        <v>86760</v>
+        <v>92258</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3762</v>
+        <v>232138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Gul lammticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Albatrellus citrinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Ryman</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>700916</v>
+        <v>700814</v>
       </c>
       <c r="R6" t="n">
-        <v>6388577</v>
+        <v>6388491</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1420,32 +1420,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128835475</v>
+        <v>128835492</v>
       </c>
       <c r="B9" t="n">
-        <v>86758</v>
+        <v>106257</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1985</v>
+        <v>220785</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1455,10 +1455,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>700804</v>
+        <v>700799</v>
       </c>
       <c r="R9" t="n">
-        <v>6388482</v>
+        <v>6388520</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1500,7 +1500,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Mycket hlgvuxen 12+ Meter</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1527,32 +1532,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128835492</v>
+        <v>128835475</v>
       </c>
       <c r="B10" t="n">
-        <v>106257</v>
+        <v>86758</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220785</v>
+        <v>1985</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1562,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>700799</v>
+        <v>700804</v>
       </c>
       <c r="R10" t="n">
-        <v>6388520</v>
+        <v>6388482</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1597,7 +1602,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1607,12 +1612,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:45</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Mycket hlgvuxen 12+ Meter</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2813,10 +2813,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128835490</v>
+        <v>128835472</v>
       </c>
       <c r="B22" t="n">
-        <v>86806</v>
+        <v>86758</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2824,16 +2824,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>424</v>
+        <v>1985</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2848,10 +2848,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>700954</v>
+        <v>700957</v>
       </c>
       <c r="R22" t="n">
-        <v>6388606</v>
+        <v>6388630</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2883,7 +2883,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2920,10 +2920,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128833068</v>
+        <v>128835464</v>
       </c>
       <c r="B23" t="n">
-        <v>86922</v>
+        <v>86935</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2931,34 +2931,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3674</v>
+        <v>1988</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Follingbo Rosendal, Gtl</t>
+          <t>Follingsbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>700938</v>
+        <v>700940</v>
       </c>
       <c r="R23" t="n">
-        <v>6388454</v>
+        <v>6388612</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2988,9 +2988,19 @@
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3005,57 +3015,57 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128835472</v>
+        <v>128833068</v>
       </c>
       <c r="B24" t="n">
-        <v>86758</v>
+        <v>86922</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1985</v>
+        <v>3674</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Follingsbo Rosendal, Gtl</t>
+          <t>Follingbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>700957</v>
+        <v>700938</v>
       </c>
       <c r="R24" t="n">
-        <v>6388630</v>
+        <v>6388454</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3085,19 +3095,9 @@
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>14:39</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>14:39</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3112,44 +3112,44 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128835464</v>
+        <v>128835490</v>
       </c>
       <c r="B25" t="n">
-        <v>86935</v>
+        <v>86806</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1988</v>
+        <v>424</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3159,10 +3159,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>700940</v>
+        <v>700954</v>
       </c>
       <c r="R25" t="n">
-        <v>6388612</v>
+        <v>6388606</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3194,7 +3194,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3204,7 +3204,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -4905,7 +4905,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128833056</v>
+        <v>128833055</v>
       </c>
       <c r="B42" t="n">
         <v>86959</v>
@@ -4940,10 +4940,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>701017</v>
+        <v>700996</v>
       </c>
       <c r="R42" t="n">
-        <v>6388485</v>
+        <v>6388473</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5003,7 +5003,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128833055</v>
+        <v>128833056</v>
       </c>
       <c r="B43" t="n">
         <v>86959</v>
@@ -5038,10 +5038,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>700996</v>
+        <v>701017</v>
       </c>
       <c r="R43" t="n">
-        <v>6388473</v>
+        <v>6388485</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>

--- a/artfynd/A 6153-2024 artfynd.xlsx
+++ b/artfynd/A 6153-2024 artfynd.xlsx
@@ -991,32 +991,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128835449</v>
+        <v>128835480</v>
       </c>
       <c r="B5" t="n">
-        <v>86760</v>
+        <v>92258</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3762</v>
+        <v>232138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Gul lammticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Albatrellus citrinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Ryman</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>700916</v>
+        <v>700814</v>
       </c>
       <c r="R5" t="n">
-        <v>6388577</v>
+        <v>6388491</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,32 +1098,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128835480</v>
+        <v>128835449</v>
       </c>
       <c r="B6" t="n">
-        <v>92258</v>
+        <v>86760</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>232138</v>
+        <v>3762</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gul lammticka</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Albatrellus citrinus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Ryman</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>700814</v>
+        <v>700916</v>
       </c>
       <c r="R6" t="n">
-        <v>6388491</v>
+        <v>6388577</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1420,32 +1420,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128835492</v>
+        <v>128835475</v>
       </c>
       <c r="B9" t="n">
-        <v>106257</v>
+        <v>86758</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220785</v>
+        <v>1985</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1455,10 +1455,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>700799</v>
+        <v>700804</v>
       </c>
       <c r="R9" t="n">
-        <v>6388520</v>
+        <v>6388482</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1500,12 +1500,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:45</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Mycket hlgvuxen 12+ Meter</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1532,32 +1527,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128835475</v>
+        <v>128835492</v>
       </c>
       <c r="B10" t="n">
-        <v>86758</v>
+        <v>106257</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1985</v>
+        <v>220785</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1567,10 +1562,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>700804</v>
+        <v>700799</v>
       </c>
       <c r="R10" t="n">
-        <v>6388482</v>
+        <v>6388520</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1602,7 +1597,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1612,7 +1607,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Mycket hlgvuxen 12+ Meter</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2813,45 +2813,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128835472</v>
+        <v>128833068</v>
       </c>
       <c r="B22" t="n">
-        <v>86758</v>
+        <v>86922</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1985</v>
+        <v>3674</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Follingsbo Rosendal, Gtl</t>
+          <t>Follingbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>700957</v>
+        <v>700938</v>
       </c>
       <c r="R22" t="n">
-        <v>6388630</v>
+        <v>6388454</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2881,19 +2881,9 @@
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>14:39</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>14:39</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2908,44 +2898,44 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128835464</v>
+        <v>128835472</v>
       </c>
       <c r="B23" t="n">
-        <v>86935</v>
+        <v>86758</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1988</v>
+        <v>1985</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2955,10 +2945,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>700940</v>
+        <v>700957</v>
       </c>
       <c r="R23" t="n">
-        <v>6388612</v>
+        <v>6388630</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2990,7 +2980,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3000,7 +2990,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3027,10 +3017,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128833068</v>
+        <v>128835464</v>
       </c>
       <c r="B24" t="n">
-        <v>86922</v>
+        <v>86935</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3038,34 +3028,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3674</v>
+        <v>1988</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Follingbo Rosendal, Gtl</t>
+          <t>Follingsbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>700938</v>
+        <v>700940</v>
       </c>
       <c r="R24" t="n">
-        <v>6388454</v>
+        <v>6388612</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3095,9 +3085,19 @@
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3112,12 +3112,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>

--- a/artfynd/A 6153-2024 artfynd.xlsx
+++ b/artfynd/A 6153-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128835463</v>
       </c>
       <c r="B2" t="n">
-        <v>86935</v>
+        <v>86939</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128835469</v>
       </c>
       <c r="B3" t="n">
-        <v>86946</v>
+        <v>86950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -991,32 +991,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128835480</v>
+        <v>128835449</v>
       </c>
       <c r="B5" t="n">
-        <v>92258</v>
+        <v>86764</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>232138</v>
+        <v>3762</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gul lammticka</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Albatrellus citrinus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Ryman</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>700814</v>
+        <v>700916</v>
       </c>
       <c r="R5" t="n">
-        <v>6388491</v>
+        <v>6388577</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,32 +1098,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128835449</v>
+        <v>128835480</v>
       </c>
       <c r="B6" t="n">
-        <v>86760</v>
+        <v>92262</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3762</v>
+        <v>232138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Gul lammticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Albatrellus citrinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Ryman</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>700916</v>
+        <v>700814</v>
       </c>
       <c r="R6" t="n">
-        <v>6388577</v>
+        <v>6388491</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1208,7 +1208,7 @@
         <v>128835494</v>
       </c>
       <c r="B7" t="n">
-        <v>86922</v>
+        <v>86926</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>128835466</v>
       </c>
       <c r="B8" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         <v>128835475</v>
       </c>
       <c r="B9" t="n">
-        <v>86758</v>
+        <v>86762</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>128835492</v>
       </c>
       <c r="B10" t="n">
-        <v>106257</v>
+        <v>106261</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>128835493</v>
       </c>
       <c r="B11" t="n">
-        <v>86922</v>
+        <v>86926</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         <v>128835443</v>
       </c>
       <c r="B12" t="n">
-        <v>87004</v>
+        <v>87008</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>128835441</v>
       </c>
       <c r="B13" t="n">
-        <v>87004</v>
+        <v>87008</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>128835450</v>
       </c>
       <c r="B14" t="n">
-        <v>86760</v>
+        <v>86764</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>128835462</v>
       </c>
       <c r="B15" t="n">
-        <v>86935</v>
+        <v>86939</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2174,10 +2174,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128835499</v>
+        <v>128833063</v>
       </c>
       <c r="B16" t="n">
-        <v>86922</v>
+        <v>86788</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2185,34 +2185,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3674</v>
+        <v>3712</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Follingsbo Rosendal, Gtl</t>
+          <t>Follingbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>700938</v>
+        <v>700953</v>
       </c>
       <c r="R16" t="n">
-        <v>6388610</v>
+        <v>6388454</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2242,19 +2242,9 @@
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>15:01</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>15:01</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2269,57 +2259,57 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128833063</v>
+        <v>128835465</v>
       </c>
       <c r="B17" t="n">
-        <v>86784</v>
+        <v>86963</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Follingbo Rosendal, Gtl</t>
+          <t>Follingsbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>700953</v>
+        <v>700869</v>
       </c>
       <c r="R17" t="n">
-        <v>6388454</v>
+        <v>6388563</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2349,61 +2339,72 @@
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128835454</v>
+        <v>128835499</v>
       </c>
       <c r="B18" t="n">
-        <v>90986</v>
+        <v>86926</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5735</v>
+        <v>3674</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svartnande fingersvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phaeoclavulina macrospora</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Brinkmann</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2413,10 +2414,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>700887</v>
+        <v>700938</v>
       </c>
       <c r="R18" t="n">
-        <v>6388572</v>
+        <v>6388610</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2448,7 +2449,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2458,12 +2459,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Riklig förekomst, Minst 47 fk i en 13 Linje!! Undr En 7-8 meter hög en</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2472,7 +2468,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2491,32 +2486,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128835465</v>
+        <v>128835454</v>
       </c>
       <c r="B19" t="n">
-        <v>86959</v>
+        <v>90990</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6003295</v>
+        <v>5735</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartnande fingersvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Phaeoclavulina macrospora</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brinkmann</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2526,10 +2521,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>700869</v>
+        <v>700887</v>
       </c>
       <c r="R19" t="n">
-        <v>6388563</v>
+        <v>6388572</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2561,7 +2556,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2571,7 +2566,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Riklig förekomst, Minst 47 fk i en 13 Linje!! Undr En 7-8 meter hög en</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2602,7 +2602,7 @@
         <v>128835498</v>
       </c>
       <c r="B20" t="n">
-        <v>86922</v>
+        <v>86926</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>128835497</v>
       </c>
       <c r="B21" t="n">
-        <v>86922</v>
+        <v>86926</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2813,45 +2813,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128833068</v>
+        <v>128835472</v>
       </c>
       <c r="B22" t="n">
-        <v>86922</v>
+        <v>86762</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3674</v>
+        <v>1985</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Follingbo Rosendal, Gtl</t>
+          <t>Follingsbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>700938</v>
+        <v>700957</v>
       </c>
       <c r="R22" t="n">
-        <v>6388454</v>
+        <v>6388630</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2881,9 +2881,19 @@
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2898,44 +2908,44 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128835472</v>
+        <v>128835464</v>
       </c>
       <c r="B23" t="n">
-        <v>86758</v>
+        <v>86939</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1985</v>
+        <v>1988</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2945,10 +2955,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>700957</v>
+        <v>700940</v>
       </c>
       <c r="R23" t="n">
-        <v>6388630</v>
+        <v>6388612</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2980,7 +2990,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2990,7 +3000,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3017,32 +3027,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128835464</v>
+        <v>128835490</v>
       </c>
       <c r="B24" t="n">
-        <v>86935</v>
+        <v>86810</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1988</v>
+        <v>424</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3052,10 +3062,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>700940</v>
+        <v>700954</v>
       </c>
       <c r="R24" t="n">
-        <v>6388612</v>
+        <v>6388606</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3087,7 +3097,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3097,7 +3107,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3124,45 +3134,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128835490</v>
+        <v>128833068</v>
       </c>
       <c r="B25" t="n">
-        <v>86806</v>
+        <v>86926</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>424</v>
+        <v>3674</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Follingsbo Rosendal, Gtl</t>
+          <t>Follingbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>700954</v>
+        <v>700938</v>
       </c>
       <c r="R25" t="n">
-        <v>6388606</v>
+        <v>6388454</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3192,19 +3202,9 @@
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>14:56</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>14:56</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3219,22 +3219,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128835444</v>
+        <v>128835473</v>
       </c>
       <c r="B26" t="n">
-        <v>87004</v>
+        <v>86762</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3242,21 +3242,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3767</v>
+        <v>1985</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3266,10 +3266,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>700957</v>
+        <v>700804</v>
       </c>
       <c r="R26" t="n">
-        <v>6388621</v>
+        <v>6388505</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3301,7 +3301,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3311,7 +3311,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3338,10 +3338,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128835473</v>
+        <v>128835470</v>
       </c>
       <c r="B27" t="n">
-        <v>86758</v>
+        <v>86950</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3349,21 +3349,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1985</v>
+        <v>3599</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3373,10 +3373,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>700804</v>
+        <v>700910</v>
       </c>
       <c r="R27" t="n">
-        <v>6388505</v>
+        <v>6388586</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3408,7 +3408,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3445,10 +3445,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128835470</v>
+        <v>128835444</v>
       </c>
       <c r="B28" t="n">
-        <v>86946</v>
+        <v>87008</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3456,21 +3456,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3599</v>
+        <v>3767</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3480,10 +3480,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>700910</v>
+        <v>700957</v>
       </c>
       <c r="R28" t="n">
-        <v>6388586</v>
+        <v>6388621</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3515,7 +3515,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3555,7 +3555,7 @@
         <v>128835448</v>
       </c>
       <c r="B29" t="n">
-        <v>86760</v>
+        <v>86764</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3662,7 +3662,7 @@
         <v>128835442</v>
       </c>
       <c r="B30" t="n">
-        <v>87004</v>
+        <v>87008</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3769,7 +3769,7 @@
         <v>128835471</v>
       </c>
       <c r="B31" t="n">
-        <v>86758</v>
+        <v>86762</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3876,7 +3876,7 @@
         <v>128835455</v>
       </c>
       <c r="B32" t="n">
-        <v>90986</v>
+        <v>90990</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3984,7 +3984,7 @@
         <v>128833061</v>
       </c>
       <c r="B33" t="n">
-        <v>86875</v>
+        <v>86879</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4081,7 +4081,7 @@
         <v>128835461</v>
       </c>
       <c r="B34" t="n">
-        <v>91039</v>
+        <v>91043</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4192,7 +4192,7 @@
         <v>128835476</v>
       </c>
       <c r="B35" t="n">
-        <v>87153</v>
+        <v>87157</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4308,7 +4308,7 @@
         <v>128833054</v>
       </c>
       <c r="B36" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4406,7 +4406,7 @@
         <v>128833066</v>
       </c>
       <c r="B37" t="n">
-        <v>86922</v>
+        <v>86926</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         <v>128833053</v>
       </c>
       <c r="B38" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         <v>128835474</v>
       </c>
       <c r="B39" t="n">
-        <v>86758</v>
+        <v>86762</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4712,7 +4712,7 @@
         <v>128833052</v>
       </c>
       <c r="B40" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
         <v>128833057</v>
       </c>
       <c r="B41" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4905,32 +4905,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128833055</v>
+        <v>128833070</v>
       </c>
       <c r="B42" t="n">
-        <v>86959</v>
+        <v>86926</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4940,10 +4940,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>700996</v>
+        <v>701026</v>
       </c>
       <c r="R42" t="n">
-        <v>6388473</v>
+        <v>6388477</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4984,7 +4984,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5003,10 +5002,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128833056</v>
+        <v>128833055</v>
       </c>
       <c r="B43" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5038,10 +5037,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>701017</v>
+        <v>700996</v>
       </c>
       <c r="R43" t="n">
-        <v>6388485</v>
+        <v>6388473</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5101,32 +5100,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128833070</v>
+        <v>128833056</v>
       </c>
       <c r="B44" t="n">
-        <v>86922</v>
+        <v>86963</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5136,10 +5135,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>701026</v>
+        <v>701017</v>
       </c>
       <c r="R44" t="n">
-        <v>6388477</v>
+        <v>6388485</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5180,6 +5179,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5201,7 +5201,7 @@
         <v>128833069</v>
       </c>
       <c r="B45" t="n">
-        <v>86922</v>
+        <v>86926</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5298,7 +5298,7 @@
         <v>128833065</v>
       </c>
       <c r="B46" t="n">
-        <v>86784</v>
+        <v>86788</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>128833064</v>
       </c>
       <c r="B47" t="n">
-        <v>86784</v>
+        <v>86788</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5492,7 +5492,7 @@
         <v>128833071</v>
       </c>
       <c r="B48" t="n">
-        <v>86922</v>
+        <v>86926</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         <v>128833067</v>
       </c>
       <c r="B49" t="n">
-        <v>86922</v>
+        <v>86926</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 6153-2024 artfynd.xlsx
+++ b/artfynd/A 6153-2024 artfynd.xlsx
@@ -991,32 +991,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128835449</v>
+        <v>128835480</v>
       </c>
       <c r="B5" t="n">
-        <v>86764</v>
+        <v>92262</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3762</v>
+        <v>232138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Gul lammticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Albatrellus citrinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Ryman</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>700916</v>
+        <v>700814</v>
       </c>
       <c r="R5" t="n">
-        <v>6388577</v>
+        <v>6388491</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,32 +1098,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128835480</v>
+        <v>128835449</v>
       </c>
       <c r="B6" t="n">
-        <v>92262</v>
+        <v>86764</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>232138</v>
+        <v>3762</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gul lammticka</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Albatrellus citrinus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Ryman</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>700814</v>
+        <v>700916</v>
       </c>
       <c r="R6" t="n">
-        <v>6388491</v>
+        <v>6388577</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1420,32 +1420,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128835475</v>
+        <v>128835492</v>
       </c>
       <c r="B9" t="n">
-        <v>86762</v>
+        <v>106261</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1985</v>
+        <v>220785</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1455,10 +1455,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>700804</v>
+        <v>700799</v>
       </c>
       <c r="R9" t="n">
-        <v>6388482</v>
+        <v>6388520</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1500,7 +1500,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Mycket hlgvuxen 12+ Meter</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1527,32 +1532,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128835492</v>
+        <v>128835475</v>
       </c>
       <c r="B10" t="n">
-        <v>106261</v>
+        <v>86762</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220785</v>
+        <v>1985</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1562,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>700799</v>
+        <v>700804</v>
       </c>
       <c r="R10" t="n">
-        <v>6388520</v>
+        <v>6388482</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1597,7 +1602,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1607,12 +1612,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:45</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Mycket hlgvuxen 12+ Meter</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1639,32 +1639,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128835493</v>
+        <v>128835443</v>
       </c>
       <c r="B11" t="n">
-        <v>86926</v>
+        <v>87008</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>700828</v>
+        <v>700956</v>
       </c>
       <c r="R11" t="n">
-        <v>6388554</v>
+        <v>6388619</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1719,7 +1719,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1746,32 +1746,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128835443</v>
+        <v>128835493</v>
       </c>
       <c r="B12" t="n">
-        <v>87008</v>
+        <v>86926</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3767</v>
+        <v>3674</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1781,10 +1781,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>700956</v>
+        <v>700828</v>
       </c>
       <c r="R12" t="n">
-        <v>6388619</v>
+        <v>6388554</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2174,45 +2174,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128833063</v>
+        <v>128835465</v>
       </c>
       <c r="B16" t="n">
-        <v>86788</v>
+        <v>86963</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Follingbo Rosendal, Gtl</t>
+          <t>Follingsbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>700953</v>
+        <v>700869</v>
       </c>
       <c r="R16" t="n">
-        <v>6388454</v>
+        <v>6388563</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2242,61 +2242,72 @@
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128835465</v>
+        <v>128835499</v>
       </c>
       <c r="B17" t="n">
-        <v>86963</v>
+        <v>86926</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2306,10 +2317,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>700869</v>
+        <v>700938</v>
       </c>
       <c r="R17" t="n">
-        <v>6388563</v>
+        <v>6388610</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2341,7 +2352,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2351,7 +2362,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2360,7 +2371,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2379,10 +2389,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128835499</v>
+        <v>128833063</v>
       </c>
       <c r="B18" t="n">
-        <v>86926</v>
+        <v>86788</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2390,34 +2400,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3674</v>
+        <v>3712</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Follingsbo Rosendal, Gtl</t>
+          <t>Follingbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>700938</v>
+        <v>700953</v>
       </c>
       <c r="R18" t="n">
-        <v>6388610</v>
+        <v>6388454</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2447,19 +2457,9 @@
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>15:01</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>15:01</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2474,12 +2474,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2813,10 +2813,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128835472</v>
+        <v>128835490</v>
       </c>
       <c r="B22" t="n">
-        <v>86762</v>
+        <v>86810</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2824,16 +2824,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1985</v>
+        <v>424</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2848,10 +2848,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>700957</v>
+        <v>700954</v>
       </c>
       <c r="R22" t="n">
-        <v>6388630</v>
+        <v>6388606</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2883,7 +2883,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2920,32 +2920,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128835464</v>
+        <v>128835472</v>
       </c>
       <c r="B23" t="n">
-        <v>86939</v>
+        <v>86762</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1988</v>
+        <v>1985</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2955,10 +2955,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>700940</v>
+        <v>700957</v>
       </c>
       <c r="R23" t="n">
-        <v>6388612</v>
+        <v>6388630</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2990,7 +2990,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3027,32 +3027,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128835490</v>
+        <v>128835464</v>
       </c>
       <c r="B24" t="n">
-        <v>86810</v>
+        <v>86939</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>424</v>
+        <v>1988</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3062,10 +3062,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>700954</v>
+        <v>700940</v>
       </c>
       <c r="R24" t="n">
-        <v>6388606</v>
+        <v>6388612</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3097,7 +3097,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3107,7 +3107,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3338,10 +3338,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128835470</v>
+        <v>128835444</v>
       </c>
       <c r="B27" t="n">
-        <v>86950</v>
+        <v>87008</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3349,21 +3349,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3599</v>
+        <v>3767</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3373,10 +3373,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>700910</v>
+        <v>700957</v>
       </c>
       <c r="R27" t="n">
-        <v>6388586</v>
+        <v>6388621</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3408,7 +3408,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3445,10 +3445,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128835444</v>
+        <v>128835470</v>
       </c>
       <c r="B28" t="n">
-        <v>87008</v>
+        <v>86950</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3456,21 +3456,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3767</v>
+        <v>3599</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3480,10 +3480,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>700957</v>
+        <v>700910</v>
       </c>
       <c r="R28" t="n">
-        <v>6388621</v>
+        <v>6388586</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3515,7 +3515,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3552,32 +3552,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128835448</v>
+        <v>128835442</v>
       </c>
       <c r="B29" t="n">
-        <v>86764</v>
+        <v>87008</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3762</v>
+        <v>3767</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3587,10 +3587,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>700817</v>
+        <v>700952</v>
       </c>
       <c r="R29" t="n">
-        <v>6388555</v>
+        <v>6388607</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3622,7 +3622,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3659,32 +3659,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128835442</v>
+        <v>128835448</v>
       </c>
       <c r="B30" t="n">
-        <v>87008</v>
+        <v>86764</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3767</v>
+        <v>3762</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3694,10 +3694,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>700952</v>
+        <v>700817</v>
       </c>
       <c r="R30" t="n">
-        <v>6388607</v>
+        <v>6388555</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3766,10 +3766,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128835471</v>
+        <v>128833061</v>
       </c>
       <c r="B31" t="n">
-        <v>86762</v>
+        <v>86879</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3777,34 +3777,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1985</v>
+        <v>248956</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Follingsbo Rosendal, Gtl</t>
+          <t>Follingbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>700792</v>
+        <v>700935</v>
       </c>
       <c r="R31" t="n">
-        <v>6388508</v>
+        <v>6388458</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3834,19 +3834,9 @@
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>17:02</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>17:02</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3861,44 +3851,44 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128835455</v>
+        <v>128835471</v>
       </c>
       <c r="B32" t="n">
-        <v>90990</v>
+        <v>86762</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5735</v>
+        <v>1985</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Svartnande fingersvamp</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phaeoclavulina macrospora</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Brinkmann</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3908,10 +3898,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>700897</v>
+        <v>700792</v>
       </c>
       <c r="R32" t="n">
-        <v>6388579</v>
+        <v>6388508</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3943,7 +3933,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3953,7 +3943,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3962,7 +3952,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3981,45 +3970,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128833061</v>
+        <v>128835455</v>
       </c>
       <c r="B33" t="n">
-        <v>86879</v>
+        <v>90990</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>248956</v>
+        <v>5735</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Svartnande fingersvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Phaeoclavulina macrospora</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Brinkmann</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Follingbo Rosendal, Gtl</t>
+          <t>Follingsbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>700935</v>
+        <v>700897</v>
       </c>
       <c r="R33" t="n">
-        <v>6388458</v>
+        <v>6388579</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4049,29 +4038,40 @@
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>

--- a/artfynd/A 6153-2024 artfynd.xlsx
+++ b/artfynd/A 6153-2024 artfynd.xlsx
@@ -991,32 +991,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128835480</v>
+        <v>128835449</v>
       </c>
       <c r="B5" t="n">
-        <v>92262</v>
+        <v>86764</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>232138</v>
+        <v>3762</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gul lammticka</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Albatrellus citrinus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Ryman</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>700814</v>
+        <v>700916</v>
       </c>
       <c r="R5" t="n">
-        <v>6388491</v>
+        <v>6388577</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,32 +1098,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128835449</v>
+        <v>128835480</v>
       </c>
       <c r="B6" t="n">
-        <v>86764</v>
+        <v>92262</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3762</v>
+        <v>232138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Gul lammticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Albatrellus citrinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Ryman</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>700916</v>
+        <v>700814</v>
       </c>
       <c r="R6" t="n">
-        <v>6388577</v>
+        <v>6388491</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1420,32 +1420,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128835492</v>
+        <v>128835475</v>
       </c>
       <c r="B9" t="n">
-        <v>106261</v>
+        <v>86762</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220785</v>
+        <v>1985</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1455,10 +1455,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>700799</v>
+        <v>700804</v>
       </c>
       <c r="R9" t="n">
-        <v>6388520</v>
+        <v>6388482</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1500,12 +1500,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:45</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Mycket hlgvuxen 12+ Meter</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1532,32 +1527,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128835475</v>
+        <v>128835492</v>
       </c>
       <c r="B10" t="n">
-        <v>86762</v>
+        <v>106261</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1985</v>
+        <v>220785</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1567,10 +1562,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>700804</v>
+        <v>700799</v>
       </c>
       <c r="R10" t="n">
-        <v>6388482</v>
+        <v>6388520</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1602,7 +1597,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1612,7 +1607,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Mycket hlgvuxen 12+ Meter</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1639,32 +1639,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128835443</v>
+        <v>128835493</v>
       </c>
       <c r="B11" t="n">
-        <v>87008</v>
+        <v>86926</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3767</v>
+        <v>3674</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>700956</v>
+        <v>700828</v>
       </c>
       <c r="R11" t="n">
-        <v>6388619</v>
+        <v>6388554</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1719,7 +1719,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1746,32 +1746,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128835493</v>
+        <v>128835443</v>
       </c>
       <c r="B12" t="n">
-        <v>86926</v>
+        <v>87008</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1781,10 +1781,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>700828</v>
+        <v>700956</v>
       </c>
       <c r="R12" t="n">
-        <v>6388554</v>
+        <v>6388619</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2920,45 +2920,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128835472</v>
+        <v>128833068</v>
       </c>
       <c r="B23" t="n">
-        <v>86762</v>
+        <v>86926</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1985</v>
+        <v>3674</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Follingsbo Rosendal, Gtl</t>
+          <t>Follingbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>700957</v>
+        <v>700938</v>
       </c>
       <c r="R23" t="n">
-        <v>6388630</v>
+        <v>6388454</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2988,19 +2988,9 @@
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>14:39</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>14:39</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3015,44 +3005,44 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128835464</v>
+        <v>128835472</v>
       </c>
       <c r="B24" t="n">
-        <v>86939</v>
+        <v>86762</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1988</v>
+        <v>1985</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3062,10 +3052,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>700940</v>
+        <v>700957</v>
       </c>
       <c r="R24" t="n">
-        <v>6388612</v>
+        <v>6388630</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3097,7 +3087,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3107,7 +3097,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3134,10 +3124,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128833068</v>
+        <v>128835464</v>
       </c>
       <c r="B25" t="n">
-        <v>86926</v>
+        <v>86939</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3145,34 +3135,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3674</v>
+        <v>1988</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Follingbo Rosendal, Gtl</t>
+          <t>Follingsbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>700938</v>
+        <v>700940</v>
       </c>
       <c r="R25" t="n">
-        <v>6388454</v>
+        <v>6388612</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3202,9 +3192,19 @@
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3219,22 +3219,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128835473</v>
+        <v>128835444</v>
       </c>
       <c r="B26" t="n">
-        <v>86762</v>
+        <v>87008</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3242,21 +3242,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1985</v>
+        <v>3767</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3266,10 +3266,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>700804</v>
+        <v>700957</v>
       </c>
       <c r="R26" t="n">
-        <v>6388505</v>
+        <v>6388621</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3301,7 +3301,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3311,7 +3311,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3338,10 +3338,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128835444</v>
+        <v>128835470</v>
       </c>
       <c r="B27" t="n">
-        <v>87008</v>
+        <v>86950</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3349,21 +3349,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3767</v>
+        <v>3599</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3373,10 +3373,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>700957</v>
+        <v>700910</v>
       </c>
       <c r="R27" t="n">
-        <v>6388621</v>
+        <v>6388586</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3408,7 +3408,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3445,10 +3445,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128835470</v>
+        <v>128835473</v>
       </c>
       <c r="B28" t="n">
-        <v>86950</v>
+        <v>86762</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3456,21 +3456,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3599</v>
+        <v>1985</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3480,10 +3480,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>700910</v>
+        <v>700804</v>
       </c>
       <c r="R28" t="n">
-        <v>6388586</v>
+        <v>6388505</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3515,7 +3515,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3552,32 +3552,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128835442</v>
+        <v>128835448</v>
       </c>
       <c r="B29" t="n">
-        <v>87008</v>
+        <v>86764</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3767</v>
+        <v>3762</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3587,10 +3587,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>700952</v>
+        <v>700817</v>
       </c>
       <c r="R29" t="n">
-        <v>6388607</v>
+        <v>6388555</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3622,7 +3622,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3659,32 +3659,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128835448</v>
+        <v>128835442</v>
       </c>
       <c r="B30" t="n">
-        <v>86764</v>
+        <v>87008</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3762</v>
+        <v>3767</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3694,10 +3694,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>700817</v>
+        <v>700952</v>
       </c>
       <c r="R30" t="n">
-        <v>6388555</v>
+        <v>6388607</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3863,32 +3863,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128835471</v>
+        <v>128835455</v>
       </c>
       <c r="B32" t="n">
-        <v>86762</v>
+        <v>90990</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1985</v>
+        <v>5735</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Svartnande fingersvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Phaeoclavulina macrospora</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Brinkmann</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3898,10 +3898,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>700792</v>
+        <v>700897</v>
       </c>
       <c r="R32" t="n">
-        <v>6388508</v>
+        <v>6388579</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3943,7 +3943,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3952,6 +3952,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3970,32 +3971,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128835455</v>
+        <v>128835471</v>
       </c>
       <c r="B33" t="n">
-        <v>90990</v>
+        <v>86762</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5735</v>
+        <v>1985</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svartnande fingersvamp</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phaeoclavulina macrospora</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Brinkmann</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4005,10 +4006,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>700897</v>
+        <v>700792</v>
       </c>
       <c r="R33" t="n">
-        <v>6388579</v>
+        <v>6388508</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4040,7 +4041,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4050,7 +4051,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4059,7 +4060,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4905,32 +4905,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128833070</v>
+        <v>128833055</v>
       </c>
       <c r="B42" t="n">
-        <v>86926</v>
+        <v>86963</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4940,10 +4940,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>701026</v>
+        <v>700996</v>
       </c>
       <c r="R42" t="n">
-        <v>6388477</v>
+        <v>6388473</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4984,6 +4984,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5002,7 +5003,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128833055</v>
+        <v>128833056</v>
       </c>
       <c r="B43" t="n">
         <v>86963</v>
@@ -5037,10 +5038,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>700996</v>
+        <v>701017</v>
       </c>
       <c r="R43" t="n">
-        <v>6388473</v>
+        <v>6388485</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5100,32 +5101,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128833056</v>
+        <v>128833070</v>
       </c>
       <c r="B44" t="n">
-        <v>86963</v>
+        <v>86926</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5135,10 +5136,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>701017</v>
+        <v>701026</v>
       </c>
       <c r="R44" t="n">
-        <v>6388485</v>
+        <v>6388477</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5179,7 +5180,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 6153-2024 artfynd.xlsx
+++ b/artfynd/A 6153-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128835463</v>
       </c>
       <c r="B2" t="n">
-        <v>86939</v>
+        <v>86944</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,45 +782,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128835469</v>
+        <v>128833059</v>
       </c>
       <c r="B3" t="n">
-        <v>86950</v>
+        <v>8450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3599</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Follingsbo Rosendal, Gtl</t>
+          <t>Follingbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>700915</v>
+        <v>700942</v>
       </c>
       <c r="R3" t="n">
-        <v>6388581</v>
+        <v>6388538</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -850,24 +850,9 @@
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>15:23</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>15:23</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>1 fk</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,57 +867,57 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128833059</v>
+        <v>128835469</v>
       </c>
       <c r="B4" t="n">
-        <v>8450</v>
+        <v>86955</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>3599</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Follingbo Rosendal, Gtl</t>
+          <t>Follingsbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>700942</v>
+        <v>700915</v>
       </c>
       <c r="R4" t="n">
-        <v>6388538</v>
+        <v>6388581</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -962,9 +947,24 @@
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>1 fk</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,44 +979,44 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128835449</v>
+        <v>128835480</v>
       </c>
       <c r="B5" t="n">
-        <v>86764</v>
+        <v>92267</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3762</v>
+        <v>232138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Gul lammticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Albatrellus citrinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Ryman</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>700916</v>
+        <v>700814</v>
       </c>
       <c r="R5" t="n">
-        <v>6388577</v>
+        <v>6388491</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,32 +1098,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128835480</v>
+        <v>128835449</v>
       </c>
       <c r="B6" t="n">
-        <v>92262</v>
+        <v>86769</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>232138</v>
+        <v>3762</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gul lammticka</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Albatrellus citrinus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Ryman</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>700814</v>
+        <v>700916</v>
       </c>
       <c r="R6" t="n">
-        <v>6388491</v>
+        <v>6388577</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1208,7 +1208,7 @@
         <v>128835494</v>
       </c>
       <c r="B7" t="n">
-        <v>86926</v>
+        <v>86931</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>128835466</v>
       </c>
       <c r="B8" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1420,32 +1420,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128835475</v>
+        <v>128835492</v>
       </c>
       <c r="B9" t="n">
-        <v>86762</v>
+        <v>106268</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1985</v>
+        <v>220785</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1455,10 +1455,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>700804</v>
+        <v>700799</v>
       </c>
       <c r="R9" t="n">
-        <v>6388482</v>
+        <v>6388520</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1500,7 +1500,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Mycket hlgvuxen 12+ Meter</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1527,32 +1532,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128835492</v>
+        <v>128835475</v>
       </c>
       <c r="B10" t="n">
-        <v>106261</v>
+        <v>86767</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220785</v>
+        <v>1985</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1562,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>700799</v>
+        <v>700804</v>
       </c>
       <c r="R10" t="n">
-        <v>6388520</v>
+        <v>6388482</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1597,7 +1602,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1607,12 +1612,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:45</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Mycket hlgvuxen 12+ Meter</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1642,7 +1642,7 @@
         <v>128835493</v>
       </c>
       <c r="B11" t="n">
-        <v>86926</v>
+        <v>86931</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         <v>128835443</v>
       </c>
       <c r="B12" t="n">
-        <v>87008</v>
+        <v>87013</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>128835441</v>
       </c>
       <c r="B13" t="n">
-        <v>87008</v>
+        <v>87013</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>128835450</v>
       </c>
       <c r="B14" t="n">
-        <v>86764</v>
+        <v>86769</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>128835462</v>
       </c>
       <c r="B15" t="n">
-        <v>86939</v>
+        <v>86944</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2174,32 +2174,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128835465</v>
+        <v>128835499</v>
       </c>
       <c r="B16" t="n">
-        <v>86963</v>
+        <v>86931</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2209,10 +2209,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>700869</v>
+        <v>700938</v>
       </c>
       <c r="R16" t="n">
-        <v>6388563</v>
+        <v>6388610</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2244,7 +2244,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2263,7 +2263,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2282,10 +2281,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128835499</v>
+        <v>128833063</v>
       </c>
       <c r="B17" t="n">
-        <v>86926</v>
+        <v>86793</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2293,34 +2292,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3674</v>
+        <v>3712</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Follingsbo Rosendal, Gtl</t>
+          <t>Follingbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>700938</v>
+        <v>700953</v>
       </c>
       <c r="R17" t="n">
-        <v>6388610</v>
+        <v>6388454</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2350,19 +2349,9 @@
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>15:01</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>15:01</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2377,57 +2366,57 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128833063</v>
+        <v>128835454</v>
       </c>
       <c r="B18" t="n">
-        <v>86788</v>
+        <v>90995</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3712</v>
+        <v>5735</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Svartnande fingersvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Phaeoclavulina macrospora</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Brinkmann</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Follingbo Rosendal, Gtl</t>
+          <t>Follingsbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>700953</v>
+        <v>700887</v>
       </c>
       <c r="R18" t="n">
-        <v>6388454</v>
+        <v>6388572</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2457,61 +2446,77 @@
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Riklig förekomst, Minst 47 fk i en 13 Linje!! Undr En 7-8 meter hög en</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128835454</v>
+        <v>128835465</v>
       </c>
       <c r="B19" t="n">
-        <v>90990</v>
+        <v>86968</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5735</v>
+        <v>6003295</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svartnande fingersvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phaeoclavulina macrospora</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Brinkmann</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2521,10 +2526,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>700887</v>
+        <v>700869</v>
       </c>
       <c r="R19" t="n">
-        <v>6388572</v>
+        <v>6388563</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2556,7 +2561,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2566,12 +2571,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Riklig förekomst, Minst 47 fk i en 13 Linje!! Undr En 7-8 meter hög en</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2602,7 +2602,7 @@
         <v>128835498</v>
       </c>
       <c r="B20" t="n">
-        <v>86926</v>
+        <v>86931</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>128835497</v>
       </c>
       <c r="B21" t="n">
-        <v>86926</v>
+        <v>86931</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>128835490</v>
       </c>
       <c r="B22" t="n">
-        <v>86810</v>
+        <v>86815</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>128833068</v>
       </c>
       <c r="B23" t="n">
-        <v>86926</v>
+        <v>86931</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         <v>128835472</v>
       </c>
       <c r="B24" t="n">
-        <v>86762</v>
+        <v>86767</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3127,7 +3127,7 @@
         <v>128835464</v>
       </c>
       <c r="B25" t="n">
-        <v>86939</v>
+        <v>86944</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3231,10 +3231,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128835444</v>
+        <v>128835473</v>
       </c>
       <c r="B26" t="n">
-        <v>87008</v>
+        <v>86767</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3242,21 +3242,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3767</v>
+        <v>1985</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3266,10 +3266,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>700957</v>
+        <v>700804</v>
       </c>
       <c r="R26" t="n">
-        <v>6388621</v>
+        <v>6388505</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3301,7 +3301,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3311,7 +3311,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3338,10 +3338,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128835470</v>
+        <v>128835444</v>
       </c>
       <c r="B27" t="n">
-        <v>86950</v>
+        <v>87013</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3349,21 +3349,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3599</v>
+        <v>3767</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3373,10 +3373,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>700910</v>
+        <v>700957</v>
       </c>
       <c r="R27" t="n">
-        <v>6388586</v>
+        <v>6388621</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3408,7 +3408,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3445,10 +3445,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128835473</v>
+        <v>128835470</v>
       </c>
       <c r="B28" t="n">
-        <v>86762</v>
+        <v>86955</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3456,21 +3456,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1985</v>
+        <v>3599</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3480,10 +3480,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>700804</v>
+        <v>700910</v>
       </c>
       <c r="R28" t="n">
-        <v>6388505</v>
+        <v>6388586</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3515,7 +3515,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3555,7 +3555,7 @@
         <v>128835448</v>
       </c>
       <c r="B29" t="n">
-        <v>86764</v>
+        <v>86769</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3662,7 +3662,7 @@
         <v>128835442</v>
       </c>
       <c r="B30" t="n">
-        <v>87008</v>
+        <v>87013</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3769,7 +3769,7 @@
         <v>128833061</v>
       </c>
       <c r="B31" t="n">
-        <v>86879</v>
+        <v>86884</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3863,32 +3863,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128835455</v>
+        <v>128835471</v>
       </c>
       <c r="B32" t="n">
-        <v>90990</v>
+        <v>86767</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5735</v>
+        <v>1985</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Svartnande fingersvamp</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phaeoclavulina macrospora</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Brinkmann</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3898,10 +3898,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>700897</v>
+        <v>700792</v>
       </c>
       <c r="R32" t="n">
-        <v>6388579</v>
+        <v>6388508</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3943,7 +3943,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3952,7 +3952,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3971,32 +3970,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128835471</v>
+        <v>128835455</v>
       </c>
       <c r="B33" t="n">
-        <v>86762</v>
+        <v>90995</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1985</v>
+        <v>5735</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Svartnande fingersvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Phaeoclavulina macrospora</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Brinkmann</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4006,10 +4005,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>700792</v>
+        <v>700897</v>
       </c>
       <c r="R33" t="n">
-        <v>6388508</v>
+        <v>6388579</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4041,7 +4040,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4051,7 +4050,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4060,6 +4059,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4081,7 +4081,7 @@
         <v>128835461</v>
       </c>
       <c r="B34" t="n">
-        <v>91043</v>
+        <v>91048</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4192,7 +4192,7 @@
         <v>128835476</v>
       </c>
       <c r="B35" t="n">
-        <v>87157</v>
+        <v>87162</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4308,7 +4308,7 @@
         <v>128833054</v>
       </c>
       <c r="B36" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4406,7 +4406,7 @@
         <v>128833066</v>
       </c>
       <c r="B37" t="n">
-        <v>86926</v>
+        <v>86931</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         <v>128833053</v>
       </c>
       <c r="B38" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4598,48 +4598,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128835474</v>
+        <v>128833052</v>
       </c>
       <c r="B39" t="n">
-        <v>86762</v>
+        <v>86968</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1985</v>
+        <v>6003295</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Follingsbo Rosendal, Gtl</t>
+          <t>Follingbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>700966</v>
+        <v>701151</v>
       </c>
       <c r="R39" t="n">
-        <v>6388635</v>
+        <v>6388524</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4669,19 +4666,9 @@
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>14:32</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>14:32</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4697,57 +4684,60 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128833052</v>
+        <v>128835474</v>
       </c>
       <c r="B40" t="n">
-        <v>86963</v>
+        <v>86767</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6003295</v>
+        <v>1985</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Follingbo Rosendal, Gtl</t>
+          <t>Follingsbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>701151</v>
+        <v>700966</v>
       </c>
       <c r="R40" t="n">
-        <v>6388524</v>
+        <v>6388635</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4777,9 +4767,19 @@
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4795,12 +4795,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -4810,7 +4810,7 @@
         <v>128833057</v>
       </c>
       <c r="B41" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4905,32 +4905,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128833055</v>
+        <v>128833070</v>
       </c>
       <c r="B42" t="n">
-        <v>86963</v>
+        <v>86931</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4940,10 +4940,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>700996</v>
+        <v>701026</v>
       </c>
       <c r="R42" t="n">
-        <v>6388473</v>
+        <v>6388477</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4984,7 +4984,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5003,10 +5002,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128833056</v>
+        <v>128833055</v>
       </c>
       <c r="B43" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5038,10 +5037,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>701017</v>
+        <v>700996</v>
       </c>
       <c r="R43" t="n">
-        <v>6388485</v>
+        <v>6388473</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5101,32 +5100,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128833070</v>
+        <v>128833056</v>
       </c>
       <c r="B44" t="n">
-        <v>86926</v>
+        <v>86968</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5136,10 +5135,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>701026</v>
+        <v>701017</v>
       </c>
       <c r="R44" t="n">
-        <v>6388477</v>
+        <v>6388485</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5180,6 +5179,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5201,7 +5201,7 @@
         <v>128833069</v>
       </c>
       <c r="B45" t="n">
-        <v>86926</v>
+        <v>86931</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5298,7 +5298,7 @@
         <v>128833065</v>
       </c>
       <c r="B46" t="n">
-        <v>86788</v>
+        <v>86793</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>128833064</v>
       </c>
       <c r="B47" t="n">
-        <v>86788</v>
+        <v>86793</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5492,7 +5492,7 @@
         <v>128833071</v>
       </c>
       <c r="B48" t="n">
-        <v>86926</v>
+        <v>86931</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         <v>128833067</v>
       </c>
       <c r="B49" t="n">
-        <v>86926</v>
+        <v>86931</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 6153-2024 artfynd.xlsx
+++ b/artfynd/A 6153-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128835463</v>
       </c>
       <c r="B2" t="n">
-        <v>86951</v>
+        <v>86954</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>128835469</v>
       </c>
       <c r="B4" t="n">
-        <v>86962</v>
+        <v>86965</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>128835480</v>
       </c>
       <c r="B5" t="n">
-        <v>92275</v>
+        <v>92280</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>128835449</v>
       </c>
       <c r="B6" t="n">
-        <v>86776</v>
+        <v>86779</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>128835494</v>
       </c>
       <c r="B7" t="n">
-        <v>86938</v>
+        <v>86941</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>128835466</v>
       </c>
       <c r="B8" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         <v>128835475</v>
       </c>
       <c r="B9" t="n">
-        <v>86774</v>
+        <v>86777</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>128835492</v>
       </c>
       <c r="B10" t="n">
-        <v>106276</v>
+        <v>106281</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>128835493</v>
       </c>
       <c r="B11" t="n">
-        <v>86938</v>
+        <v>86941</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         <v>128835443</v>
       </c>
       <c r="B12" t="n">
-        <v>87020</v>
+        <v>87023</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>128835441</v>
       </c>
       <c r="B13" t="n">
-        <v>87020</v>
+        <v>87023</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>128835450</v>
       </c>
       <c r="B14" t="n">
-        <v>86776</v>
+        <v>86779</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>128835462</v>
       </c>
       <c r="B15" t="n">
-        <v>86951</v>
+        <v>86954</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2174,32 +2174,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128835499</v>
+        <v>128835454</v>
       </c>
       <c r="B16" t="n">
-        <v>86938</v>
+        <v>91005</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3674</v>
+        <v>5735</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Svartnande fingersvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Phaeoclavulina macrospora</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brinkmann</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2209,10 +2209,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>700938</v>
+        <v>700887</v>
       </c>
       <c r="R16" t="n">
-        <v>6388610</v>
+        <v>6388572</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2244,7 +2244,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2254,7 +2254,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Riklig förekomst, Minst 47 fk i en 13 Linje!! Undr En 7-8 meter hög en</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2263,6 +2268,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2281,10 +2287,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128833063</v>
+        <v>128835499</v>
       </c>
       <c r="B17" t="n">
-        <v>86800</v>
+        <v>86941</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2292,34 +2298,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3712</v>
+        <v>3674</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Follingbo Rosendal, Gtl</t>
+          <t>Follingsbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>700953</v>
+        <v>700938</v>
       </c>
       <c r="R17" t="n">
-        <v>6388454</v>
+        <v>6388610</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2349,9 +2355,19 @@
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2366,57 +2382,57 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128835454</v>
+        <v>128833063</v>
       </c>
       <c r="B18" t="n">
-        <v>91002</v>
+        <v>86803</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5735</v>
+        <v>3712</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svartnande fingersvamp</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phaeoclavulina macrospora</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Brinkmann</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Follingsbo Rosendal, Gtl</t>
+          <t>Follingbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>700887</v>
+        <v>700953</v>
       </c>
       <c r="R18" t="n">
-        <v>6388572</v>
+        <v>6388454</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2446,45 +2462,29 @@
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Riklig förekomst, Minst 47 fk i en 13 Linje!! Undr En 7-8 meter hög en</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2494,7 +2494,7 @@
         <v>128835465</v>
       </c>
       <c r="B19" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2599,10 +2599,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128835498</v>
+        <v>128835497</v>
       </c>
       <c r="B20" t="n">
-        <v>86938</v>
+        <v>86941</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2634,10 +2634,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>700817</v>
+        <v>700948</v>
       </c>
       <c r="R20" t="n">
-        <v>6388548</v>
+        <v>6388722</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2706,10 +2706,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128835497</v>
+        <v>128835498</v>
       </c>
       <c r="B21" t="n">
-        <v>86938</v>
+        <v>86941</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>700948</v>
+        <v>700817</v>
       </c>
       <c r="R21" t="n">
-        <v>6388722</v>
+        <v>6388548</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2813,45 +2813,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128833068</v>
+        <v>128835472</v>
       </c>
       <c r="B22" t="n">
-        <v>86938</v>
+        <v>86777</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3674</v>
+        <v>1985</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Follingbo Rosendal, Gtl</t>
+          <t>Follingsbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>700938</v>
+        <v>700957</v>
       </c>
       <c r="R22" t="n">
-        <v>6388454</v>
+        <v>6388630</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2881,9 +2881,19 @@
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2898,44 +2908,44 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128835490</v>
+        <v>128835464</v>
       </c>
       <c r="B23" t="n">
-        <v>86822</v>
+        <v>86954</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>424</v>
+        <v>1988</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2945,10 +2955,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>700954</v>
+        <v>700940</v>
       </c>
       <c r="R23" t="n">
-        <v>6388606</v>
+        <v>6388612</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2980,7 +2990,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2990,7 +3000,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3017,10 +3027,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128835472</v>
+        <v>128835490</v>
       </c>
       <c r="B24" t="n">
-        <v>86774</v>
+        <v>86825</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3028,16 +3038,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1985</v>
+        <v>424</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3052,10 +3062,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>700957</v>
+        <v>700954</v>
       </c>
       <c r="R24" t="n">
-        <v>6388630</v>
+        <v>6388606</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3087,7 +3097,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3097,7 +3107,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3124,10 +3134,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128835464</v>
+        <v>128833068</v>
       </c>
       <c r="B25" t="n">
-        <v>86951</v>
+        <v>86941</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3135,34 +3145,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1988</v>
+        <v>3674</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Follingsbo Rosendal, Gtl</t>
+          <t>Follingbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>700940</v>
+        <v>700938</v>
       </c>
       <c r="R25" t="n">
-        <v>6388612</v>
+        <v>6388454</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3192,19 +3202,9 @@
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>15:01</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>15:01</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3219,12 +3219,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3234,7 +3234,7 @@
         <v>128835473</v>
       </c>
       <c r="B26" t="n">
-        <v>86774</v>
+        <v>86777</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3338,10 +3338,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128835470</v>
+        <v>128835444</v>
       </c>
       <c r="B27" t="n">
-        <v>86962</v>
+        <v>87023</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3349,21 +3349,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3599</v>
+        <v>3767</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3373,10 +3373,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>700910</v>
+        <v>700957</v>
       </c>
       <c r="R27" t="n">
-        <v>6388586</v>
+        <v>6388621</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3408,7 +3408,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3445,10 +3445,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128835444</v>
+        <v>128835470</v>
       </c>
       <c r="B28" t="n">
-        <v>87020</v>
+        <v>86965</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3456,21 +3456,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3767</v>
+        <v>3599</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3480,10 +3480,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>700957</v>
+        <v>700910</v>
       </c>
       <c r="R28" t="n">
-        <v>6388621</v>
+        <v>6388586</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3515,7 +3515,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3555,7 +3555,7 @@
         <v>128835448</v>
       </c>
       <c r="B29" t="n">
-        <v>86776</v>
+        <v>86779</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3662,7 +3662,7 @@
         <v>128835442</v>
       </c>
       <c r="B30" t="n">
-        <v>87020</v>
+        <v>87023</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3766,32 +3766,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128835471</v>
+        <v>128835455</v>
       </c>
       <c r="B31" t="n">
-        <v>86774</v>
+        <v>91005</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1985</v>
+        <v>5735</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Svartnande fingersvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Phaeoclavulina macrospora</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Brinkmann</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3801,10 +3801,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>700792</v>
+        <v>700897</v>
       </c>
       <c r="R31" t="n">
-        <v>6388508</v>
+        <v>6388579</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3855,6 +3855,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3873,32 +3874,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128835455</v>
+        <v>128835471</v>
       </c>
       <c r="B32" t="n">
-        <v>91002</v>
+        <v>86777</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5735</v>
+        <v>1985</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Svartnande fingersvamp</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phaeoclavulina macrospora</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Brinkmann</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3908,10 +3909,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>700897</v>
+        <v>700792</v>
       </c>
       <c r="R32" t="n">
-        <v>6388579</v>
+        <v>6388508</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3943,7 +3944,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3953,7 +3954,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3962,7 +3963,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3984,7 +3984,7 @@
         <v>128833061</v>
       </c>
       <c r="B33" t="n">
-        <v>86891</v>
+        <v>86894</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4081,7 +4081,7 @@
         <v>128835461</v>
       </c>
       <c r="B34" t="n">
-        <v>91055</v>
+        <v>91058</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4192,7 +4192,7 @@
         <v>128835476</v>
       </c>
       <c r="B35" t="n">
-        <v>87169</v>
+        <v>87172</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4308,7 +4308,7 @@
         <v>128833054</v>
       </c>
       <c r="B36" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4406,7 +4406,7 @@
         <v>128833066</v>
       </c>
       <c r="B37" t="n">
-        <v>86938</v>
+        <v>86941</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         <v>128833053</v>
       </c>
       <c r="B38" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         <v>128835474</v>
       </c>
       <c r="B39" t="n">
-        <v>86774</v>
+        <v>86777</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4712,7 +4712,7 @@
         <v>128833052</v>
       </c>
       <c r="B40" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
         <v>128833057</v>
       </c>
       <c r="B41" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4908,7 +4908,7 @@
         <v>128833055</v>
       </c>
       <c r="B42" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5006,7 +5006,7 @@
         <v>128833056</v>
       </c>
       <c r="B43" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5104,7 +5104,7 @@
         <v>128833070</v>
       </c>
       <c r="B44" t="n">
-        <v>86938</v>
+        <v>86941</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5201,7 +5201,7 @@
         <v>128833069</v>
       </c>
       <c r="B45" t="n">
-        <v>86938</v>
+        <v>86941</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5298,7 +5298,7 @@
         <v>128833065</v>
       </c>
       <c r="B46" t="n">
-        <v>86800</v>
+        <v>86803</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>128833064</v>
       </c>
       <c r="B47" t="n">
-        <v>86800</v>
+        <v>86803</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5492,7 +5492,7 @@
         <v>128833071</v>
       </c>
       <c r="B48" t="n">
-        <v>86938</v>
+        <v>86941</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         <v>128833067</v>
       </c>
       <c r="B49" t="n">
-        <v>86938</v>
+        <v>86941</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 6153-2024 artfynd.xlsx
+++ b/artfynd/A 6153-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128835463</v>
       </c>
       <c r="B2" t="n">
-        <v>86954</v>
+        <v>86957</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,45 +782,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128833059</v>
+        <v>128835469</v>
       </c>
       <c r="B3" t="n">
-        <v>8450</v>
+        <v>86968</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>3599</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Follingbo Rosendal, Gtl</t>
+          <t>Follingsbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>700942</v>
+        <v>700915</v>
       </c>
       <c r="R3" t="n">
-        <v>6388538</v>
+        <v>6388581</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -850,9 +850,24 @@
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>1 fk</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,57 +882,57 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128835469</v>
+        <v>128833059</v>
       </c>
       <c r="B4" t="n">
-        <v>86965</v>
+        <v>8450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3599</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Follingsbo Rosendal, Gtl</t>
+          <t>Follingbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>700915</v>
+        <v>700942</v>
       </c>
       <c r="R4" t="n">
-        <v>6388581</v>
+        <v>6388538</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -947,24 +962,9 @@
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>15:23</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>15:23</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>1 fk</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,44 +979,44 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128835480</v>
+        <v>128835449</v>
       </c>
       <c r="B5" t="n">
-        <v>92280</v>
+        <v>86782</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>232138</v>
+        <v>3762</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gul lammticka</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Albatrellus citrinus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Ryman</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>700814</v>
+        <v>700916</v>
       </c>
       <c r="R5" t="n">
-        <v>6388491</v>
+        <v>6388577</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,32 +1098,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128835449</v>
+        <v>128835480</v>
       </c>
       <c r="B6" t="n">
-        <v>86779</v>
+        <v>92283</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3762</v>
+        <v>232138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Gul lammticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Albatrellus citrinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Ryman</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>700916</v>
+        <v>700814</v>
       </c>
       <c r="R6" t="n">
-        <v>6388577</v>
+        <v>6388491</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1208,7 +1208,7 @@
         <v>128835494</v>
       </c>
       <c r="B7" t="n">
-        <v>86941</v>
+        <v>86944</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>128835466</v>
       </c>
       <c r="B8" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         <v>128835475</v>
       </c>
       <c r="B9" t="n">
-        <v>86777</v>
+        <v>86780</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>128835492</v>
       </c>
       <c r="B10" t="n">
-        <v>106281</v>
+        <v>106284</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1639,32 +1639,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128835493</v>
+        <v>128835443</v>
       </c>
       <c r="B11" t="n">
-        <v>86941</v>
+        <v>87026</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>700828</v>
+        <v>700956</v>
       </c>
       <c r="R11" t="n">
-        <v>6388554</v>
+        <v>6388619</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1719,7 +1719,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1746,32 +1746,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128835443</v>
+        <v>128835493</v>
       </c>
       <c r="B12" t="n">
-        <v>87023</v>
+        <v>86944</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3767</v>
+        <v>3674</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1781,10 +1781,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>700956</v>
+        <v>700828</v>
       </c>
       <c r="R12" t="n">
-        <v>6388619</v>
+        <v>6388554</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1856,7 +1856,7 @@
         <v>128835441</v>
       </c>
       <c r="B13" t="n">
-        <v>87023</v>
+        <v>87026</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>128835450</v>
       </c>
       <c r="B14" t="n">
-        <v>86779</v>
+        <v>86782</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>128835462</v>
       </c>
       <c r="B15" t="n">
-        <v>86954</v>
+        <v>86957</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>128835454</v>
       </c>
       <c r="B16" t="n">
-        <v>91005</v>
+        <v>91008</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2287,32 +2287,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128835499</v>
+        <v>128835465</v>
       </c>
       <c r="B17" t="n">
-        <v>86941</v>
+        <v>86981</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2322,10 +2322,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>700938</v>
+        <v>700869</v>
       </c>
       <c r="R17" t="n">
-        <v>6388610</v>
+        <v>6388563</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2357,7 +2357,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2367,7 +2367,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2376,6 +2376,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2394,10 +2395,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128833063</v>
+        <v>128835499</v>
       </c>
       <c r="B18" t="n">
-        <v>86803</v>
+        <v>86944</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2405,34 +2406,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3712</v>
+        <v>3674</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Follingbo Rosendal, Gtl</t>
+          <t>Follingsbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>700953</v>
+        <v>700938</v>
       </c>
       <c r="R18" t="n">
-        <v>6388454</v>
+        <v>6388610</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2462,9 +2463,19 @@
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2479,57 +2490,57 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128835465</v>
+        <v>128833063</v>
       </c>
       <c r="B19" t="n">
-        <v>86978</v>
+        <v>86806</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Follingsbo Rosendal, Gtl</t>
+          <t>Follingbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>700869</v>
+        <v>700953</v>
       </c>
       <c r="R19" t="n">
-        <v>6388563</v>
+        <v>6388454</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2559,50 +2570,39 @@
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>16:25</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>16:25</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128835497</v>
+        <v>128835498</v>
       </c>
       <c r="B20" t="n">
-        <v>86941</v>
+        <v>86944</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2634,10 +2634,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>700948</v>
+        <v>700817</v>
       </c>
       <c r="R20" t="n">
-        <v>6388722</v>
+        <v>6388548</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2706,10 +2706,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128835498</v>
+        <v>128835497</v>
       </c>
       <c r="B21" t="n">
-        <v>86941</v>
+        <v>86944</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>700817</v>
+        <v>700948</v>
       </c>
       <c r="R21" t="n">
-        <v>6388548</v>
+        <v>6388722</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2813,10 +2813,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128835472</v>
+        <v>128835490</v>
       </c>
       <c r="B22" t="n">
-        <v>86777</v>
+        <v>86828</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2824,16 +2824,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1985</v>
+        <v>424</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2848,10 +2848,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>700957</v>
+        <v>700954</v>
       </c>
       <c r="R22" t="n">
-        <v>6388630</v>
+        <v>6388606</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2883,7 +2883,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2920,32 +2920,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128835464</v>
+        <v>128835472</v>
       </c>
       <c r="B23" t="n">
-        <v>86954</v>
+        <v>86780</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1988</v>
+        <v>1985</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2955,10 +2955,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>700940</v>
+        <v>700957</v>
       </c>
       <c r="R23" t="n">
-        <v>6388612</v>
+        <v>6388630</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2990,7 +2990,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3027,32 +3027,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128835490</v>
+        <v>128835464</v>
       </c>
       <c r="B24" t="n">
-        <v>86825</v>
+        <v>86957</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>424</v>
+        <v>1988</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3062,10 +3062,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>700954</v>
+        <v>700940</v>
       </c>
       <c r="R24" t="n">
-        <v>6388606</v>
+        <v>6388612</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3097,7 +3097,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3107,7 +3107,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3137,7 +3137,7 @@
         <v>128833068</v>
       </c>
       <c r="B25" t="n">
-        <v>86941</v>
+        <v>86944</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3231,10 +3231,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128835473</v>
+        <v>128835444</v>
       </c>
       <c r="B26" t="n">
-        <v>86777</v>
+        <v>87026</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3242,21 +3242,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1985</v>
+        <v>3767</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3266,10 +3266,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>700804</v>
+        <v>700957</v>
       </c>
       <c r="R26" t="n">
-        <v>6388505</v>
+        <v>6388621</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3301,7 +3301,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3311,7 +3311,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3338,10 +3338,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128835444</v>
+        <v>128835470</v>
       </c>
       <c r="B27" t="n">
-        <v>87023</v>
+        <v>86968</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3349,21 +3349,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3767</v>
+        <v>3599</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3373,10 +3373,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>700957</v>
+        <v>700910</v>
       </c>
       <c r="R27" t="n">
-        <v>6388621</v>
+        <v>6388586</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3408,7 +3408,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3445,10 +3445,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128835470</v>
+        <v>128835473</v>
       </c>
       <c r="B28" t="n">
-        <v>86965</v>
+        <v>86780</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3456,21 +3456,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3599</v>
+        <v>1985</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3480,10 +3480,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>700910</v>
+        <v>700804</v>
       </c>
       <c r="R28" t="n">
-        <v>6388586</v>
+        <v>6388505</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3515,7 +3515,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3555,7 +3555,7 @@
         <v>128835448</v>
       </c>
       <c r="B29" t="n">
-        <v>86779</v>
+        <v>86782</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3662,7 +3662,7 @@
         <v>128835442</v>
       </c>
       <c r="B30" t="n">
-        <v>87023</v>
+        <v>87026</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3769,7 +3769,7 @@
         <v>128835455</v>
       </c>
       <c r="B31" t="n">
-        <v>91005</v>
+        <v>91008</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         <v>128835471</v>
       </c>
       <c r="B32" t="n">
-        <v>86777</v>
+        <v>86780</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3984,7 +3984,7 @@
         <v>128833061</v>
       </c>
       <c r="B33" t="n">
-        <v>86894</v>
+        <v>86897</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4081,7 +4081,7 @@
         <v>128835461</v>
       </c>
       <c r="B34" t="n">
-        <v>91058</v>
+        <v>91061</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4192,7 +4192,7 @@
         <v>128835476</v>
       </c>
       <c r="B35" t="n">
-        <v>87172</v>
+        <v>87175</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4308,7 +4308,7 @@
         <v>128833054</v>
       </c>
       <c r="B36" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4406,7 +4406,7 @@
         <v>128833066</v>
       </c>
       <c r="B37" t="n">
-        <v>86941</v>
+        <v>86944</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         <v>128833053</v>
       </c>
       <c r="B38" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         <v>128835474</v>
       </c>
       <c r="B39" t="n">
-        <v>86777</v>
+        <v>86780</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4712,7 +4712,7 @@
         <v>128833052</v>
       </c>
       <c r="B40" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
         <v>128833057</v>
       </c>
       <c r="B41" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4905,32 +4905,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128833055</v>
+        <v>128833070</v>
       </c>
       <c r="B42" t="n">
-        <v>86978</v>
+        <v>86944</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4940,10 +4940,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>700996</v>
+        <v>701026</v>
       </c>
       <c r="R42" t="n">
-        <v>6388473</v>
+        <v>6388477</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4984,7 +4984,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5006,7 +5005,7 @@
         <v>128833056</v>
       </c>
       <c r="B43" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5101,32 +5100,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128833070</v>
+        <v>128833055</v>
       </c>
       <c r="B44" t="n">
-        <v>86941</v>
+        <v>86981</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5136,10 +5135,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>701026</v>
+        <v>700996</v>
       </c>
       <c r="R44" t="n">
-        <v>6388477</v>
+        <v>6388473</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5180,6 +5179,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5201,7 +5201,7 @@
         <v>128833069</v>
       </c>
       <c r="B45" t="n">
-        <v>86941</v>
+        <v>86944</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5298,7 +5298,7 @@
         <v>128833065</v>
       </c>
       <c r="B46" t="n">
-        <v>86803</v>
+        <v>86806</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>128833064</v>
       </c>
       <c r="B47" t="n">
-        <v>86803</v>
+        <v>86806</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5492,7 +5492,7 @@
         <v>128833071</v>
       </c>
       <c r="B48" t="n">
-        <v>86941</v>
+        <v>86944</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         <v>128833067</v>
       </c>
       <c r="B49" t="n">
-        <v>86941</v>
+        <v>86944</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 6153-2024 artfynd.xlsx
+++ b/artfynd/A 6153-2024 artfynd.xlsx
@@ -1420,32 +1420,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128835475</v>
+        <v>128835492</v>
       </c>
       <c r="B9" t="n">
-        <v>86780</v>
+        <v>106284</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1985</v>
+        <v>220785</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1455,10 +1455,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>700804</v>
+        <v>700799</v>
       </c>
       <c r="R9" t="n">
-        <v>6388482</v>
+        <v>6388520</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1500,7 +1500,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Mycket hlgvuxen 12+ Meter</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1527,32 +1532,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128835492</v>
+        <v>128835475</v>
       </c>
       <c r="B10" t="n">
-        <v>106284</v>
+        <v>86780</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220785</v>
+        <v>1985</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1562,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>700799</v>
+        <v>700804</v>
       </c>
       <c r="R10" t="n">
-        <v>6388520</v>
+        <v>6388482</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1597,7 +1602,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1607,12 +1612,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:45</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Mycket hlgvuxen 12+ Meter</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1639,32 +1639,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128835443</v>
+        <v>128835493</v>
       </c>
       <c r="B11" t="n">
-        <v>87026</v>
+        <v>86944</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3767</v>
+        <v>3674</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>700956</v>
+        <v>700828</v>
       </c>
       <c r="R11" t="n">
-        <v>6388619</v>
+        <v>6388554</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1719,7 +1719,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1746,32 +1746,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128835493</v>
+        <v>128835443</v>
       </c>
       <c r="B12" t="n">
-        <v>86944</v>
+        <v>87026</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1781,10 +1781,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>700828</v>
+        <v>700956</v>
       </c>
       <c r="R12" t="n">
-        <v>6388554</v>
+        <v>6388619</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2174,32 +2174,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128835454</v>
+        <v>128835499</v>
       </c>
       <c r="B16" t="n">
-        <v>91008</v>
+        <v>86944</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5735</v>
+        <v>3674</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svartnande fingersvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phaeoclavulina macrospora</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Brinkmann</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2209,10 +2209,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>700887</v>
+        <v>700938</v>
       </c>
       <c r="R16" t="n">
-        <v>6388572</v>
+        <v>6388610</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2244,7 +2244,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2254,12 +2254,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Riklig förekomst, Minst 47 fk i en 13 Linje!! Undr En 7-8 meter hög en</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2268,7 +2263,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2287,45 +2281,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128835465</v>
+        <v>128833063</v>
       </c>
       <c r="B17" t="n">
-        <v>86981</v>
+        <v>86806</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Follingsbo Rosendal, Gtl</t>
+          <t>Follingbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>700869</v>
+        <v>700953</v>
       </c>
       <c r="R17" t="n">
-        <v>6388563</v>
+        <v>6388454</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2355,72 +2349,61 @@
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>16:25</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>16:25</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128835499</v>
+        <v>128835454</v>
       </c>
       <c r="B18" t="n">
-        <v>86944</v>
+        <v>91008</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3674</v>
+        <v>5735</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Svartnande fingersvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Phaeoclavulina macrospora</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brinkmann</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2430,10 +2413,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>700938</v>
+        <v>700887</v>
       </c>
       <c r="R18" t="n">
-        <v>6388610</v>
+        <v>6388572</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2465,7 +2448,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2475,7 +2458,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Riklig förekomst, Minst 47 fk i en 13 Linje!! Undr En 7-8 meter hög en</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2484,6 +2472,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2502,45 +2491,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128833063</v>
+        <v>128835465</v>
       </c>
       <c r="B19" t="n">
-        <v>86806</v>
+        <v>86981</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Follingbo Rosendal, Gtl</t>
+          <t>Follingsbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>700953</v>
+        <v>700869</v>
       </c>
       <c r="R19" t="n">
-        <v>6388454</v>
+        <v>6388563</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2570,29 +2559,40 @@
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2813,10 +2813,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128835490</v>
+        <v>128835472</v>
       </c>
       <c r="B22" t="n">
-        <v>86828</v>
+        <v>86780</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2824,16 +2824,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>424</v>
+        <v>1985</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2848,10 +2848,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>700954</v>
+        <v>700957</v>
       </c>
       <c r="R22" t="n">
-        <v>6388606</v>
+        <v>6388630</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2883,7 +2883,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2920,32 +2920,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128835472</v>
+        <v>128835464</v>
       </c>
       <c r="B23" t="n">
-        <v>86780</v>
+        <v>86957</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1985</v>
+        <v>1988</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2955,10 +2955,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>700957</v>
+        <v>700940</v>
       </c>
       <c r="R23" t="n">
-        <v>6388630</v>
+        <v>6388612</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2990,7 +2990,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3027,10 +3027,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128835464</v>
+        <v>128833068</v>
       </c>
       <c r="B24" t="n">
-        <v>86957</v>
+        <v>86944</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3038,34 +3038,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1988</v>
+        <v>3674</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Follingsbo Rosendal, Gtl</t>
+          <t>Follingbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>700940</v>
+        <v>700938</v>
       </c>
       <c r="R24" t="n">
-        <v>6388612</v>
+        <v>6388454</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3095,19 +3095,9 @@
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>15:01</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>15:01</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3122,57 +3112,57 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128833068</v>
+        <v>128835490</v>
       </c>
       <c r="B25" t="n">
-        <v>86944</v>
+        <v>86828</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3674</v>
+        <v>424</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Follingbo Rosendal, Gtl</t>
+          <t>Follingsbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>700938</v>
+        <v>700954</v>
       </c>
       <c r="R25" t="n">
-        <v>6388454</v>
+        <v>6388606</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3202,9 +3192,19 @@
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3219,22 +3219,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128835444</v>
+        <v>128835473</v>
       </c>
       <c r="B26" t="n">
-        <v>87026</v>
+        <v>86780</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3242,21 +3242,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3767</v>
+        <v>1985</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3266,10 +3266,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>700957</v>
+        <v>700804</v>
       </c>
       <c r="R26" t="n">
-        <v>6388621</v>
+        <v>6388505</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3301,7 +3301,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3311,7 +3311,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3338,10 +3338,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128835470</v>
+        <v>128835444</v>
       </c>
       <c r="B27" t="n">
-        <v>86968</v>
+        <v>87026</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3349,21 +3349,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3599</v>
+        <v>3767</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3373,10 +3373,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>700910</v>
+        <v>700957</v>
       </c>
       <c r="R27" t="n">
-        <v>6388586</v>
+        <v>6388621</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3408,7 +3408,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3445,10 +3445,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128835473</v>
+        <v>128835470</v>
       </c>
       <c r="B28" t="n">
-        <v>86780</v>
+        <v>86968</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3456,21 +3456,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1985</v>
+        <v>3599</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3480,10 +3480,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>700804</v>
+        <v>700910</v>
       </c>
       <c r="R28" t="n">
-        <v>6388505</v>
+        <v>6388586</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3515,7 +3515,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3874,10 +3874,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128835471</v>
+        <v>128833061</v>
       </c>
       <c r="B32" t="n">
-        <v>86780</v>
+        <v>86897</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3885,34 +3885,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1985</v>
+        <v>248956</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Follingsbo Rosendal, Gtl</t>
+          <t>Follingbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>700792</v>
+        <v>700935</v>
       </c>
       <c r="R32" t="n">
-        <v>6388508</v>
+        <v>6388458</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3942,19 +3942,9 @@
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>17:02</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>17:02</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3969,22 +3959,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128833061</v>
+        <v>128835471</v>
       </c>
       <c r="B33" t="n">
-        <v>86897</v>
+        <v>86780</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3992,34 +3982,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>248956</v>
+        <v>1985</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Follingbo Rosendal, Gtl</t>
+          <t>Follingsbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>700935</v>
+        <v>700792</v>
       </c>
       <c r="R33" t="n">
-        <v>6388458</v>
+        <v>6388508</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4049,9 +4039,19 @@
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>17:02</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4066,12 +4066,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4598,48 +4598,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128835474</v>
+        <v>128833052</v>
       </c>
       <c r="B39" t="n">
-        <v>86780</v>
+        <v>86981</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1985</v>
+        <v>6003295</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Follingsbo Rosendal, Gtl</t>
+          <t>Follingbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>700966</v>
+        <v>701151</v>
       </c>
       <c r="R39" t="n">
-        <v>6388635</v>
+        <v>6388524</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4669,19 +4666,9 @@
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>14:32</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>14:32</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4697,57 +4684,60 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128833052</v>
+        <v>128835474</v>
       </c>
       <c r="B40" t="n">
-        <v>86981</v>
+        <v>86780</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6003295</v>
+        <v>1985</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Follingbo Rosendal, Gtl</t>
+          <t>Follingsbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>701151</v>
+        <v>700966</v>
       </c>
       <c r="R40" t="n">
-        <v>6388524</v>
+        <v>6388635</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4777,9 +4767,19 @@
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4795,12 +4795,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -5002,7 +5002,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128833056</v>
+        <v>128833055</v>
       </c>
       <c r="B43" t="n">
         <v>86981</v>
@@ -5037,10 +5037,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>701017</v>
+        <v>700996</v>
       </c>
       <c r="R43" t="n">
-        <v>6388485</v>
+        <v>6388473</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5100,7 +5100,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128833055</v>
+        <v>128833056</v>
       </c>
       <c r="B44" t="n">
         <v>86981</v>
@@ -5135,10 +5135,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>700996</v>
+        <v>701017</v>
       </c>
       <c r="R44" t="n">
-        <v>6388473</v>
+        <v>6388485</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>

--- a/artfynd/A 6153-2024 artfynd.xlsx
+++ b/artfynd/A 6153-2024 artfynd.xlsx
@@ -991,32 +991,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128835449</v>
+        <v>128835480</v>
       </c>
       <c r="B5" t="n">
-        <v>86782</v>
+        <v>92283</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3762</v>
+        <v>232138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Gul lammticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Albatrellus citrinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Ryman</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>700916</v>
+        <v>700814</v>
       </c>
       <c r="R5" t="n">
-        <v>6388577</v>
+        <v>6388491</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,32 +1098,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128835480</v>
+        <v>128835449</v>
       </c>
       <c r="B6" t="n">
-        <v>92283</v>
+        <v>86782</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>232138</v>
+        <v>3762</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gul lammticka</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Albatrellus citrinus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Ryman</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>700814</v>
+        <v>700916</v>
       </c>
       <c r="R6" t="n">
-        <v>6388491</v>
+        <v>6388577</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1420,32 +1420,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128835492</v>
+        <v>128835475</v>
       </c>
       <c r="B9" t="n">
-        <v>106284</v>
+        <v>86780</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220785</v>
+        <v>1985</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1455,10 +1455,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>700799</v>
+        <v>700804</v>
       </c>
       <c r="R9" t="n">
-        <v>6388520</v>
+        <v>6388482</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1500,12 +1500,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:45</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Mycket hlgvuxen 12+ Meter</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1532,32 +1527,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128835475</v>
+        <v>128835492</v>
       </c>
       <c r="B10" t="n">
-        <v>86780</v>
+        <v>106284</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1985</v>
+        <v>220785</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1567,10 +1562,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>700804</v>
+        <v>700799</v>
       </c>
       <c r="R10" t="n">
-        <v>6388482</v>
+        <v>6388520</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1602,7 +1597,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1612,7 +1607,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Mycket hlgvuxen 12+ Meter</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2174,32 +2174,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128835499</v>
+        <v>128835454</v>
       </c>
       <c r="B16" t="n">
-        <v>86944</v>
+        <v>91008</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3674</v>
+        <v>5735</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Svartnande fingersvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Phaeoclavulina macrospora</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brinkmann</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2209,10 +2209,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>700938</v>
+        <v>700887</v>
       </c>
       <c r="R16" t="n">
-        <v>6388610</v>
+        <v>6388572</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2244,7 +2244,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2254,7 +2254,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Riklig förekomst, Minst 47 fk i en 13 Linje!! Undr En 7-8 meter hög en</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2263,6 +2268,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2281,10 +2287,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128833063</v>
+        <v>128835499</v>
       </c>
       <c r="B17" t="n">
-        <v>86806</v>
+        <v>86944</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2292,34 +2298,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3712</v>
+        <v>3674</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Follingbo Rosendal, Gtl</t>
+          <t>Follingsbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>700953</v>
+        <v>700938</v>
       </c>
       <c r="R17" t="n">
-        <v>6388454</v>
+        <v>6388610</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2349,9 +2355,19 @@
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2366,57 +2382,57 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128835454</v>
+        <v>128833063</v>
       </c>
       <c r="B18" t="n">
-        <v>91008</v>
+        <v>86806</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5735</v>
+        <v>3712</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svartnande fingersvamp</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phaeoclavulina macrospora</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Brinkmann</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Follingsbo Rosendal, Gtl</t>
+          <t>Follingbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>700887</v>
+        <v>700953</v>
       </c>
       <c r="R18" t="n">
-        <v>6388572</v>
+        <v>6388454</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2446,45 +2462,29 @@
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Riklig förekomst, Minst 47 fk i en 13 Linje!! Undr En 7-8 meter hög en</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -4598,45 +4598,48 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128833052</v>
+        <v>128835474</v>
       </c>
       <c r="B39" t="n">
-        <v>86981</v>
+        <v>86780</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6003295</v>
+        <v>1985</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Follingbo Rosendal, Gtl</t>
+          <t>Follingsbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>701151</v>
+        <v>700966</v>
       </c>
       <c r="R39" t="n">
-        <v>6388524</v>
+        <v>6388635</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4666,9 +4669,19 @@
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4684,60 +4697,57 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128835474</v>
+        <v>128833052</v>
       </c>
       <c r="B40" t="n">
-        <v>86780</v>
+        <v>86981</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1985</v>
+        <v>6003295</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Follingsbo Rosendal, Gtl</t>
+          <t>Follingbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>700966</v>
+        <v>701151</v>
       </c>
       <c r="R40" t="n">
-        <v>6388635</v>
+        <v>6388524</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4767,19 +4777,9 @@
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>14:32</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>14:32</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4795,12 +4795,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>

--- a/artfynd/A 6153-2024 artfynd.xlsx
+++ b/artfynd/A 6153-2024 artfynd.xlsx
@@ -782,45 +782,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128835469</v>
+        <v>128833059</v>
       </c>
       <c r="B3" t="n">
-        <v>86968</v>
+        <v>8450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3599</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Follingsbo Rosendal, Gtl</t>
+          <t>Follingbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>700915</v>
+        <v>700942</v>
       </c>
       <c r="R3" t="n">
-        <v>6388581</v>
+        <v>6388538</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -850,24 +850,9 @@
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>15:23</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>15:23</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>1 fk</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,57 +867,57 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128833059</v>
+        <v>128835469</v>
       </c>
       <c r="B4" t="n">
-        <v>8450</v>
+        <v>86968</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>3599</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Follingbo Rosendal, Gtl</t>
+          <t>Follingsbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>700942</v>
+        <v>700915</v>
       </c>
       <c r="R4" t="n">
-        <v>6388538</v>
+        <v>6388581</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -962,9 +947,24 @@
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>1 fk</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,12 +979,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1205,32 +1205,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128835494</v>
+        <v>128835466</v>
       </c>
       <c r="B7" t="n">
-        <v>86944</v>
+        <v>86981</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>700929</v>
+        <v>700824</v>
       </c>
       <c r="R7" t="n">
-        <v>6388692</v>
+        <v>6388554</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1275,7 +1275,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1294,6 +1294,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1312,32 +1313,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128835466</v>
+        <v>128835494</v>
       </c>
       <c r="B8" t="n">
-        <v>86981</v>
+        <v>86944</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1347,10 +1348,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>700824</v>
+        <v>700929</v>
       </c>
       <c r="R8" t="n">
-        <v>6388554</v>
+        <v>6388692</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1382,7 +1383,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1392,7 +1393,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1401,7 +1402,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -2174,45 +2174,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128835454</v>
+        <v>128833063</v>
       </c>
       <c r="B16" t="n">
-        <v>91008</v>
+        <v>86806</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5735</v>
+        <v>3712</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svartnande fingersvamp</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phaeoclavulina macrospora</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Brinkmann</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Follingsbo Rosendal, Gtl</t>
+          <t>Follingbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>700887</v>
+        <v>700953</v>
       </c>
       <c r="R16" t="n">
-        <v>6388572</v>
+        <v>6388454</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2242,77 +2242,61 @@
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Riklig förekomst, Minst 47 fk i en 13 Linje!! Undr En 7-8 meter hög en</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128835499</v>
+        <v>128835465</v>
       </c>
       <c r="B17" t="n">
-        <v>86944</v>
+        <v>86981</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2322,10 +2306,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>700938</v>
+        <v>700869</v>
       </c>
       <c r="R17" t="n">
-        <v>6388610</v>
+        <v>6388563</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2357,7 +2341,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2367,7 +2351,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2376,6 +2360,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2394,10 +2379,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128833063</v>
+        <v>128835499</v>
       </c>
       <c r="B18" t="n">
-        <v>86806</v>
+        <v>86944</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2405,34 +2390,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3712</v>
+        <v>3674</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Follingbo Rosendal, Gtl</t>
+          <t>Follingsbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>700953</v>
+        <v>700938</v>
       </c>
       <c r="R18" t="n">
-        <v>6388454</v>
+        <v>6388610</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2462,9 +2447,19 @@
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2479,44 +2474,44 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128835465</v>
+        <v>128835454</v>
       </c>
       <c r="B19" t="n">
-        <v>86981</v>
+        <v>91008</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6003295</v>
+        <v>5735</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartnande fingersvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Phaeoclavulina macrospora</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brinkmann</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2526,10 +2521,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>700869</v>
+        <v>700887</v>
       </c>
       <c r="R19" t="n">
-        <v>6388563</v>
+        <v>6388572</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2561,7 +2556,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2571,7 +2566,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Riklig förekomst, Minst 47 fk i en 13 Linje!! Undr En 7-8 meter hög en</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2599,7 +2599,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128835498</v>
+        <v>128835497</v>
       </c>
       <c r="B20" t="n">
         <v>86944</v>
@@ -2634,10 +2634,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>700817</v>
+        <v>700948</v>
       </c>
       <c r="R20" t="n">
-        <v>6388548</v>
+        <v>6388722</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2706,7 +2706,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128835497</v>
+        <v>128835498</v>
       </c>
       <c r="B21" t="n">
         <v>86944</v>
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>700948</v>
+        <v>700817</v>
       </c>
       <c r="R21" t="n">
-        <v>6388722</v>
+        <v>6388548</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2813,45 +2813,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128835472</v>
+        <v>128833068</v>
       </c>
       <c r="B22" t="n">
-        <v>86780</v>
+        <v>86944</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1985</v>
+        <v>3674</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Follingsbo Rosendal, Gtl</t>
+          <t>Follingbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>700957</v>
+        <v>700938</v>
       </c>
       <c r="R22" t="n">
-        <v>6388630</v>
+        <v>6388454</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2881,19 +2881,9 @@
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>14:39</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>14:39</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2908,44 +2898,44 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128835464</v>
+        <v>128835490</v>
       </c>
       <c r="B23" t="n">
-        <v>86957</v>
+        <v>86828</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1988</v>
+        <v>424</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2955,10 +2945,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>700940</v>
+        <v>700954</v>
       </c>
       <c r="R23" t="n">
-        <v>6388612</v>
+        <v>6388606</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2990,7 +2980,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3000,7 +2990,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3027,45 +3017,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128833068</v>
+        <v>128835472</v>
       </c>
       <c r="B24" t="n">
-        <v>86944</v>
+        <v>86780</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3674</v>
+        <v>1985</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Follingbo Rosendal, Gtl</t>
+          <t>Follingsbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>700938</v>
+        <v>700957</v>
       </c>
       <c r="R24" t="n">
-        <v>6388454</v>
+        <v>6388630</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3095,9 +3085,19 @@
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3112,44 +3112,44 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128835490</v>
+        <v>128835464</v>
       </c>
       <c r="B25" t="n">
-        <v>86828</v>
+        <v>86957</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>424</v>
+        <v>1988</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3159,10 +3159,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>700954</v>
+        <v>700940</v>
       </c>
       <c r="R25" t="n">
-        <v>6388606</v>
+        <v>6388612</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3194,7 +3194,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3204,7 +3204,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3338,10 +3338,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128835444</v>
+        <v>128835470</v>
       </c>
       <c r="B27" t="n">
-        <v>87026</v>
+        <v>86968</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3349,21 +3349,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3767</v>
+        <v>3599</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3373,10 +3373,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>700957</v>
+        <v>700910</v>
       </c>
       <c r="R27" t="n">
-        <v>6388621</v>
+        <v>6388586</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3408,7 +3408,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3445,10 +3445,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128835470</v>
+        <v>128835444</v>
       </c>
       <c r="B28" t="n">
-        <v>86968</v>
+        <v>87026</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3456,21 +3456,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3599</v>
+        <v>3767</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3480,10 +3480,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>700910</v>
+        <v>700957</v>
       </c>
       <c r="R28" t="n">
-        <v>6388586</v>
+        <v>6388621</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3515,7 +3515,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3552,32 +3552,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128835448</v>
+        <v>128835442</v>
       </c>
       <c r="B29" t="n">
-        <v>86782</v>
+        <v>87026</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3762</v>
+        <v>3767</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3587,10 +3587,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>700817</v>
+        <v>700952</v>
       </c>
       <c r="R29" t="n">
-        <v>6388555</v>
+        <v>6388607</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3622,7 +3622,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3659,32 +3659,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128835442</v>
+        <v>128835448</v>
       </c>
       <c r="B30" t="n">
-        <v>87026</v>
+        <v>86782</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3767</v>
+        <v>3762</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3694,10 +3694,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>700952</v>
+        <v>700817</v>
       </c>
       <c r="R30" t="n">
-        <v>6388607</v>
+        <v>6388555</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3766,32 +3766,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128835455</v>
+        <v>128835471</v>
       </c>
       <c r="B31" t="n">
-        <v>91008</v>
+        <v>86780</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5735</v>
+        <v>1985</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Svartnande fingersvamp</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phaeoclavulina macrospora</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Brinkmann</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3801,10 +3801,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>700897</v>
+        <v>700792</v>
       </c>
       <c r="R31" t="n">
-        <v>6388579</v>
+        <v>6388508</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3855,7 +3855,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3874,45 +3873,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128833061</v>
+        <v>128835455</v>
       </c>
       <c r="B32" t="n">
-        <v>86897</v>
+        <v>91008</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>248956</v>
+        <v>5735</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Svartnande fingersvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Phaeoclavulina macrospora</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Brinkmann</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Follingbo Rosendal, Gtl</t>
+          <t>Follingsbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>700935</v>
+        <v>700897</v>
       </c>
       <c r="R32" t="n">
-        <v>6388458</v>
+        <v>6388579</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3942,39 +3941,50 @@
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128835471</v>
+        <v>128833061</v>
       </c>
       <c r="B33" t="n">
-        <v>86780</v>
+        <v>86897</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3982,34 +3992,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1985</v>
+        <v>248956</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Follingsbo Rosendal, Gtl</t>
+          <t>Follingbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>700792</v>
+        <v>700935</v>
       </c>
       <c r="R33" t="n">
-        <v>6388508</v>
+        <v>6388458</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4039,19 +4049,9 @@
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>17:02</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>17:02</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4066,12 +4066,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4403,32 +4403,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128833066</v>
+        <v>128833053</v>
       </c>
       <c r="B37" t="n">
-        <v>86944</v>
+        <v>86981</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4438,10 +4438,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>701012</v>
+        <v>700979</v>
       </c>
       <c r="R37" t="n">
-        <v>6388573</v>
+        <v>6388550</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4482,6 +4482,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4500,32 +4501,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128833053</v>
+        <v>128833066</v>
       </c>
       <c r="B38" t="n">
-        <v>86981</v>
+        <v>86944</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4535,10 +4536,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>700979</v>
+        <v>701012</v>
       </c>
       <c r="R38" t="n">
-        <v>6388550</v>
+        <v>6388573</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4579,7 +4580,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4905,32 +4905,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128833070</v>
+        <v>128833055</v>
       </c>
       <c r="B42" t="n">
-        <v>86944</v>
+        <v>86981</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4940,10 +4940,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>701026</v>
+        <v>700996</v>
       </c>
       <c r="R42" t="n">
-        <v>6388477</v>
+        <v>6388473</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4984,6 +4984,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5002,7 +5003,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128833055</v>
+        <v>128833056</v>
       </c>
       <c r="B43" t="n">
         <v>86981</v>
@@ -5037,10 +5038,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>700996</v>
+        <v>701017</v>
       </c>
       <c r="R43" t="n">
-        <v>6388473</v>
+        <v>6388485</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5100,32 +5101,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128833056</v>
+        <v>128833070</v>
       </c>
       <c r="B44" t="n">
-        <v>86981</v>
+        <v>86944</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5135,10 +5136,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>701017</v>
+        <v>701026</v>
       </c>
       <c r="R44" t="n">
-        <v>6388485</v>
+        <v>6388477</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5179,7 +5180,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 6153-2024 artfynd.xlsx
+++ b/artfynd/A 6153-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128835463</v>
       </c>
       <c r="B2" t="n">
-        <v>86957</v>
+        <v>86961</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,45 +782,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128833059</v>
+        <v>128835469</v>
       </c>
       <c r="B3" t="n">
-        <v>8450</v>
+        <v>86972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>3599</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Follingbo Rosendal, Gtl</t>
+          <t>Follingsbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>700942</v>
+        <v>700915</v>
       </c>
       <c r="R3" t="n">
-        <v>6388538</v>
+        <v>6388581</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -850,9 +850,24 @@
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>1 fk</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,57 +882,57 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128835469</v>
+        <v>128833059</v>
       </c>
       <c r="B4" t="n">
-        <v>86968</v>
+        <v>8450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3599</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Follingsbo Rosendal, Gtl</t>
+          <t>Follingbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>700915</v>
+        <v>700942</v>
       </c>
       <c r="R4" t="n">
-        <v>6388581</v>
+        <v>6388538</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -947,24 +962,9 @@
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>15:23</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>15:23</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>1 fk</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,44 +979,44 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128835480</v>
+        <v>128835449</v>
       </c>
       <c r="B5" t="n">
-        <v>92283</v>
+        <v>86786</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>232138</v>
+        <v>3762</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gul lammticka</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Albatrellus citrinus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Ryman</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>700814</v>
+        <v>700916</v>
       </c>
       <c r="R5" t="n">
-        <v>6388491</v>
+        <v>6388577</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,32 +1098,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128835449</v>
+        <v>128835480</v>
       </c>
       <c r="B6" t="n">
-        <v>86782</v>
+        <v>92290</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3762</v>
+        <v>232138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Gul lammticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Albatrellus citrinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Ryman</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>700916</v>
+        <v>700814</v>
       </c>
       <c r="R6" t="n">
-        <v>6388577</v>
+        <v>6388491</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1208,7 +1208,7 @@
         <v>128835466</v>
       </c>
       <c r="B7" t="n">
-        <v>86981</v>
+        <v>86985</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1316,7 +1316,7 @@
         <v>128835494</v>
       </c>
       <c r="B8" t="n">
-        <v>86944</v>
+        <v>86948</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1420,32 +1420,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128835475</v>
+        <v>128835492</v>
       </c>
       <c r="B9" t="n">
-        <v>86780</v>
+        <v>106294</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1985</v>
+        <v>220785</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1455,10 +1455,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>700804</v>
+        <v>700799</v>
       </c>
       <c r="R9" t="n">
-        <v>6388482</v>
+        <v>6388520</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1500,7 +1500,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Mycket hlgvuxen 12+ Meter</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1527,32 +1532,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128835492</v>
+        <v>128835475</v>
       </c>
       <c r="B10" t="n">
-        <v>106284</v>
+        <v>86784</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220785</v>
+        <v>1985</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1562,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>700799</v>
+        <v>700804</v>
       </c>
       <c r="R10" t="n">
-        <v>6388520</v>
+        <v>6388482</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1597,7 +1602,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1607,12 +1612,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:45</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Mycket hlgvuxen 12+ Meter</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1642,7 +1642,7 @@
         <v>128835493</v>
       </c>
       <c r="B11" t="n">
-        <v>86944</v>
+        <v>86948</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         <v>128835443</v>
       </c>
       <c r="B12" t="n">
-        <v>87026</v>
+        <v>87030</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>128835441</v>
       </c>
       <c r="B13" t="n">
-        <v>87026</v>
+        <v>87030</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>128835450</v>
       </c>
       <c r="B14" t="n">
-        <v>86782</v>
+        <v>86786</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>128835462</v>
       </c>
       <c r="B15" t="n">
-        <v>86957</v>
+        <v>86961</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2174,10 +2174,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128833063</v>
+        <v>128835499</v>
       </c>
       <c r="B16" t="n">
-        <v>86806</v>
+        <v>86948</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2185,34 +2185,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3712</v>
+        <v>3674</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Follingbo Rosendal, Gtl</t>
+          <t>Follingsbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>700953</v>
+        <v>700938</v>
       </c>
       <c r="R16" t="n">
-        <v>6388454</v>
+        <v>6388610</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2242,9 +2242,19 @@
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2259,57 +2269,57 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128835465</v>
+        <v>128833063</v>
       </c>
       <c r="B17" t="n">
-        <v>86981</v>
+        <v>86810</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Follingsbo Rosendal, Gtl</t>
+          <t>Follingbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>700869</v>
+        <v>700953</v>
       </c>
       <c r="R17" t="n">
-        <v>6388563</v>
+        <v>6388454</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2339,72 +2349,61 @@
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>16:25</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>16:25</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128835499</v>
+        <v>128835454</v>
       </c>
       <c r="B18" t="n">
-        <v>86944</v>
+        <v>91012</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3674</v>
+        <v>5735</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Svartnande fingersvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Phaeoclavulina macrospora</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brinkmann</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2414,10 +2413,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>700938</v>
+        <v>700887</v>
       </c>
       <c r="R18" t="n">
-        <v>6388610</v>
+        <v>6388572</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2449,7 +2448,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2459,7 +2458,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Riklig förekomst, Minst 47 fk i en 13 Linje!! Undr En 7-8 meter hög en</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2468,6 +2472,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2486,32 +2491,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128835454</v>
+        <v>128835465</v>
       </c>
       <c r="B19" t="n">
-        <v>91008</v>
+        <v>86985</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5735</v>
+        <v>6003295</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svartnande fingersvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phaeoclavulina macrospora</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Brinkmann</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2521,10 +2526,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>700887</v>
+        <v>700869</v>
       </c>
       <c r="R19" t="n">
-        <v>6388572</v>
+        <v>6388563</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2556,7 +2561,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2566,12 +2571,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Riklig förekomst, Minst 47 fk i en 13 Linje!! Undr En 7-8 meter hög en</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2599,10 +2599,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128835497</v>
+        <v>128835498</v>
       </c>
       <c r="B20" t="n">
-        <v>86944</v>
+        <v>86948</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2634,10 +2634,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>700948</v>
+        <v>700817</v>
       </c>
       <c r="R20" t="n">
-        <v>6388722</v>
+        <v>6388548</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2706,10 +2706,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128835498</v>
+        <v>128835497</v>
       </c>
       <c r="B21" t="n">
-        <v>86944</v>
+        <v>86948</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>700817</v>
+        <v>700948</v>
       </c>
       <c r="R21" t="n">
-        <v>6388548</v>
+        <v>6388722</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2813,45 +2813,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128833068</v>
+        <v>128835472</v>
       </c>
       <c r="B22" t="n">
-        <v>86944</v>
+        <v>86784</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3674</v>
+        <v>1985</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Follingbo Rosendal, Gtl</t>
+          <t>Follingsbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>700938</v>
+        <v>700957</v>
       </c>
       <c r="R22" t="n">
-        <v>6388454</v>
+        <v>6388630</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2881,9 +2881,19 @@
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2898,12 +2908,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -2913,7 +2923,7 @@
         <v>128835490</v>
       </c>
       <c r="B23" t="n">
-        <v>86828</v>
+        <v>86832</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3017,32 +3027,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128835472</v>
+        <v>128835464</v>
       </c>
       <c r="B24" t="n">
-        <v>86780</v>
+        <v>86961</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1985</v>
+        <v>1988</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3052,10 +3062,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>700957</v>
+        <v>700940</v>
       </c>
       <c r="R24" t="n">
-        <v>6388630</v>
+        <v>6388612</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3087,7 +3097,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3097,7 +3107,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3124,10 +3134,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128835464</v>
+        <v>128833068</v>
       </c>
       <c r="B25" t="n">
-        <v>86957</v>
+        <v>86948</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3135,34 +3145,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1988</v>
+        <v>3674</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Follingsbo Rosendal, Gtl</t>
+          <t>Follingbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>700940</v>
+        <v>700938</v>
       </c>
       <c r="R25" t="n">
-        <v>6388612</v>
+        <v>6388454</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3192,19 +3202,9 @@
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>15:01</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>15:01</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3219,12 +3219,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3234,7 +3234,7 @@
         <v>128835473</v>
       </c>
       <c r="B26" t="n">
-        <v>86780</v>
+        <v>86784</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3338,10 +3338,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128835470</v>
+        <v>128835444</v>
       </c>
       <c r="B27" t="n">
-        <v>86968</v>
+        <v>87030</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3349,21 +3349,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3599</v>
+        <v>3767</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3373,10 +3373,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>700910</v>
+        <v>700957</v>
       </c>
       <c r="R27" t="n">
-        <v>6388586</v>
+        <v>6388621</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3408,7 +3408,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3445,10 +3445,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128835444</v>
+        <v>128835470</v>
       </c>
       <c r="B28" t="n">
-        <v>87026</v>
+        <v>86972</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3456,21 +3456,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3767</v>
+        <v>3599</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3480,10 +3480,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>700957</v>
+        <v>700910</v>
       </c>
       <c r="R28" t="n">
-        <v>6388621</v>
+        <v>6388586</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3515,7 +3515,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3552,32 +3552,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128835442</v>
+        <v>128835448</v>
       </c>
       <c r="B29" t="n">
-        <v>87026</v>
+        <v>86786</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3767</v>
+        <v>3762</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3587,10 +3587,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>700952</v>
+        <v>700817</v>
       </c>
       <c r="R29" t="n">
-        <v>6388607</v>
+        <v>6388555</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3622,7 +3622,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3659,32 +3659,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128835448</v>
+        <v>128835442</v>
       </c>
       <c r="B30" t="n">
-        <v>86782</v>
+        <v>87030</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3762</v>
+        <v>3767</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3694,10 +3694,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>700817</v>
+        <v>700952</v>
       </c>
       <c r="R30" t="n">
-        <v>6388555</v>
+        <v>6388607</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3769,7 +3769,7 @@
         <v>128835471</v>
       </c>
       <c r="B31" t="n">
-        <v>86780</v>
+        <v>86784</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3876,7 +3876,7 @@
         <v>128835455</v>
       </c>
       <c r="B32" t="n">
-        <v>91008</v>
+        <v>91012</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3984,7 +3984,7 @@
         <v>128833061</v>
       </c>
       <c r="B33" t="n">
-        <v>86897</v>
+        <v>86901</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4081,7 +4081,7 @@
         <v>128835461</v>
       </c>
       <c r="B34" t="n">
-        <v>91061</v>
+        <v>91065</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4192,7 +4192,7 @@
         <v>128835476</v>
       </c>
       <c r="B35" t="n">
-        <v>87175</v>
+        <v>87179</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4308,7 +4308,7 @@
         <v>128833054</v>
       </c>
       <c r="B36" t="n">
-        <v>86981</v>
+        <v>86985</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4403,32 +4403,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128833053</v>
+        <v>128833066</v>
       </c>
       <c r="B37" t="n">
-        <v>86981</v>
+        <v>86948</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4438,10 +4438,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>700979</v>
+        <v>701012</v>
       </c>
       <c r="R37" t="n">
-        <v>6388550</v>
+        <v>6388573</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4482,7 +4482,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4501,32 +4500,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128833066</v>
+        <v>128833053</v>
       </c>
       <c r="B38" t="n">
-        <v>86944</v>
+        <v>86985</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4536,10 +4535,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>701012</v>
+        <v>700979</v>
       </c>
       <c r="R38" t="n">
-        <v>6388573</v>
+        <v>6388550</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4580,6 +4579,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4598,48 +4598,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128835474</v>
+        <v>128833052</v>
       </c>
       <c r="B39" t="n">
-        <v>86780</v>
+        <v>86985</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1985</v>
+        <v>6003295</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Follingsbo Rosendal, Gtl</t>
+          <t>Follingbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>700966</v>
+        <v>701151</v>
       </c>
       <c r="R39" t="n">
-        <v>6388635</v>
+        <v>6388524</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4669,19 +4666,9 @@
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>14:32</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>14:32</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4697,57 +4684,60 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128833052</v>
+        <v>128835474</v>
       </c>
       <c r="B40" t="n">
-        <v>86981</v>
+        <v>86784</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6003295</v>
+        <v>1985</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Follingbo Rosendal, Gtl</t>
+          <t>Follingsbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>701151</v>
+        <v>700966</v>
       </c>
       <c r="R40" t="n">
-        <v>6388524</v>
+        <v>6388635</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4777,9 +4767,19 @@
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4795,12 +4795,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -4810,7 +4810,7 @@
         <v>128833057</v>
       </c>
       <c r="B41" t="n">
-        <v>86981</v>
+        <v>86985</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4905,32 +4905,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128833055</v>
+        <v>128833070</v>
       </c>
       <c r="B42" t="n">
-        <v>86981</v>
+        <v>86948</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4940,10 +4940,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>700996</v>
+        <v>701026</v>
       </c>
       <c r="R42" t="n">
-        <v>6388473</v>
+        <v>6388477</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4984,7 +4984,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5003,10 +5002,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128833056</v>
+        <v>128833055</v>
       </c>
       <c r="B43" t="n">
-        <v>86981</v>
+        <v>86985</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5038,10 +5037,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>701017</v>
+        <v>700996</v>
       </c>
       <c r="R43" t="n">
-        <v>6388485</v>
+        <v>6388473</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5101,32 +5100,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128833070</v>
+        <v>128833056</v>
       </c>
       <c r="B44" t="n">
-        <v>86944</v>
+        <v>86985</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5136,10 +5135,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>701026</v>
+        <v>701017</v>
       </c>
       <c r="R44" t="n">
-        <v>6388477</v>
+        <v>6388485</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5180,6 +5179,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5201,7 +5201,7 @@
         <v>128833069</v>
       </c>
       <c r="B45" t="n">
-        <v>86944</v>
+        <v>86948</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5298,7 +5298,7 @@
         <v>128833065</v>
       </c>
       <c r="B46" t="n">
-        <v>86806</v>
+        <v>86810</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>128833064</v>
       </c>
       <c r="B47" t="n">
-        <v>86806</v>
+        <v>86810</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5492,7 +5492,7 @@
         <v>128833071</v>
       </c>
       <c r="B48" t="n">
-        <v>86944</v>
+        <v>86948</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         <v>128833067</v>
       </c>
       <c r="B49" t="n">
-        <v>86944</v>
+        <v>86948</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 6153-2024 artfynd.xlsx
+++ b/artfynd/A 6153-2024 artfynd.xlsx
@@ -782,45 +782,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128835469</v>
+        <v>128833059</v>
       </c>
       <c r="B3" t="n">
-        <v>86972</v>
+        <v>8450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3599</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Follingsbo Rosendal, Gtl</t>
+          <t>Follingbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>700915</v>
+        <v>700942</v>
       </c>
       <c r="R3" t="n">
-        <v>6388581</v>
+        <v>6388538</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -850,24 +850,9 @@
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>15:23</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>15:23</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>1 fk</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,57 +867,57 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128833059</v>
+        <v>128835469</v>
       </c>
       <c r="B4" t="n">
-        <v>8450</v>
+        <v>86972</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>3599</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Follingbo Rosendal, Gtl</t>
+          <t>Follingsbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>700942</v>
+        <v>700915</v>
       </c>
       <c r="R4" t="n">
-        <v>6388538</v>
+        <v>6388581</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -962,9 +947,24 @@
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>1 fk</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,44 +979,44 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128835449</v>
+        <v>128835480</v>
       </c>
       <c r="B5" t="n">
-        <v>86786</v>
+        <v>92290</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3762</v>
+        <v>232138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Gul lammticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Albatrellus citrinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Ryman</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>700916</v>
+        <v>700814</v>
       </c>
       <c r="R5" t="n">
-        <v>6388577</v>
+        <v>6388491</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,32 +1098,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128835480</v>
+        <v>128835449</v>
       </c>
       <c r="B6" t="n">
-        <v>92290</v>
+        <v>86786</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>232138</v>
+        <v>3762</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gul lammticka</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Albatrellus citrinus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Ryman</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>700814</v>
+        <v>700916</v>
       </c>
       <c r="R6" t="n">
-        <v>6388491</v>
+        <v>6388577</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,32 +1205,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128835466</v>
+        <v>128835494</v>
       </c>
       <c r="B7" t="n">
-        <v>86985</v>
+        <v>86948</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>700824</v>
+        <v>700929</v>
       </c>
       <c r="R7" t="n">
-        <v>6388554</v>
+        <v>6388692</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1275,7 +1275,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1294,7 +1294,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1313,32 +1312,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128835494</v>
+        <v>128835466</v>
       </c>
       <c r="B8" t="n">
-        <v>86948</v>
+        <v>86985</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1348,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>700929</v>
+        <v>700824</v>
       </c>
       <c r="R8" t="n">
-        <v>6388692</v>
+        <v>6388554</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1383,7 +1382,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1393,7 +1392,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1402,6 +1401,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1420,32 +1420,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128835492</v>
+        <v>128835475</v>
       </c>
       <c r="B9" t="n">
-        <v>106294</v>
+        <v>86784</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220785</v>
+        <v>1985</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1455,10 +1455,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>700799</v>
+        <v>700804</v>
       </c>
       <c r="R9" t="n">
-        <v>6388520</v>
+        <v>6388482</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1500,12 +1500,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:45</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Mycket hlgvuxen 12+ Meter</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1532,32 +1527,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128835475</v>
+        <v>128835492</v>
       </c>
       <c r="B10" t="n">
-        <v>86784</v>
+        <v>106294</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1985</v>
+        <v>220785</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1567,10 +1562,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>700804</v>
+        <v>700799</v>
       </c>
       <c r="R10" t="n">
-        <v>6388482</v>
+        <v>6388520</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1602,7 +1597,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1612,7 +1607,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Mycket hlgvuxen 12+ Meter</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -4598,45 +4598,48 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128833052</v>
+        <v>128835474</v>
       </c>
       <c r="B39" t="n">
-        <v>86985</v>
+        <v>86784</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6003295</v>
+        <v>1985</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Follingbo Rosendal, Gtl</t>
+          <t>Follingsbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>701151</v>
+        <v>700966</v>
       </c>
       <c r="R39" t="n">
-        <v>6388524</v>
+        <v>6388635</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4666,9 +4669,19 @@
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4684,60 +4697,57 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128835474</v>
+        <v>128833052</v>
       </c>
       <c r="B40" t="n">
-        <v>86784</v>
+        <v>86985</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1985</v>
+        <v>6003295</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Follingsbo Rosendal, Gtl</t>
+          <t>Follingbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>700966</v>
+        <v>701151</v>
       </c>
       <c r="R40" t="n">
-        <v>6388635</v>
+        <v>6388524</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4767,19 +4777,9 @@
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>14:32</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>14:32</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4795,12 +4795,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>

--- a/artfynd/A 6153-2024 artfynd.xlsx
+++ b/artfynd/A 6153-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128835463</v>
       </c>
       <c r="B2" t="n">
-        <v>86961</v>
+        <v>86968</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,45 +782,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128833059</v>
+        <v>128835469</v>
       </c>
       <c r="B3" t="n">
-        <v>8450</v>
+        <v>86979</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>3599</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Follingbo Rosendal, Gtl</t>
+          <t>Follingsbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>700942</v>
+        <v>700915</v>
       </c>
       <c r="R3" t="n">
-        <v>6388538</v>
+        <v>6388581</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -850,9 +850,24 @@
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>1 fk</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,57 +882,57 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128835469</v>
+        <v>128833059</v>
       </c>
       <c r="B4" t="n">
-        <v>86972</v>
+        <v>8450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3599</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Follingsbo Rosendal, Gtl</t>
+          <t>Follingbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>700915</v>
+        <v>700942</v>
       </c>
       <c r="R4" t="n">
-        <v>6388581</v>
+        <v>6388538</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -947,24 +962,9 @@
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>15:23</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>15:23</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>1 fk</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,44 +979,44 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128835480</v>
+        <v>128835449</v>
       </c>
       <c r="B5" t="n">
-        <v>92290</v>
+        <v>86793</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>232138</v>
+        <v>3762</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gul lammticka</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Albatrellus citrinus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Ryman</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>700814</v>
+        <v>700916</v>
       </c>
       <c r="R5" t="n">
-        <v>6388491</v>
+        <v>6388577</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,32 +1098,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128835449</v>
+        <v>128835480</v>
       </c>
       <c r="B6" t="n">
-        <v>86786</v>
+        <v>92297</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3762</v>
+        <v>232138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Gul lammticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Albatrellus citrinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Ryman</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>700916</v>
+        <v>700814</v>
       </c>
       <c r="R6" t="n">
-        <v>6388577</v>
+        <v>6388491</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1208,7 +1208,7 @@
         <v>128835494</v>
       </c>
       <c r="B7" t="n">
-        <v>86948</v>
+        <v>86955</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>128835466</v>
       </c>
       <c r="B8" t="n">
-        <v>86985</v>
+        <v>86992</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         <v>128835475</v>
       </c>
       <c r="B9" t="n">
-        <v>86784</v>
+        <v>86791</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>128835492</v>
       </c>
       <c r="B10" t="n">
-        <v>106294</v>
+        <v>106301</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>128835493</v>
       </c>
       <c r="B11" t="n">
-        <v>86948</v>
+        <v>86955</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         <v>128835443</v>
       </c>
       <c r="B12" t="n">
-        <v>87030</v>
+        <v>87037</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>128835441</v>
       </c>
       <c r="B13" t="n">
-        <v>87030</v>
+        <v>87037</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>128835450</v>
       </c>
       <c r="B14" t="n">
-        <v>86786</v>
+        <v>86793</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>128835462</v>
       </c>
       <c r="B15" t="n">
-        <v>86961</v>
+        <v>86968</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>128835499</v>
       </c>
       <c r="B16" t="n">
-        <v>86948</v>
+        <v>86955</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         <v>128833063</v>
       </c>
       <c r="B17" t="n">
-        <v>86810</v>
+        <v>86817</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         <v>128835454</v>
       </c>
       <c r="B18" t="n">
-        <v>91012</v>
+        <v>91019</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
         <v>128835465</v>
       </c>
       <c r="B19" t="n">
-        <v>86985</v>
+        <v>86992</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2602,7 +2602,7 @@
         <v>128835498</v>
       </c>
       <c r="B20" t="n">
-        <v>86948</v>
+        <v>86955</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>128835497</v>
       </c>
       <c r="B21" t="n">
-        <v>86948</v>
+        <v>86955</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>128835472</v>
       </c>
       <c r="B22" t="n">
-        <v>86784</v>
+        <v>86791</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2920,32 +2920,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128835490</v>
+        <v>128835464</v>
       </c>
       <c r="B23" t="n">
-        <v>86832</v>
+        <v>86968</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>424</v>
+        <v>1988</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2955,10 +2955,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>700954</v>
+        <v>700940</v>
       </c>
       <c r="R23" t="n">
-        <v>6388606</v>
+        <v>6388612</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2990,7 +2990,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3027,32 +3027,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128835464</v>
+        <v>128835490</v>
       </c>
       <c r="B24" t="n">
-        <v>86961</v>
+        <v>86839</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1988</v>
+        <v>424</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3062,10 +3062,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>700940</v>
+        <v>700954</v>
       </c>
       <c r="R24" t="n">
-        <v>6388612</v>
+        <v>6388606</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3097,7 +3097,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3107,7 +3107,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3137,7 +3137,7 @@
         <v>128833068</v>
       </c>
       <c r="B25" t="n">
-        <v>86948</v>
+        <v>86955</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3234,7 +3234,7 @@
         <v>128835473</v>
       </c>
       <c r="B26" t="n">
-        <v>86784</v>
+        <v>86791</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
         <v>128835444</v>
       </c>
       <c r="B27" t="n">
-        <v>87030</v>
+        <v>87037</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3448,7 +3448,7 @@
         <v>128835470</v>
       </c>
       <c r="B28" t="n">
-        <v>86972</v>
+        <v>86979</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3555,7 +3555,7 @@
         <v>128835448</v>
       </c>
       <c r="B29" t="n">
-        <v>86786</v>
+        <v>86793</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3662,7 +3662,7 @@
         <v>128835442</v>
       </c>
       <c r="B30" t="n">
-        <v>87030</v>
+        <v>87037</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3769,7 +3769,7 @@
         <v>128835471</v>
       </c>
       <c r="B31" t="n">
-        <v>86784</v>
+        <v>86791</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3876,7 +3876,7 @@
         <v>128835455</v>
       </c>
       <c r="B32" t="n">
-        <v>91012</v>
+        <v>91019</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3984,7 +3984,7 @@
         <v>128833061</v>
       </c>
       <c r="B33" t="n">
-        <v>86901</v>
+        <v>86908</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4081,7 +4081,7 @@
         <v>128835461</v>
       </c>
       <c r="B34" t="n">
-        <v>91065</v>
+        <v>91072</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4192,7 +4192,7 @@
         <v>128835476</v>
       </c>
       <c r="B35" t="n">
-        <v>87179</v>
+        <v>87186</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4308,7 +4308,7 @@
         <v>128833054</v>
       </c>
       <c r="B36" t="n">
-        <v>86985</v>
+        <v>86992</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4406,7 +4406,7 @@
         <v>128833066</v>
       </c>
       <c r="B37" t="n">
-        <v>86948</v>
+        <v>86955</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         <v>128833053</v>
       </c>
       <c r="B38" t="n">
-        <v>86985</v>
+        <v>86992</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         <v>128835474</v>
       </c>
       <c r="B39" t="n">
-        <v>86784</v>
+        <v>86791</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4712,7 +4712,7 @@
         <v>128833052</v>
       </c>
       <c r="B40" t="n">
-        <v>86985</v>
+        <v>86992</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
         <v>128833057</v>
       </c>
       <c r="B41" t="n">
-        <v>86985</v>
+        <v>86992</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4908,7 +4908,7 @@
         <v>128833070</v>
       </c>
       <c r="B42" t="n">
-        <v>86948</v>
+        <v>86955</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5005,7 +5005,7 @@
         <v>128833055</v>
       </c>
       <c r="B43" t="n">
-        <v>86985</v>
+        <v>86992</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         <v>128833056</v>
       </c>
       <c r="B44" t="n">
-        <v>86985</v>
+        <v>86992</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5201,7 +5201,7 @@
         <v>128833069</v>
       </c>
       <c r="B45" t="n">
-        <v>86948</v>
+        <v>86955</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5298,7 +5298,7 @@
         <v>128833065</v>
       </c>
       <c r="B46" t="n">
-        <v>86810</v>
+        <v>86817</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>128833064</v>
       </c>
       <c r="B47" t="n">
-        <v>86810</v>
+        <v>86817</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5492,7 +5492,7 @@
         <v>128833071</v>
       </c>
       <c r="B48" t="n">
-        <v>86948</v>
+        <v>86955</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         <v>128833067</v>
       </c>
       <c r="B49" t="n">
-        <v>86948</v>
+        <v>86955</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 6153-2024 artfynd.xlsx
+++ b/artfynd/A 6153-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128835463</v>
       </c>
       <c r="B2" t="n">
-        <v>86968</v>
+        <v>86970</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128835469</v>
       </c>
       <c r="B3" t="n">
-        <v>86979</v>
+        <v>86981</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>128835449</v>
       </c>
       <c r="B5" t="n">
-        <v>86793</v>
+        <v>86795</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>128835480</v>
       </c>
       <c r="B6" t="n">
-        <v>92297</v>
+        <v>92299</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>128835494</v>
       </c>
       <c r="B7" t="n">
-        <v>86955</v>
+        <v>86957</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>128835466</v>
       </c>
       <c r="B8" t="n">
-        <v>86992</v>
+        <v>86994</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         <v>128835475</v>
       </c>
       <c r="B9" t="n">
-        <v>86791</v>
+        <v>86793</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>128835492</v>
       </c>
       <c r="B10" t="n">
-        <v>106301</v>
+        <v>106303</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>128835493</v>
       </c>
       <c r="B11" t="n">
-        <v>86955</v>
+        <v>86957</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         <v>128835443</v>
       </c>
       <c r="B12" t="n">
-        <v>87037</v>
+        <v>87039</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>128835441</v>
       </c>
       <c r="B13" t="n">
-        <v>87037</v>
+        <v>87039</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>128835450</v>
       </c>
       <c r="B14" t="n">
-        <v>86793</v>
+        <v>86795</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>128835462</v>
       </c>
       <c r="B15" t="n">
-        <v>86968</v>
+        <v>86970</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>128835499</v>
       </c>
       <c r="B16" t="n">
-        <v>86955</v>
+        <v>86957</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         <v>128833063</v>
       </c>
       <c r="B17" t="n">
-        <v>86817</v>
+        <v>86819</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         <v>128835454</v>
       </c>
       <c r="B18" t="n">
-        <v>91019</v>
+        <v>91021</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
         <v>128835465</v>
       </c>
       <c r="B19" t="n">
-        <v>86992</v>
+        <v>86994</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2602,7 +2602,7 @@
         <v>128835498</v>
       </c>
       <c r="B20" t="n">
-        <v>86955</v>
+        <v>86957</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>128835497</v>
       </c>
       <c r="B21" t="n">
-        <v>86955</v>
+        <v>86957</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2813,10 +2813,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128835472</v>
+        <v>128835490</v>
       </c>
       <c r="B22" t="n">
-        <v>86791</v>
+        <v>86841</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2824,16 +2824,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1985</v>
+        <v>424</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2848,10 +2848,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>700957</v>
+        <v>700954</v>
       </c>
       <c r="R22" t="n">
-        <v>6388630</v>
+        <v>6388606</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2883,7 +2883,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2920,32 +2920,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128835464</v>
+        <v>128835472</v>
       </c>
       <c r="B23" t="n">
-        <v>86968</v>
+        <v>86793</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1988</v>
+        <v>1985</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2955,10 +2955,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>700940</v>
+        <v>700957</v>
       </c>
       <c r="R23" t="n">
-        <v>6388612</v>
+        <v>6388630</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2990,7 +2990,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3027,32 +3027,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128835490</v>
+        <v>128835464</v>
       </c>
       <c r="B24" t="n">
-        <v>86839</v>
+        <v>86970</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>424</v>
+        <v>1988</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3062,10 +3062,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>700954</v>
+        <v>700940</v>
       </c>
       <c r="R24" t="n">
-        <v>6388606</v>
+        <v>6388612</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3097,7 +3097,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3107,7 +3107,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3137,7 +3137,7 @@
         <v>128833068</v>
       </c>
       <c r="B25" t="n">
-        <v>86955</v>
+        <v>86957</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3231,10 +3231,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128835473</v>
+        <v>128835470</v>
       </c>
       <c r="B26" t="n">
-        <v>86791</v>
+        <v>86981</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3242,21 +3242,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1985</v>
+        <v>3599</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3266,10 +3266,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>700804</v>
+        <v>700910</v>
       </c>
       <c r="R26" t="n">
-        <v>6388505</v>
+        <v>6388586</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3301,7 +3301,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3311,7 +3311,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3338,10 +3338,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128835444</v>
+        <v>128835473</v>
       </c>
       <c r="B27" t="n">
-        <v>87037</v>
+        <v>86793</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3349,21 +3349,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3767</v>
+        <v>1985</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3373,10 +3373,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>700957</v>
+        <v>700804</v>
       </c>
       <c r="R27" t="n">
-        <v>6388621</v>
+        <v>6388505</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3408,7 +3408,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3445,10 +3445,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128835470</v>
+        <v>128835444</v>
       </c>
       <c r="B28" t="n">
-        <v>86979</v>
+        <v>87039</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3456,21 +3456,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3599</v>
+        <v>3767</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3480,10 +3480,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>700910</v>
+        <v>700957</v>
       </c>
       <c r="R28" t="n">
-        <v>6388586</v>
+        <v>6388621</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3515,7 +3515,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3555,7 +3555,7 @@
         <v>128835448</v>
       </c>
       <c r="B29" t="n">
-        <v>86793</v>
+        <v>86795</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3662,7 +3662,7 @@
         <v>128835442</v>
       </c>
       <c r="B30" t="n">
-        <v>87037</v>
+        <v>87039</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3766,10 +3766,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128835471</v>
+        <v>128833061</v>
       </c>
       <c r="B31" t="n">
-        <v>86791</v>
+        <v>86910</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3777,34 +3777,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1985</v>
+        <v>248956</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Follingsbo Rosendal, Gtl</t>
+          <t>Follingbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>700792</v>
+        <v>700935</v>
       </c>
       <c r="R31" t="n">
-        <v>6388508</v>
+        <v>6388458</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3834,19 +3834,9 @@
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>17:02</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>17:02</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3861,44 +3851,44 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128835455</v>
+        <v>128835471</v>
       </c>
       <c r="B32" t="n">
-        <v>91019</v>
+        <v>86793</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5735</v>
+        <v>1985</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Svartnande fingersvamp</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phaeoclavulina macrospora</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Brinkmann</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3908,10 +3898,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>700897</v>
+        <v>700792</v>
       </c>
       <c r="R32" t="n">
-        <v>6388579</v>
+        <v>6388508</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3943,7 +3933,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3953,7 +3943,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3962,7 +3952,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3981,45 +3970,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128833061</v>
+        <v>128835455</v>
       </c>
       <c r="B33" t="n">
-        <v>86908</v>
+        <v>91021</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>248956</v>
+        <v>5735</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Svartnande fingersvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Phaeoclavulina macrospora</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Brinkmann</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Follingbo Rosendal, Gtl</t>
+          <t>Follingsbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>700935</v>
+        <v>700897</v>
       </c>
       <c r="R33" t="n">
-        <v>6388458</v>
+        <v>6388579</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4049,29 +4038,40 @@
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4081,7 +4081,7 @@
         <v>128835461</v>
       </c>
       <c r="B34" t="n">
-        <v>91072</v>
+        <v>91074</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4192,7 +4192,7 @@
         <v>128835476</v>
       </c>
       <c r="B35" t="n">
-        <v>87186</v>
+        <v>87188</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4308,7 +4308,7 @@
         <v>128833054</v>
       </c>
       <c r="B36" t="n">
-        <v>86992</v>
+        <v>86994</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4406,7 +4406,7 @@
         <v>128833066</v>
       </c>
       <c r="B37" t="n">
-        <v>86955</v>
+        <v>86957</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         <v>128833053</v>
       </c>
       <c r="B38" t="n">
-        <v>86992</v>
+        <v>86994</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         <v>128835474</v>
       </c>
       <c r="B39" t="n">
-        <v>86791</v>
+        <v>86793</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4712,7 +4712,7 @@
         <v>128833052</v>
       </c>
       <c r="B40" t="n">
-        <v>86992</v>
+        <v>86994</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
         <v>128833057</v>
       </c>
       <c r="B41" t="n">
-        <v>86992</v>
+        <v>86994</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4905,32 +4905,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128833070</v>
+        <v>128833055</v>
       </c>
       <c r="B42" t="n">
-        <v>86955</v>
+        <v>86994</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4940,10 +4940,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>701026</v>
+        <v>700996</v>
       </c>
       <c r="R42" t="n">
-        <v>6388477</v>
+        <v>6388473</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4984,6 +4984,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5002,10 +5003,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128833055</v>
+        <v>128833056</v>
       </c>
       <c r="B43" t="n">
-        <v>86992</v>
+        <v>86994</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5037,10 +5038,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>700996</v>
+        <v>701017</v>
       </c>
       <c r="R43" t="n">
-        <v>6388473</v>
+        <v>6388485</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5100,32 +5101,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128833056</v>
+        <v>128833070</v>
       </c>
       <c r="B44" t="n">
-        <v>86992</v>
+        <v>86957</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5135,10 +5136,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>701017</v>
+        <v>701026</v>
       </c>
       <c r="R44" t="n">
-        <v>6388485</v>
+        <v>6388477</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5179,7 +5180,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5201,7 +5201,7 @@
         <v>128833069</v>
       </c>
       <c r="B45" t="n">
-        <v>86955</v>
+        <v>86957</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5298,7 +5298,7 @@
         <v>128833065</v>
       </c>
       <c r="B46" t="n">
-        <v>86817</v>
+        <v>86819</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>128833064</v>
       </c>
       <c r="B47" t="n">
-        <v>86817</v>
+        <v>86819</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5492,7 +5492,7 @@
         <v>128833071</v>
       </c>
       <c r="B48" t="n">
-        <v>86955</v>
+        <v>86957</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         <v>128833067</v>
       </c>
       <c r="B49" t="n">
-        <v>86955</v>
+        <v>86957</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 6153-2024 artfynd.xlsx
+++ b/artfynd/A 6153-2024 artfynd.xlsx
@@ -991,32 +991,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128835449</v>
+        <v>128835480</v>
       </c>
       <c r="B5" t="n">
-        <v>86795</v>
+        <v>92299</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3762</v>
+        <v>232138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Gul lammticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Albatrellus citrinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Ryman</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>700916</v>
+        <v>700814</v>
       </c>
       <c r="R5" t="n">
-        <v>6388577</v>
+        <v>6388491</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,32 +1098,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128835480</v>
+        <v>128835449</v>
       </c>
       <c r="B6" t="n">
-        <v>92299</v>
+        <v>86795</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>232138</v>
+        <v>3762</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gul lammticka</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Albatrellus citrinus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Ryman</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>700814</v>
+        <v>700916</v>
       </c>
       <c r="R6" t="n">
-        <v>6388491</v>
+        <v>6388577</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1420,32 +1420,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128835475</v>
+        <v>128835492</v>
       </c>
       <c r="B9" t="n">
-        <v>86793</v>
+        <v>106303</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1985</v>
+        <v>220785</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1455,10 +1455,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>700804</v>
+        <v>700799</v>
       </c>
       <c r="R9" t="n">
-        <v>6388482</v>
+        <v>6388520</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1500,7 +1500,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Mycket hlgvuxen 12+ Meter</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1527,32 +1532,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128835492</v>
+        <v>128835475</v>
       </c>
       <c r="B10" t="n">
-        <v>106303</v>
+        <v>86793</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220785</v>
+        <v>1985</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1562,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>700799</v>
+        <v>700804</v>
       </c>
       <c r="R10" t="n">
-        <v>6388520</v>
+        <v>6388482</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1597,7 +1602,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1607,12 +1612,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:45</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Mycket hlgvuxen 12+ Meter</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1639,32 +1639,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128835493</v>
+        <v>128835443</v>
       </c>
       <c r="B11" t="n">
-        <v>86957</v>
+        <v>87039</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>700828</v>
+        <v>700956</v>
       </c>
       <c r="R11" t="n">
-        <v>6388554</v>
+        <v>6388619</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1719,7 +1719,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1746,32 +1746,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128835443</v>
+        <v>128835493</v>
       </c>
       <c r="B12" t="n">
-        <v>87039</v>
+        <v>86957</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3767</v>
+        <v>3674</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1781,10 +1781,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>700956</v>
+        <v>700828</v>
       </c>
       <c r="R12" t="n">
-        <v>6388619</v>
+        <v>6388554</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2174,10 +2174,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128835499</v>
+        <v>128833063</v>
       </c>
       <c r="B16" t="n">
-        <v>86957</v>
+        <v>86819</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2185,34 +2185,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3674</v>
+        <v>3712</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Follingsbo Rosendal, Gtl</t>
+          <t>Follingbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>700938</v>
+        <v>700953</v>
       </c>
       <c r="R16" t="n">
-        <v>6388610</v>
+        <v>6388454</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2242,19 +2242,9 @@
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>15:01</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>15:01</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2269,22 +2259,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128833063</v>
+        <v>128835499</v>
       </c>
       <c r="B17" t="n">
-        <v>86819</v>
+        <v>86957</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2292,34 +2282,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3712</v>
+        <v>3674</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Follingbo Rosendal, Gtl</t>
+          <t>Follingsbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>700953</v>
+        <v>700938</v>
       </c>
       <c r="R17" t="n">
-        <v>6388454</v>
+        <v>6388610</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2349,9 +2339,19 @@
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2366,12 +2366,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2599,7 +2599,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128835498</v>
+        <v>128835497</v>
       </c>
       <c r="B20" t="n">
         <v>86957</v>
@@ -2634,10 +2634,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>700817</v>
+        <v>700948</v>
       </c>
       <c r="R20" t="n">
-        <v>6388548</v>
+        <v>6388722</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2706,7 +2706,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128835497</v>
+        <v>128835498</v>
       </c>
       <c r="B21" t="n">
         <v>86957</v>
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>700948</v>
+        <v>700817</v>
       </c>
       <c r="R21" t="n">
-        <v>6388722</v>
+        <v>6388548</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2813,45 +2813,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128835490</v>
+        <v>128833068</v>
       </c>
       <c r="B22" t="n">
-        <v>86841</v>
+        <v>86957</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>424</v>
+        <v>3674</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Follingsbo Rosendal, Gtl</t>
+          <t>Follingbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>700954</v>
+        <v>700938</v>
       </c>
       <c r="R22" t="n">
-        <v>6388606</v>
+        <v>6388454</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2881,19 +2881,9 @@
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>14:56</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>14:56</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2908,22 +2898,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128835472</v>
+        <v>128835490</v>
       </c>
       <c r="B23" t="n">
-        <v>86793</v>
+        <v>86841</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2931,16 +2921,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1985</v>
+        <v>424</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2955,10 +2945,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>700957</v>
+        <v>700954</v>
       </c>
       <c r="R23" t="n">
-        <v>6388630</v>
+        <v>6388606</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2990,7 +2980,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3000,7 +2990,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3027,32 +3017,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128835464</v>
+        <v>128835472</v>
       </c>
       <c r="B24" t="n">
-        <v>86970</v>
+        <v>86793</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1988</v>
+        <v>1985</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3062,10 +3052,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>700940</v>
+        <v>700957</v>
       </c>
       <c r="R24" t="n">
-        <v>6388612</v>
+        <v>6388630</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3097,7 +3087,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3107,7 +3097,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3134,10 +3124,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128833068</v>
+        <v>128835464</v>
       </c>
       <c r="B25" t="n">
-        <v>86957</v>
+        <v>86970</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3145,34 +3135,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3674</v>
+        <v>1988</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Follingbo Rosendal, Gtl</t>
+          <t>Follingsbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>700938</v>
+        <v>700940</v>
       </c>
       <c r="R25" t="n">
-        <v>6388454</v>
+        <v>6388612</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3202,9 +3192,19 @@
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3219,22 +3219,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128835470</v>
+        <v>128835444</v>
       </c>
       <c r="B26" t="n">
-        <v>86981</v>
+        <v>87039</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3242,21 +3242,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3599</v>
+        <v>3767</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3266,10 +3266,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>700910</v>
+        <v>700957</v>
       </c>
       <c r="R26" t="n">
-        <v>6388586</v>
+        <v>6388621</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3301,7 +3301,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3311,7 +3311,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3338,10 +3338,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128835473</v>
+        <v>128835470</v>
       </c>
       <c r="B27" t="n">
-        <v>86793</v>
+        <v>86981</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3349,21 +3349,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1985</v>
+        <v>3599</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3373,10 +3373,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>700804</v>
+        <v>700910</v>
       </c>
       <c r="R27" t="n">
-        <v>6388505</v>
+        <v>6388586</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3408,7 +3408,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3445,10 +3445,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128835444</v>
+        <v>128835473</v>
       </c>
       <c r="B28" t="n">
-        <v>87039</v>
+        <v>86793</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3456,21 +3456,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3767</v>
+        <v>1985</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3480,10 +3480,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>700957</v>
+        <v>700804</v>
       </c>
       <c r="R28" t="n">
-        <v>6388621</v>
+        <v>6388505</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3515,7 +3515,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3552,32 +3552,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128835448</v>
+        <v>128835442</v>
       </c>
       <c r="B29" t="n">
-        <v>86795</v>
+        <v>87039</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3762</v>
+        <v>3767</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3587,10 +3587,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>700817</v>
+        <v>700952</v>
       </c>
       <c r="R29" t="n">
-        <v>6388555</v>
+        <v>6388607</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3622,7 +3622,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3659,32 +3659,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128835442</v>
+        <v>128835448</v>
       </c>
       <c r="B30" t="n">
-        <v>87039</v>
+        <v>86795</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3767</v>
+        <v>3762</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3694,10 +3694,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>700952</v>
+        <v>700817</v>
       </c>
       <c r="R30" t="n">
-        <v>6388607</v>
+        <v>6388555</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4598,48 +4598,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128835474</v>
+        <v>128833052</v>
       </c>
       <c r="B39" t="n">
-        <v>86793</v>
+        <v>86994</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1985</v>
+        <v>6003295</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Follingsbo Rosendal, Gtl</t>
+          <t>Follingbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>700966</v>
+        <v>701151</v>
       </c>
       <c r="R39" t="n">
-        <v>6388635</v>
+        <v>6388524</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4669,19 +4666,9 @@
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>14:32</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>14:32</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4697,57 +4684,60 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128833052</v>
+        <v>128835474</v>
       </c>
       <c r="B40" t="n">
-        <v>86994</v>
+        <v>86793</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6003295</v>
+        <v>1985</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Follingbo Rosendal, Gtl</t>
+          <t>Follingsbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>701151</v>
+        <v>700966</v>
       </c>
       <c r="R40" t="n">
-        <v>6388524</v>
+        <v>6388635</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4777,9 +4767,19 @@
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4795,12 +4795,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -4905,32 +4905,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128833055</v>
+        <v>128833070</v>
       </c>
       <c r="B42" t="n">
-        <v>86994</v>
+        <v>86957</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4940,10 +4940,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>700996</v>
+        <v>701026</v>
       </c>
       <c r="R42" t="n">
-        <v>6388473</v>
+        <v>6388477</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4984,7 +4984,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5003,7 +5002,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128833056</v>
+        <v>128833055</v>
       </c>
       <c r="B43" t="n">
         <v>86994</v>
@@ -5038,10 +5037,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>701017</v>
+        <v>700996</v>
       </c>
       <c r="R43" t="n">
-        <v>6388485</v>
+        <v>6388473</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5101,32 +5100,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128833070</v>
+        <v>128833056</v>
       </c>
       <c r="B44" t="n">
-        <v>86957</v>
+        <v>86994</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5136,10 +5135,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>701026</v>
+        <v>701017</v>
       </c>
       <c r="R44" t="n">
-        <v>6388477</v>
+        <v>6388485</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5180,6 +5179,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 6153-2024 artfynd.xlsx
+++ b/artfynd/A 6153-2024 artfynd.xlsx
@@ -991,32 +991,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128835480</v>
+        <v>128835449</v>
       </c>
       <c r="B5" t="n">
-        <v>92299</v>
+        <v>86795</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>232138</v>
+        <v>3762</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gul lammticka</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Albatrellus citrinus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Ryman</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>700814</v>
+        <v>700916</v>
       </c>
       <c r="R5" t="n">
-        <v>6388491</v>
+        <v>6388577</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,32 +1098,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128835449</v>
+        <v>128835480</v>
       </c>
       <c r="B6" t="n">
-        <v>86795</v>
+        <v>92299</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3762</v>
+        <v>232138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Gul lammticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Albatrellus citrinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Ryman</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>700916</v>
+        <v>700814</v>
       </c>
       <c r="R6" t="n">
-        <v>6388577</v>
+        <v>6388491</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -2174,45 +2174,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128833063</v>
+        <v>128835465</v>
       </c>
       <c r="B16" t="n">
-        <v>86819</v>
+        <v>86994</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Follingbo Rosendal, Gtl</t>
+          <t>Follingsbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>700953</v>
+        <v>700869</v>
       </c>
       <c r="R16" t="n">
-        <v>6388454</v>
+        <v>6388563</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2242,39 +2242,50 @@
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128835499</v>
+        <v>128833063</v>
       </c>
       <c r="B17" t="n">
-        <v>86957</v>
+        <v>86819</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2282,34 +2293,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3674</v>
+        <v>3712</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Follingsbo Rosendal, Gtl</t>
+          <t>Follingbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>700938</v>
+        <v>700953</v>
       </c>
       <c r="R17" t="n">
-        <v>6388610</v>
+        <v>6388454</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2339,19 +2350,9 @@
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>15:01</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>15:01</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2366,44 +2367,44 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128835454</v>
+        <v>128835499</v>
       </c>
       <c r="B18" t="n">
-        <v>91021</v>
+        <v>86957</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5735</v>
+        <v>3674</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svartnande fingersvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phaeoclavulina macrospora</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Brinkmann</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2413,10 +2414,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>700887</v>
+        <v>700938</v>
       </c>
       <c r="R18" t="n">
-        <v>6388572</v>
+        <v>6388610</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2448,7 +2449,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2458,12 +2459,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Riklig förekomst, Minst 47 fk i en 13 Linje!! Undr En 7-8 meter hög en</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2472,7 +2468,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2491,32 +2486,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128835465</v>
+        <v>128835454</v>
       </c>
       <c r="B19" t="n">
-        <v>86994</v>
+        <v>91021</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6003295</v>
+        <v>5735</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartnande fingersvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Phaeoclavulina macrospora</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brinkmann</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2526,10 +2521,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>700869</v>
+        <v>700887</v>
       </c>
       <c r="R19" t="n">
-        <v>6388563</v>
+        <v>6388572</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2561,7 +2556,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2571,7 +2566,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Riklig förekomst, Minst 47 fk i en 13 Linje!! Undr En 7-8 meter hög en</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2813,45 +2813,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128833068</v>
+        <v>128835490</v>
       </c>
       <c r="B22" t="n">
-        <v>86957</v>
+        <v>86841</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3674</v>
+        <v>424</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Follingbo Rosendal, Gtl</t>
+          <t>Follingsbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>700938</v>
+        <v>700954</v>
       </c>
       <c r="R22" t="n">
-        <v>6388454</v>
+        <v>6388606</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2881,9 +2881,19 @@
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2898,22 +2908,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128835490</v>
+        <v>128835472</v>
       </c>
       <c r="B23" t="n">
-        <v>86841</v>
+        <v>86793</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2921,16 +2931,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>424</v>
+        <v>1985</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2945,10 +2955,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>700954</v>
+        <v>700957</v>
       </c>
       <c r="R23" t="n">
-        <v>6388606</v>
+        <v>6388630</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2980,7 +2990,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2990,7 +3000,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3017,32 +3027,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128835472</v>
+        <v>128835464</v>
       </c>
       <c r="B24" t="n">
-        <v>86793</v>
+        <v>86970</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1985</v>
+        <v>1988</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3052,10 +3062,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>700957</v>
+        <v>700940</v>
       </c>
       <c r="R24" t="n">
-        <v>6388630</v>
+        <v>6388612</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3087,7 +3097,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3097,7 +3107,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3124,10 +3134,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128835464</v>
+        <v>128833068</v>
       </c>
       <c r="B25" t="n">
-        <v>86970</v>
+        <v>86957</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3135,34 +3145,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1988</v>
+        <v>3674</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Follingsbo Rosendal, Gtl</t>
+          <t>Follingbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>700940</v>
+        <v>700938</v>
       </c>
       <c r="R25" t="n">
-        <v>6388612</v>
+        <v>6388454</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3192,19 +3202,9 @@
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>15:01</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>15:01</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3219,12 +3219,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -4905,32 +4905,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128833070</v>
+        <v>128833055</v>
       </c>
       <c r="B42" t="n">
-        <v>86957</v>
+        <v>86994</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4940,10 +4940,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>701026</v>
+        <v>700996</v>
       </c>
       <c r="R42" t="n">
-        <v>6388477</v>
+        <v>6388473</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4984,6 +4984,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5002,7 +5003,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128833055</v>
+        <v>128833056</v>
       </c>
       <c r="B43" t="n">
         <v>86994</v>
@@ -5037,10 +5038,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>700996</v>
+        <v>701017</v>
       </c>
       <c r="R43" t="n">
-        <v>6388473</v>
+        <v>6388485</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5100,32 +5101,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128833056</v>
+        <v>128833070</v>
       </c>
       <c r="B44" t="n">
-        <v>86994</v>
+        <v>86957</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5135,10 +5136,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>701017</v>
+        <v>701026</v>
       </c>
       <c r="R44" t="n">
-        <v>6388485</v>
+        <v>6388477</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5179,7 +5180,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 6153-2024 artfynd.xlsx
+++ b/artfynd/A 6153-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128835463</v>
       </c>
       <c r="B2" t="n">
-        <v>86970</v>
+        <v>86971</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128835469</v>
       </c>
       <c r="B3" t="n">
-        <v>86981</v>
+        <v>86982</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>128835449</v>
       </c>
       <c r="B5" t="n">
-        <v>86795</v>
+        <v>86796</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>128835480</v>
       </c>
       <c r="B6" t="n">
-        <v>92299</v>
+        <v>92313</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1205,32 +1205,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128835494</v>
+        <v>128835466</v>
       </c>
       <c r="B7" t="n">
-        <v>86957</v>
+        <v>86995</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>700929</v>
+        <v>700824</v>
       </c>
       <c r="R7" t="n">
-        <v>6388692</v>
+        <v>6388554</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1275,7 +1275,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1294,6 +1294,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1312,32 +1313,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128835466</v>
+        <v>128835494</v>
       </c>
       <c r="B8" t="n">
-        <v>86994</v>
+        <v>86958</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1347,10 +1348,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>700824</v>
+        <v>700929</v>
       </c>
       <c r="R8" t="n">
-        <v>6388554</v>
+        <v>6388692</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1382,7 +1383,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1392,7 +1393,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1401,7 +1402,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1420,32 +1420,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128835492</v>
+        <v>128835475</v>
       </c>
       <c r="B9" t="n">
-        <v>106303</v>
+        <v>86794</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220785</v>
+        <v>1985</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1455,10 +1455,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>700799</v>
+        <v>700804</v>
       </c>
       <c r="R9" t="n">
-        <v>6388520</v>
+        <v>6388482</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1500,12 +1500,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:45</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Mycket hlgvuxen 12+ Meter</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1532,32 +1527,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128835475</v>
+        <v>128835492</v>
       </c>
       <c r="B10" t="n">
-        <v>86793</v>
+        <v>106329</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1985</v>
+        <v>220785</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1567,10 +1562,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>700804</v>
+        <v>700799</v>
       </c>
       <c r="R10" t="n">
-        <v>6388482</v>
+        <v>6388520</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1602,7 +1597,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1612,7 +1607,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Mycket hlgvuxen 12+ Meter</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1639,32 +1639,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128835443</v>
+        <v>128835493</v>
       </c>
       <c r="B11" t="n">
-        <v>87039</v>
+        <v>86958</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3767</v>
+        <v>3674</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>700956</v>
+        <v>700828</v>
       </c>
       <c r="R11" t="n">
-        <v>6388619</v>
+        <v>6388554</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1719,7 +1719,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1746,32 +1746,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128835493</v>
+        <v>128835443</v>
       </c>
       <c r="B12" t="n">
-        <v>86957</v>
+        <v>87040</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1781,10 +1781,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>700828</v>
+        <v>700956</v>
       </c>
       <c r="R12" t="n">
-        <v>6388554</v>
+        <v>6388619</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1856,7 +1856,7 @@
         <v>128835441</v>
       </c>
       <c r="B13" t="n">
-        <v>87039</v>
+        <v>87040</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>128835450</v>
       </c>
       <c r="B14" t="n">
-        <v>86795</v>
+        <v>86796</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>128835462</v>
       </c>
       <c r="B15" t="n">
-        <v>86970</v>
+        <v>86971</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2174,32 +2174,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128835465</v>
+        <v>128835499</v>
       </c>
       <c r="B16" t="n">
-        <v>86994</v>
+        <v>86958</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2209,10 +2209,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>700869</v>
+        <v>700938</v>
       </c>
       <c r="R16" t="n">
-        <v>6388563</v>
+        <v>6388610</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2244,7 +2244,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2263,7 +2263,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2285,7 +2284,7 @@
         <v>128833063</v>
       </c>
       <c r="B17" t="n">
-        <v>86819</v>
+        <v>86820</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2379,32 +2378,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128835499</v>
+        <v>128835454</v>
       </c>
       <c r="B18" t="n">
-        <v>86957</v>
+        <v>91022</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3674</v>
+        <v>5735</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Svartnande fingersvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Phaeoclavulina macrospora</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brinkmann</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2414,10 +2413,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>700938</v>
+        <v>700887</v>
       </c>
       <c r="R18" t="n">
-        <v>6388610</v>
+        <v>6388572</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2449,7 +2448,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2459,7 +2458,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Riklig förekomst, Minst 47 fk i en 13 Linje!! Undr En 7-8 meter hög en</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2468,6 +2472,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2486,32 +2491,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128835454</v>
+        <v>128835465</v>
       </c>
       <c r="B19" t="n">
-        <v>91021</v>
+        <v>86995</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5735</v>
+        <v>6003295</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svartnande fingersvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phaeoclavulina macrospora</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Brinkmann</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2521,10 +2526,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>700887</v>
+        <v>700869</v>
       </c>
       <c r="R19" t="n">
-        <v>6388572</v>
+        <v>6388563</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2556,7 +2561,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2566,12 +2571,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Riklig förekomst, Minst 47 fk i en 13 Linje!! Undr En 7-8 meter hög en</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2599,10 +2599,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128835497</v>
+        <v>128835498</v>
       </c>
       <c r="B20" t="n">
-        <v>86957</v>
+        <v>86958</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2634,10 +2634,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>700948</v>
+        <v>700817</v>
       </c>
       <c r="R20" t="n">
-        <v>6388722</v>
+        <v>6388548</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2706,10 +2706,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128835498</v>
+        <v>128835497</v>
       </c>
       <c r="B21" t="n">
-        <v>86957</v>
+        <v>86958</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>700817</v>
+        <v>700948</v>
       </c>
       <c r="R21" t="n">
-        <v>6388548</v>
+        <v>6388722</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2813,10 +2813,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128835490</v>
+        <v>128835472</v>
       </c>
       <c r="B22" t="n">
-        <v>86841</v>
+        <v>86794</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2824,16 +2824,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>424</v>
+        <v>1985</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2848,10 +2848,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>700954</v>
+        <v>700957</v>
       </c>
       <c r="R22" t="n">
-        <v>6388606</v>
+        <v>6388630</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2883,7 +2883,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2920,32 +2920,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128835472</v>
+        <v>128835464</v>
       </c>
       <c r="B23" t="n">
-        <v>86793</v>
+        <v>86971</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1985</v>
+        <v>1988</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2955,10 +2955,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>700957</v>
+        <v>700940</v>
       </c>
       <c r="R23" t="n">
-        <v>6388630</v>
+        <v>6388612</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2990,7 +2990,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3027,10 +3027,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128835464</v>
+        <v>128833068</v>
       </c>
       <c r="B24" t="n">
-        <v>86970</v>
+        <v>86958</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3038,34 +3038,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1988</v>
+        <v>3674</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Follingsbo Rosendal, Gtl</t>
+          <t>Follingbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>700940</v>
+        <v>700938</v>
       </c>
       <c r="R24" t="n">
-        <v>6388612</v>
+        <v>6388454</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3095,19 +3095,9 @@
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>15:01</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>15:01</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3122,57 +3112,57 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128833068</v>
+        <v>128835490</v>
       </c>
       <c r="B25" t="n">
-        <v>86957</v>
+        <v>86842</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3674</v>
+        <v>424</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Follingbo Rosendal, Gtl</t>
+          <t>Follingsbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>700938</v>
+        <v>700954</v>
       </c>
       <c r="R25" t="n">
-        <v>6388454</v>
+        <v>6388606</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3202,9 +3192,19 @@
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3219,22 +3219,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128835444</v>
+        <v>128835473</v>
       </c>
       <c r="B26" t="n">
-        <v>87039</v>
+        <v>86794</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3242,21 +3242,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3767</v>
+        <v>1985</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3266,10 +3266,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>700957</v>
+        <v>700804</v>
       </c>
       <c r="R26" t="n">
-        <v>6388621</v>
+        <v>6388505</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3301,7 +3301,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3311,7 +3311,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3338,10 +3338,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128835470</v>
+        <v>128835444</v>
       </c>
       <c r="B27" t="n">
-        <v>86981</v>
+        <v>87040</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3349,21 +3349,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3599</v>
+        <v>3767</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3373,10 +3373,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>700910</v>
+        <v>700957</v>
       </c>
       <c r="R27" t="n">
-        <v>6388586</v>
+        <v>6388621</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3408,7 +3408,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3445,10 +3445,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128835473</v>
+        <v>128835470</v>
       </c>
       <c r="B28" t="n">
-        <v>86793</v>
+        <v>86982</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3456,21 +3456,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1985</v>
+        <v>3599</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3480,10 +3480,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>700804</v>
+        <v>700910</v>
       </c>
       <c r="R28" t="n">
-        <v>6388505</v>
+        <v>6388586</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3515,7 +3515,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3552,32 +3552,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128835442</v>
+        <v>128835448</v>
       </c>
       <c r="B29" t="n">
-        <v>87039</v>
+        <v>86796</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3767</v>
+        <v>3762</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3587,10 +3587,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>700952</v>
+        <v>700817</v>
       </c>
       <c r="R29" t="n">
-        <v>6388607</v>
+        <v>6388555</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3622,7 +3622,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3659,32 +3659,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128835448</v>
+        <v>128835442</v>
       </c>
       <c r="B30" t="n">
-        <v>86795</v>
+        <v>87040</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3762</v>
+        <v>3767</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3694,10 +3694,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>700817</v>
+        <v>700952</v>
       </c>
       <c r="R30" t="n">
-        <v>6388555</v>
+        <v>6388607</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3769,7 +3769,7 @@
         <v>128833061</v>
       </c>
       <c r="B31" t="n">
-        <v>86910</v>
+        <v>86911</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3866,7 +3866,7 @@
         <v>128835471</v>
       </c>
       <c r="B32" t="n">
-        <v>86793</v>
+        <v>86794</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3973,7 +3973,7 @@
         <v>128835455</v>
       </c>
       <c r="B33" t="n">
-        <v>91021</v>
+        <v>91022</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4081,7 +4081,7 @@
         <v>128835461</v>
       </c>
       <c r="B34" t="n">
-        <v>91074</v>
+        <v>91075</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4192,7 +4192,7 @@
         <v>128835476</v>
       </c>
       <c r="B35" t="n">
-        <v>87188</v>
+        <v>87189</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4308,7 +4308,7 @@
         <v>128833054</v>
       </c>
       <c r="B36" t="n">
-        <v>86994</v>
+        <v>86995</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4403,32 +4403,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128833066</v>
+        <v>128833053</v>
       </c>
       <c r="B37" t="n">
-        <v>86957</v>
+        <v>86995</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4438,10 +4438,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>701012</v>
+        <v>700979</v>
       </c>
       <c r="R37" t="n">
-        <v>6388573</v>
+        <v>6388550</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4482,6 +4482,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4500,32 +4501,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128833053</v>
+        <v>128833066</v>
       </c>
       <c r="B38" t="n">
-        <v>86994</v>
+        <v>86958</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4535,10 +4536,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>700979</v>
+        <v>701012</v>
       </c>
       <c r="R38" t="n">
-        <v>6388550</v>
+        <v>6388573</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4579,7 +4580,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4598,45 +4598,48 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128833052</v>
+        <v>128835474</v>
       </c>
       <c r="B39" t="n">
-        <v>86994</v>
+        <v>86794</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6003295</v>
+        <v>1985</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Follingbo Rosendal, Gtl</t>
+          <t>Follingsbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>701151</v>
+        <v>700966</v>
       </c>
       <c r="R39" t="n">
-        <v>6388524</v>
+        <v>6388635</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4666,9 +4669,19 @@
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4684,60 +4697,57 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128835474</v>
+        <v>128833052</v>
       </c>
       <c r="B40" t="n">
-        <v>86793</v>
+        <v>86995</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1985</v>
+        <v>6003295</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Follingsbo Rosendal, Gtl</t>
+          <t>Follingbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>700966</v>
+        <v>701151</v>
       </c>
       <c r="R40" t="n">
-        <v>6388635</v>
+        <v>6388524</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4767,19 +4777,9 @@
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>14:32</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>14:32</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4795,12 +4795,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -4810,7 +4810,7 @@
         <v>128833057</v>
       </c>
       <c r="B41" t="n">
-        <v>86994</v>
+        <v>86995</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4905,32 +4905,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128833055</v>
+        <v>128833070</v>
       </c>
       <c r="B42" t="n">
-        <v>86994</v>
+        <v>86958</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4940,10 +4940,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>700996</v>
+        <v>701026</v>
       </c>
       <c r="R42" t="n">
-        <v>6388473</v>
+        <v>6388477</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4984,7 +4984,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5003,10 +5002,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128833056</v>
+        <v>128833055</v>
       </c>
       <c r="B43" t="n">
-        <v>86994</v>
+        <v>86995</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5038,10 +5037,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>701017</v>
+        <v>700996</v>
       </c>
       <c r="R43" t="n">
-        <v>6388485</v>
+        <v>6388473</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5101,32 +5100,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128833070</v>
+        <v>128833056</v>
       </c>
       <c r="B44" t="n">
-        <v>86957</v>
+        <v>86995</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5136,10 +5135,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>701026</v>
+        <v>701017</v>
       </c>
       <c r="R44" t="n">
-        <v>6388477</v>
+        <v>6388485</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5180,6 +5179,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5201,7 +5201,7 @@
         <v>128833069</v>
       </c>
       <c r="B45" t="n">
-        <v>86957</v>
+        <v>86958</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5298,7 +5298,7 @@
         <v>128833065</v>
       </c>
       <c r="B46" t="n">
-        <v>86819</v>
+        <v>86820</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>128833064</v>
       </c>
       <c r="B47" t="n">
-        <v>86819</v>
+        <v>86820</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5492,7 +5492,7 @@
         <v>128833071</v>
       </c>
       <c r="B48" t="n">
-        <v>86957</v>
+        <v>86958</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         <v>128833067</v>
       </c>
       <c r="B49" t="n">
-        <v>86957</v>
+        <v>86958</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 6153-2024 artfynd.xlsx
+++ b/artfynd/A 6153-2024 artfynd.xlsx
@@ -782,45 +782,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128835469</v>
+        <v>128833059</v>
       </c>
       <c r="B3" t="n">
-        <v>86982</v>
+        <v>8450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3599</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Follingsbo Rosendal, Gtl</t>
+          <t>Follingbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>700915</v>
+        <v>700942</v>
       </c>
       <c r="R3" t="n">
-        <v>6388581</v>
+        <v>6388538</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -850,24 +850,9 @@
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>15:23</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>15:23</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>1 fk</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,57 +867,57 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128833059</v>
+        <v>128835469</v>
       </c>
       <c r="B4" t="n">
-        <v>8450</v>
+        <v>86982</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>3599</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Follingbo Rosendal, Gtl</t>
+          <t>Follingsbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>700942</v>
+        <v>700915</v>
       </c>
       <c r="R4" t="n">
-        <v>6388538</v>
+        <v>6388581</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -962,9 +947,24 @@
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>1 fk</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,12 +979,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1101,7 +1101,7 @@
         <v>128835480</v>
       </c>
       <c r="B6" t="n">
-        <v>92313</v>
+        <v>92314</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>128835492</v>
       </c>
       <c r="B10" t="n">
-        <v>106329</v>
+        <v>106331</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2174,32 +2174,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128835499</v>
+        <v>128835454</v>
       </c>
       <c r="B16" t="n">
-        <v>86958</v>
+        <v>91022</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3674</v>
+        <v>5735</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Svartnande fingersvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Phaeoclavulina macrospora</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brinkmann</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2209,10 +2209,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>700938</v>
+        <v>700887</v>
       </c>
       <c r="R16" t="n">
-        <v>6388610</v>
+        <v>6388572</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2244,7 +2244,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2254,7 +2254,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Riklig förekomst, Minst 47 fk i en 13 Linje!! Undr En 7-8 meter hög en</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2263,6 +2268,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2281,45 +2287,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128833063</v>
+        <v>128835465</v>
       </c>
       <c r="B17" t="n">
-        <v>86820</v>
+        <v>86995</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Follingbo Rosendal, Gtl</t>
+          <t>Follingsbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>700953</v>
+        <v>700869</v>
       </c>
       <c r="R17" t="n">
-        <v>6388454</v>
+        <v>6388563</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2349,61 +2355,72 @@
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128835454</v>
+        <v>128835499</v>
       </c>
       <c r="B18" t="n">
-        <v>91022</v>
+        <v>86958</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5735</v>
+        <v>3674</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svartnande fingersvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phaeoclavulina macrospora</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Brinkmann</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2413,10 +2430,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>700887</v>
+        <v>700938</v>
       </c>
       <c r="R18" t="n">
-        <v>6388572</v>
+        <v>6388610</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2448,7 +2465,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2458,12 +2475,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Riklig förekomst, Minst 47 fk i en 13 Linje!! Undr En 7-8 meter hög en</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2472,7 +2484,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2491,45 +2502,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128835465</v>
+        <v>128833063</v>
       </c>
       <c r="B19" t="n">
-        <v>86995</v>
+        <v>86820</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Follingsbo Rosendal, Gtl</t>
+          <t>Follingbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>700869</v>
+        <v>700953</v>
       </c>
       <c r="R19" t="n">
-        <v>6388563</v>
+        <v>6388454</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2559,40 +2570,29 @@
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>16:25</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>16:25</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2813,45 +2813,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128835472</v>
+        <v>128833068</v>
       </c>
       <c r="B22" t="n">
-        <v>86794</v>
+        <v>86958</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1985</v>
+        <v>3674</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Follingsbo Rosendal, Gtl</t>
+          <t>Follingbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>700957</v>
+        <v>700938</v>
       </c>
       <c r="R22" t="n">
-        <v>6388630</v>
+        <v>6388454</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2881,19 +2881,9 @@
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>14:39</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>14:39</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2908,44 +2898,44 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128835464</v>
+        <v>128835490</v>
       </c>
       <c r="B23" t="n">
-        <v>86971</v>
+        <v>86842</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1988</v>
+        <v>424</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2955,10 +2945,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>700940</v>
+        <v>700954</v>
       </c>
       <c r="R23" t="n">
-        <v>6388612</v>
+        <v>6388606</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2990,7 +2980,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3000,7 +2990,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3027,45 +3017,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128833068</v>
+        <v>128835472</v>
       </c>
       <c r="B24" t="n">
-        <v>86958</v>
+        <v>86794</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3674</v>
+        <v>1985</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Follingbo Rosendal, Gtl</t>
+          <t>Follingsbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>700938</v>
+        <v>700957</v>
       </c>
       <c r="R24" t="n">
-        <v>6388454</v>
+        <v>6388630</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3095,9 +3085,19 @@
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3112,44 +3112,44 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128835490</v>
+        <v>128835464</v>
       </c>
       <c r="B25" t="n">
-        <v>86842</v>
+        <v>86971</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>424</v>
+        <v>1988</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3159,10 +3159,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>700954</v>
+        <v>700940</v>
       </c>
       <c r="R25" t="n">
-        <v>6388606</v>
+        <v>6388612</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3194,7 +3194,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3204,7 +3204,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3231,10 +3231,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128835473</v>
+        <v>128835444</v>
       </c>
       <c r="B26" t="n">
-        <v>86794</v>
+        <v>87040</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3242,21 +3242,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1985</v>
+        <v>3767</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3266,10 +3266,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>700804</v>
+        <v>700957</v>
       </c>
       <c r="R26" t="n">
-        <v>6388505</v>
+        <v>6388621</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3301,7 +3301,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3311,7 +3311,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3338,10 +3338,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128835444</v>
+        <v>128835470</v>
       </c>
       <c r="B27" t="n">
-        <v>87040</v>
+        <v>86982</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3349,21 +3349,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3767</v>
+        <v>3599</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3373,10 +3373,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>700957</v>
+        <v>700910</v>
       </c>
       <c r="R27" t="n">
-        <v>6388621</v>
+        <v>6388586</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3408,7 +3408,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3445,10 +3445,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128835470</v>
+        <v>128835473</v>
       </c>
       <c r="B28" t="n">
-        <v>86982</v>
+        <v>86794</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3456,21 +3456,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3599</v>
+        <v>1985</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3480,10 +3480,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>700910</v>
+        <v>700804</v>
       </c>
       <c r="R28" t="n">
-        <v>6388586</v>
+        <v>6388505</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3515,7 +3515,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3766,45 +3766,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128833061</v>
+        <v>128835455</v>
       </c>
       <c r="B31" t="n">
-        <v>86911</v>
+        <v>91022</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>248956</v>
+        <v>5735</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Svartnande fingersvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Phaeoclavulina macrospora</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Brinkmann</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Follingbo Rosendal, Gtl</t>
+          <t>Follingsbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>700935</v>
+        <v>700897</v>
       </c>
       <c r="R31" t="n">
-        <v>6388458</v>
+        <v>6388579</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3834,39 +3834,50 @@
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128835471</v>
+        <v>128833061</v>
       </c>
       <c r="B32" t="n">
-        <v>86794</v>
+        <v>86911</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3874,34 +3885,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1985</v>
+        <v>248956</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Follingsbo Rosendal, Gtl</t>
+          <t>Follingbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>700792</v>
+        <v>700935</v>
       </c>
       <c r="R32" t="n">
-        <v>6388508</v>
+        <v>6388458</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3931,19 +3942,9 @@
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>17:02</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>17:02</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3958,44 +3959,44 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128835455</v>
+        <v>128835471</v>
       </c>
       <c r="B33" t="n">
-        <v>91022</v>
+        <v>86794</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5735</v>
+        <v>1985</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svartnande fingersvamp</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phaeoclavulina macrospora</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Brinkmann</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4005,10 +4006,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>700897</v>
+        <v>700792</v>
       </c>
       <c r="R33" t="n">
-        <v>6388579</v>
+        <v>6388508</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4040,7 +4041,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4050,7 +4051,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4059,7 +4060,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4905,32 +4905,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128833070</v>
+        <v>128833055</v>
       </c>
       <c r="B42" t="n">
-        <v>86958</v>
+        <v>86995</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4940,10 +4940,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>701026</v>
+        <v>700996</v>
       </c>
       <c r="R42" t="n">
-        <v>6388477</v>
+        <v>6388473</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4984,6 +4984,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5002,7 +5003,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128833055</v>
+        <v>128833056</v>
       </c>
       <c r="B43" t="n">
         <v>86995</v>
@@ -5037,10 +5038,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>700996</v>
+        <v>701017</v>
       </c>
       <c r="R43" t="n">
-        <v>6388473</v>
+        <v>6388485</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5100,32 +5101,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128833056</v>
+        <v>128833070</v>
       </c>
       <c r="B44" t="n">
-        <v>86995</v>
+        <v>86958</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5135,10 +5136,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>701017</v>
+        <v>701026</v>
       </c>
       <c r="R44" t="n">
-        <v>6388485</v>
+        <v>6388477</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5179,7 +5180,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 6153-2024 artfynd.xlsx
+++ b/artfynd/A 6153-2024 artfynd.xlsx
@@ -782,45 +782,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128833059</v>
+        <v>128835469</v>
       </c>
       <c r="B3" t="n">
-        <v>8450</v>
+        <v>86982</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>3599</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Follingbo Rosendal, Gtl</t>
+          <t>Follingsbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>700942</v>
+        <v>700915</v>
       </c>
       <c r="R3" t="n">
-        <v>6388538</v>
+        <v>6388581</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -850,9 +850,24 @@
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>1 fk</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,57 +882,57 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128835469</v>
+        <v>128833059</v>
       </c>
       <c r="B4" t="n">
-        <v>86982</v>
+        <v>8450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3599</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Follingsbo Rosendal, Gtl</t>
+          <t>Follingbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>700915</v>
+        <v>700942</v>
       </c>
       <c r="R4" t="n">
-        <v>6388581</v>
+        <v>6388538</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -947,24 +962,9 @@
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>15:23</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>15:23</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>1 fk</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,44 +979,44 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128835449</v>
+        <v>128835480</v>
       </c>
       <c r="B5" t="n">
-        <v>86796</v>
+        <v>92314</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3762</v>
+        <v>232138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Gul lammticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Albatrellus citrinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Ryman</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>700916</v>
+        <v>700814</v>
       </c>
       <c r="R5" t="n">
-        <v>6388577</v>
+        <v>6388491</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,32 +1098,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128835480</v>
+        <v>128835449</v>
       </c>
       <c r="B6" t="n">
-        <v>92314</v>
+        <v>86796</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>232138</v>
+        <v>3762</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gul lammticka</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Albatrellus citrinus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Ryman</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>700814</v>
+        <v>700916</v>
       </c>
       <c r="R6" t="n">
-        <v>6388491</v>
+        <v>6388577</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,32 +1205,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128835466</v>
+        <v>128835494</v>
       </c>
       <c r="B7" t="n">
-        <v>86995</v>
+        <v>86958</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>700824</v>
+        <v>700929</v>
       </c>
       <c r="R7" t="n">
-        <v>6388554</v>
+        <v>6388692</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1275,7 +1275,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1294,7 +1294,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1313,32 +1312,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128835494</v>
+        <v>128835466</v>
       </c>
       <c r="B8" t="n">
-        <v>86958</v>
+        <v>86995</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1348,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>700929</v>
+        <v>700824</v>
       </c>
       <c r="R8" t="n">
-        <v>6388692</v>
+        <v>6388554</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1383,7 +1382,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1393,7 +1392,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1402,6 +1401,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1420,32 +1420,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128835475</v>
+        <v>128835492</v>
       </c>
       <c r="B9" t="n">
-        <v>86794</v>
+        <v>106332</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1985</v>
+        <v>220785</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1455,10 +1455,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>700804</v>
+        <v>700799</v>
       </c>
       <c r="R9" t="n">
-        <v>6388482</v>
+        <v>6388520</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1500,7 +1500,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Mycket hlgvuxen 12+ Meter</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1527,32 +1532,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128835492</v>
+        <v>128835475</v>
       </c>
       <c r="B10" t="n">
-        <v>106331</v>
+        <v>86794</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220785</v>
+        <v>1985</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1562,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>700799</v>
+        <v>700804</v>
       </c>
       <c r="R10" t="n">
-        <v>6388520</v>
+        <v>6388482</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1597,7 +1602,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1607,12 +1612,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:45</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Mycket hlgvuxen 12+ Meter</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2174,32 +2174,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128835454</v>
+        <v>128835465</v>
       </c>
       <c r="B16" t="n">
-        <v>91022</v>
+        <v>86995</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5735</v>
+        <v>6003295</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svartnande fingersvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phaeoclavulina macrospora</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Brinkmann</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2209,10 +2209,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>700887</v>
+        <v>700869</v>
       </c>
       <c r="R16" t="n">
-        <v>6388572</v>
+        <v>6388563</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2244,7 +2244,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2254,12 +2254,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Riklig förekomst, Minst 47 fk i en 13 Linje!! Undr En 7-8 meter hög en</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2287,32 +2282,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128835465</v>
+        <v>128835499</v>
       </c>
       <c r="B17" t="n">
-        <v>86995</v>
+        <v>86958</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2322,10 +2317,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>700869</v>
+        <v>700938</v>
       </c>
       <c r="R17" t="n">
-        <v>6388563</v>
+        <v>6388610</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2357,7 +2352,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2367,7 +2362,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2376,7 +2371,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2395,10 +2389,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128835499</v>
+        <v>128833063</v>
       </c>
       <c r="B18" t="n">
-        <v>86958</v>
+        <v>86820</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2406,34 +2400,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3674</v>
+        <v>3712</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Follingsbo Rosendal, Gtl</t>
+          <t>Follingbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>700938</v>
+        <v>700953</v>
       </c>
       <c r="R18" t="n">
-        <v>6388610</v>
+        <v>6388454</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2463,19 +2457,9 @@
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>15:01</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>15:01</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2490,57 +2474,57 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128833063</v>
+        <v>128835454</v>
       </c>
       <c r="B19" t="n">
-        <v>86820</v>
+        <v>91022</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3712</v>
+        <v>5735</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Svartnande fingersvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Phaeoclavulina macrospora</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Brinkmann</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Follingbo Rosendal, Gtl</t>
+          <t>Follingsbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>700953</v>
+        <v>700887</v>
       </c>
       <c r="R19" t="n">
-        <v>6388454</v>
+        <v>6388572</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2570,29 +2554,45 @@
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Riklig förekomst, Minst 47 fk i en 13 Linje!! Undr En 7-8 meter hög en</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2910,10 +2910,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128835490</v>
+        <v>128835472</v>
       </c>
       <c r="B23" t="n">
-        <v>86842</v>
+        <v>86794</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2921,16 +2921,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>424</v>
+        <v>1985</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2945,10 +2945,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>700954</v>
+        <v>700957</v>
       </c>
       <c r="R23" t="n">
-        <v>6388606</v>
+        <v>6388630</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2980,7 +2980,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2990,7 +2990,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3017,32 +3017,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128835472</v>
+        <v>128835464</v>
       </c>
       <c r="B24" t="n">
-        <v>86794</v>
+        <v>86971</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1985</v>
+        <v>1988</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3052,10 +3052,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>700957</v>
+        <v>700940</v>
       </c>
       <c r="R24" t="n">
-        <v>6388630</v>
+        <v>6388612</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3087,7 +3087,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3124,32 +3124,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128835464</v>
+        <v>128835490</v>
       </c>
       <c r="B25" t="n">
-        <v>86971</v>
+        <v>86842</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1988</v>
+        <v>424</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3159,10 +3159,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>700940</v>
+        <v>700954</v>
       </c>
       <c r="R25" t="n">
-        <v>6388612</v>
+        <v>6388606</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3194,7 +3194,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3204,7 +3204,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3231,10 +3231,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128835444</v>
+        <v>128835473</v>
       </c>
       <c r="B26" t="n">
-        <v>87040</v>
+        <v>86794</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3242,21 +3242,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3767</v>
+        <v>1985</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3266,10 +3266,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>700957</v>
+        <v>700804</v>
       </c>
       <c r="R26" t="n">
-        <v>6388621</v>
+        <v>6388505</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3301,7 +3301,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3311,7 +3311,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3338,10 +3338,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128835470</v>
+        <v>128835444</v>
       </c>
       <c r="B27" t="n">
-        <v>86982</v>
+        <v>87040</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3349,21 +3349,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3599</v>
+        <v>3767</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3373,10 +3373,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>700910</v>
+        <v>700957</v>
       </c>
       <c r="R27" t="n">
-        <v>6388586</v>
+        <v>6388621</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3408,7 +3408,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3445,10 +3445,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128835473</v>
+        <v>128835470</v>
       </c>
       <c r="B28" t="n">
-        <v>86794</v>
+        <v>86982</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3456,21 +3456,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1985</v>
+        <v>3599</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3480,10 +3480,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>700804</v>
+        <v>700910</v>
       </c>
       <c r="R28" t="n">
-        <v>6388505</v>
+        <v>6388586</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3515,7 +3515,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3766,32 +3766,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128835455</v>
+        <v>128835471</v>
       </c>
       <c r="B31" t="n">
-        <v>91022</v>
+        <v>86794</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5735</v>
+        <v>1985</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Svartnande fingersvamp</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phaeoclavulina macrospora</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Brinkmann</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3801,10 +3801,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>700897</v>
+        <v>700792</v>
       </c>
       <c r="R31" t="n">
-        <v>6388579</v>
+        <v>6388508</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3855,7 +3855,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3874,45 +3873,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128833061</v>
+        <v>128835455</v>
       </c>
       <c r="B32" t="n">
-        <v>86911</v>
+        <v>91022</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>248956</v>
+        <v>5735</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Svartnande fingersvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Phaeoclavulina macrospora</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Brinkmann</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Follingbo Rosendal, Gtl</t>
+          <t>Follingsbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>700935</v>
+        <v>700897</v>
       </c>
       <c r="R32" t="n">
-        <v>6388458</v>
+        <v>6388579</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3942,39 +3941,50 @@
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128835471</v>
+        <v>128833061</v>
       </c>
       <c r="B33" t="n">
-        <v>86794</v>
+        <v>86911</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3982,34 +3992,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1985</v>
+        <v>248956</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Follingsbo Rosendal, Gtl</t>
+          <t>Follingbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>700792</v>
+        <v>700935</v>
       </c>
       <c r="R33" t="n">
-        <v>6388508</v>
+        <v>6388458</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4039,19 +4049,9 @@
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>17:02</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>17:02</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4066,12 +4066,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4403,32 +4403,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128833053</v>
+        <v>128833066</v>
       </c>
       <c r="B37" t="n">
-        <v>86995</v>
+        <v>86958</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4438,10 +4438,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>700979</v>
+        <v>701012</v>
       </c>
       <c r="R37" t="n">
-        <v>6388550</v>
+        <v>6388573</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4482,7 +4482,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4501,32 +4500,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128833066</v>
+        <v>128833053</v>
       </c>
       <c r="B38" t="n">
-        <v>86958</v>
+        <v>86995</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4536,10 +4535,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>701012</v>
+        <v>700979</v>
       </c>
       <c r="R38" t="n">
-        <v>6388573</v>
+        <v>6388550</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4580,6 +4579,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4598,48 +4598,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128835474</v>
+        <v>128833052</v>
       </c>
       <c r="B39" t="n">
-        <v>86794</v>
+        <v>86995</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1985</v>
+        <v>6003295</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Follingsbo Rosendal, Gtl</t>
+          <t>Follingbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>700966</v>
+        <v>701151</v>
       </c>
       <c r="R39" t="n">
-        <v>6388635</v>
+        <v>6388524</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4669,19 +4666,9 @@
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>14:32</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>14:32</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4697,57 +4684,60 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128833052</v>
+        <v>128835474</v>
       </c>
       <c r="B40" t="n">
-        <v>86995</v>
+        <v>86794</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6003295</v>
+        <v>1985</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Follingbo Rosendal, Gtl</t>
+          <t>Follingsbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>701151</v>
+        <v>700966</v>
       </c>
       <c r="R40" t="n">
-        <v>6388524</v>
+        <v>6388635</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4777,9 +4767,19 @@
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4795,12 +4795,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -4905,32 +4905,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128833055</v>
+        <v>128833070</v>
       </c>
       <c r="B42" t="n">
-        <v>86995</v>
+        <v>86958</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4940,10 +4940,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>700996</v>
+        <v>701026</v>
       </c>
       <c r="R42" t="n">
-        <v>6388473</v>
+        <v>6388477</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4984,7 +4984,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5003,7 +5002,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128833056</v>
+        <v>128833055</v>
       </c>
       <c r="B43" t="n">
         <v>86995</v>
@@ -5038,10 +5037,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>701017</v>
+        <v>700996</v>
       </c>
       <c r="R43" t="n">
-        <v>6388485</v>
+        <v>6388473</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5101,32 +5100,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128833070</v>
+        <v>128833056</v>
       </c>
       <c r="B44" t="n">
-        <v>86958</v>
+        <v>86995</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5136,10 +5135,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>701026</v>
+        <v>701017</v>
       </c>
       <c r="R44" t="n">
-        <v>6388477</v>
+        <v>6388485</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5180,6 +5179,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 6153-2024 artfynd.xlsx
+++ b/artfynd/A 6153-2024 artfynd.xlsx
@@ -4081,7 +4081,7 @@
         <v>128835461</v>
       </c>
       <c r="B34" t="n">
-        <v>91075</v>
+        <v>91078</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4192,7 +4192,7 @@
         <v>128835476</v>
       </c>
       <c r="B35" t="n">
-        <v>87189</v>
+        <v>87192</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 6153-2024 artfynd.xlsx
+++ b/artfynd/A 6153-2024 artfynd.xlsx
@@ -4192,7 +4192,7 @@
         <v>128835476</v>
       </c>
       <c r="B35" t="n">
-        <v>87192</v>
+        <v>87194</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 6153-2024 artfynd.xlsx
+++ b/artfynd/A 6153-2024 artfynd.xlsx
@@ -2489,7 +2489,7 @@
         <v>128835454</v>
       </c>
       <c r="B19" t="n">
-        <v>91210</v>
+        <v>91213</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 6153-2024 artfynd.xlsx
+++ b/artfynd/A 6153-2024 artfynd.xlsx
@@ -2489,7 +2489,7 @@
         <v>128835454</v>
       </c>
       <c r="B19" t="n">
-        <v>91213</v>
+        <v>91239</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 6153-2024 artfynd.xlsx
+++ b/artfynd/A 6153-2024 artfynd.xlsx
@@ -2489,7 +2489,7 @@
         <v>128835454</v>
       </c>
       <c r="B19" t="n">
-        <v>91239</v>
+        <v>91240</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 6153-2024 artfynd.xlsx
+++ b/artfynd/A 6153-2024 artfynd.xlsx
@@ -2489,7 +2489,7 @@
         <v>128835454</v>
       </c>
       <c r="B19" t="n">
-        <v>91240</v>
+        <v>91241</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 6153-2024 artfynd.xlsx
+++ b/artfynd/A 6153-2024 artfynd.xlsx
@@ -2489,7 +2489,7 @@
         <v>128835454</v>
       </c>
       <c r="B19" t="n">
-        <v>91241</v>
+        <v>91243</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 6153-2024 artfynd.xlsx
+++ b/artfynd/A 6153-2024 artfynd.xlsx
@@ -2489,7 +2489,7 @@
         <v>128835454</v>
       </c>
       <c r="B19" t="n">
-        <v>91243</v>
+        <v>91255</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 6153-2024 artfynd.xlsx
+++ b/artfynd/A 6153-2024 artfynd.xlsx
@@ -2489,7 +2489,7 @@
         <v>128835454</v>
       </c>
       <c r="B19" t="n">
-        <v>91255</v>
+        <v>91256</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 6153-2024 artfynd.xlsx
+++ b/artfynd/A 6153-2024 artfynd.xlsx
@@ -2489,7 +2489,7 @@
         <v>128835454</v>
       </c>
       <c r="B19" t="n">
-        <v>91256</v>
+        <v>91257</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 6153-2024 artfynd.xlsx
+++ b/artfynd/A 6153-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY49"/>
+  <dimension ref="A1:AY50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128835463</v>
+        <v>128835490</v>
       </c>
       <c r="B2" t="n">
-        <v>86971</v>
+        <v>87193</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1988</v>
+        <v>424</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>700887</v>
+        <v>700954</v>
       </c>
       <c r="R2" t="n">
-        <v>6388581</v>
+        <v>6388606</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128835469</v>
+        <v>128835471</v>
       </c>
       <c r="B3" t="n">
-        <v>86982</v>
+        <v>87144</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3599</v>
+        <v>1985</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>700915</v>
+        <v>700792</v>
       </c>
       <c r="R3" t="n">
-        <v>6388581</v>
+        <v>6388508</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,12 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:23</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>1 fk</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,45 +889,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128833059</v>
+        <v>128835472</v>
       </c>
       <c r="B4" t="n">
-        <v>8450</v>
+        <v>87144</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>1985</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Follingbo Rosendal, Gtl</t>
+          <t>Follingsbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>700942</v>
+        <v>700957</v>
       </c>
       <c r="R4" t="n">
-        <v>6388538</v>
+        <v>6388630</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -962,9 +957,19 @@
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,22 +984,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128835480</v>
+        <v>128835473</v>
       </c>
       <c r="B5" t="n">
-        <v>92314</v>
+        <v>87144</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1002,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>232138</v>
+        <v>1985</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gul lammticka</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Albatrellus citrinus</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Ryman</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>700814</v>
+        <v>700804</v>
       </c>
       <c r="R5" t="n">
-        <v>6388491</v>
+        <v>6388505</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1071,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,45 +1103,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128835449</v>
+        <v>128835474</v>
       </c>
       <c r="B6" t="n">
-        <v>86796</v>
+        <v>87144</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3762</v>
+        <v>1985</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Follingsbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>700916</v>
+        <v>700966</v>
       </c>
       <c r="R6" t="n">
-        <v>6388577</v>
+        <v>6388635</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,7 +1176,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1178,7 +1186,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1187,6 +1195,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1205,32 +1214,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128835494</v>
+        <v>128835475</v>
       </c>
       <c r="B7" t="n">
-        <v>86958</v>
+        <v>87144</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3674</v>
+        <v>1985</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>700929</v>
+        <v>700804</v>
       </c>
       <c r="R7" t="n">
-        <v>6388692</v>
+        <v>6388482</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1275,7 +1284,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1285,7 +1294,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128835466</v>
+        <v>128835462</v>
       </c>
       <c r="B8" t="n">
-        <v>86995</v>
+        <v>87322</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1323,21 +1332,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6003295</v>
+        <v>1988</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1347,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>700824</v>
+        <v>700813</v>
       </c>
       <c r="R8" t="n">
-        <v>6388554</v>
+        <v>6388546</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1382,7 +1391,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1392,7 +1401,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1401,7 +1410,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1420,32 +1428,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128835492</v>
+        <v>128835463</v>
       </c>
       <c r="B9" t="n">
-        <v>106332</v>
+        <v>87322</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220785</v>
+        <v>1988</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1455,10 +1463,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>700799</v>
+        <v>700887</v>
       </c>
       <c r="R9" t="n">
-        <v>6388520</v>
+        <v>6388581</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1490,7 +1498,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1500,12 +1508,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:45</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Mycket hlgvuxen 12+ Meter</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1532,32 +1535,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128835475</v>
+        <v>128835464</v>
       </c>
       <c r="B10" t="n">
-        <v>86794</v>
+        <v>87322</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1985</v>
+        <v>1988</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1567,10 +1570,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>700804</v>
+        <v>700940</v>
       </c>
       <c r="R10" t="n">
-        <v>6388482</v>
+        <v>6388612</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1602,7 +1605,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1612,7 +1615,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1639,32 +1642,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128835493</v>
+        <v>128835469</v>
       </c>
       <c r="B11" t="n">
-        <v>86958</v>
+        <v>87333</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3674</v>
+        <v>3599</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1674,10 +1677,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>700828</v>
+        <v>700915</v>
       </c>
       <c r="R11" t="n">
-        <v>6388554</v>
+        <v>6388581</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1709,7 +1712,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1719,7 +1722,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>1 fk</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1746,10 +1754,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128835443</v>
+        <v>128835470</v>
       </c>
       <c r="B12" t="n">
-        <v>87040</v>
+        <v>87333</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1757,21 +1765,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3767</v>
+        <v>3599</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1781,10 +1789,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>700956</v>
+        <v>700910</v>
       </c>
       <c r="R12" t="n">
-        <v>6388619</v>
+        <v>6388586</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1816,7 +1824,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1826,7 +1834,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1853,45 +1861,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128835441</v>
+        <v>128833066</v>
       </c>
       <c r="B13" t="n">
-        <v>87040</v>
+        <v>87309</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3767</v>
+        <v>3674</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Follingsbo Rosendal, Gtl</t>
+          <t>Follingbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>700883</v>
+        <v>701012</v>
       </c>
       <c r="R13" t="n">
-        <v>6388583</v>
+        <v>6388573</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1921,19 +1929,9 @@
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>15:43</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>15:43</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1948,22 +1946,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128835450</v>
+        <v>128833067</v>
       </c>
       <c r="B14" t="n">
-        <v>86796</v>
+        <v>87309</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1971,34 +1969,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3762</v>
+        <v>3674</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Follingsbo Rosendal, Gtl</t>
+          <t>Follingbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>700914</v>
+        <v>700982</v>
       </c>
       <c r="R14" t="n">
-        <v>6388586</v>
+        <v>6388557</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2028,19 +2026,9 @@
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>15:05</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>15:05</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2055,22 +2043,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128835462</v>
+        <v>128833068</v>
       </c>
       <c r="B15" t="n">
-        <v>86971</v>
+        <v>87309</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2078,34 +2066,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1988</v>
+        <v>3674</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Follingsbo Rosendal, Gtl</t>
+          <t>Follingbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>700813</v>
+        <v>700938</v>
       </c>
       <c r="R15" t="n">
-        <v>6388546</v>
+        <v>6388454</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2135,19 +2123,9 @@
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>16:43</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>16:43</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2162,57 +2140,57 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128835465</v>
+        <v>128833069</v>
       </c>
       <c r="B16" t="n">
-        <v>86995</v>
+        <v>87309</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Follingsbo Rosendal, Gtl</t>
+          <t>Follingbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>700869</v>
+        <v>700967</v>
       </c>
       <c r="R16" t="n">
-        <v>6388563</v>
+        <v>6388445</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2242,50 +2220,39 @@
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>16:25</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>16:25</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128835499</v>
+        <v>128833070</v>
       </c>
       <c r="B17" t="n">
-        <v>86958</v>
+        <v>87309</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2313,14 +2280,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Follingsbo Rosendal, Gtl</t>
+          <t>Follingbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>700938</v>
+        <v>701026</v>
       </c>
       <c r="R17" t="n">
-        <v>6388610</v>
+        <v>6388477</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2350,19 +2317,9 @@
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>15:01</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>15:01</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2377,22 +2334,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128833063</v>
+        <v>128833071</v>
       </c>
       <c r="B18" t="n">
-        <v>86820</v>
+        <v>87309</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2400,21 +2357,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3712</v>
+        <v>3674</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2424,10 +2381,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>700953</v>
+        <v>701130</v>
       </c>
       <c r="R18" t="n">
-        <v>6388454</v>
+        <v>6388509</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2486,48 +2443,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128835454</v>
+        <v>128835493</v>
       </c>
       <c r="B19" t="n">
-        <v>91257</v>
+        <v>87309</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5735</v>
+        <v>3674</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svartnande fingersvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phaeoclavulina macrospora</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Brinkmann</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Follingsbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>700887</v>
+        <v>700828</v>
       </c>
       <c r="R19" t="n">
-        <v>6388572</v>
+        <v>6388554</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2559,7 +2513,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2569,12 +2523,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Riklig förekomst, Minst 47 fk i en 13 Linje!! Undr En 7-8 meter hög en</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2583,7 +2532,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2598,18 +2546,14 @@
           <t>Martin Axegård</t>
         </is>
       </c>
-      <c r="AY19" t="inlineStr">
-        <is>
-          <t>Fynd med DNA-sekvens - extern</t>
-        </is>
-      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128835498</v>
+        <v>128835494</v>
       </c>
       <c r="B20" t="n">
-        <v>86958</v>
+        <v>87309</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2641,10 +2585,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>700817</v>
+        <v>700929</v>
       </c>
       <c r="R20" t="n">
-        <v>6388548</v>
+        <v>6388692</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2676,7 +2620,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2686,7 +2630,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2713,10 +2657,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128835497</v>
+        <v>128835495</v>
       </c>
       <c r="B21" t="n">
-        <v>86958</v>
+        <v>87309</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2748,10 +2692,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>700948</v>
+        <v>700906</v>
       </c>
       <c r="R21" t="n">
-        <v>6388722</v>
+        <v>6388731</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2783,7 +2727,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2793,7 +2737,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2820,10 +2764,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128833068</v>
+        <v>128835497</v>
       </c>
       <c r="B22" t="n">
-        <v>86958</v>
+        <v>87309</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2851,14 +2795,14 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Follingbo Rosendal, Gtl</t>
+          <t>Follingsbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>700938</v>
+        <v>700948</v>
       </c>
       <c r="R22" t="n">
-        <v>6388454</v>
+        <v>6388722</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2888,9 +2832,19 @@
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2905,44 +2859,44 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128835472</v>
+        <v>128835498</v>
       </c>
       <c r="B23" t="n">
-        <v>86794</v>
+        <v>87309</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1985</v>
+        <v>3674</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2952,10 +2906,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>700957</v>
+        <v>700817</v>
       </c>
       <c r="R23" t="n">
-        <v>6388630</v>
+        <v>6388548</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2987,7 +2941,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2997,7 +2951,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3024,10 +2978,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128835464</v>
+        <v>128835499</v>
       </c>
       <c r="B24" t="n">
-        <v>86971</v>
+        <v>87309</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3035,21 +2989,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1988</v>
+        <v>3674</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3059,10 +3013,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>700940</v>
+        <v>700938</v>
       </c>
       <c r="R24" t="n">
-        <v>6388612</v>
+        <v>6388610</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3131,45 +3085,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128835490</v>
+        <v>128833063</v>
       </c>
       <c r="B25" t="n">
-        <v>86842</v>
+        <v>87170</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>424</v>
+        <v>3712</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Follingsbo Rosendal, Gtl</t>
+          <t>Follingbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>700954</v>
+        <v>700953</v>
       </c>
       <c r="R25" t="n">
-        <v>6388606</v>
+        <v>6388454</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3199,19 +3153,9 @@
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>14:56</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>14:56</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3226,57 +3170,57 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128835473</v>
+        <v>128833064</v>
       </c>
       <c r="B26" t="n">
-        <v>86794</v>
+        <v>87170</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1985</v>
+        <v>3712</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Follingsbo Rosendal, Gtl</t>
+          <t>Follingbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>700804</v>
+        <v>701018</v>
       </c>
       <c r="R26" t="n">
-        <v>6388505</v>
+        <v>6388486</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3306,19 +3250,9 @@
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>16:56</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>16:56</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3333,57 +3267,57 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128835444</v>
+        <v>128833065</v>
       </c>
       <c r="B27" t="n">
-        <v>87040</v>
+        <v>87170</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3767</v>
+        <v>3712</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Follingsbo Rosendal, Gtl</t>
+          <t>Follingbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>700957</v>
+        <v>701142</v>
       </c>
       <c r="R27" t="n">
-        <v>6388621</v>
+        <v>6388527</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3413,19 +3347,9 @@
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>14:49</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>14:49</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3440,44 +3364,44 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128835470</v>
+        <v>128835448</v>
       </c>
       <c r="B28" t="n">
-        <v>86982</v>
+        <v>87146</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3599</v>
+        <v>3762</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3487,10 +3411,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>700910</v>
+        <v>700817</v>
       </c>
       <c r="R28" t="n">
-        <v>6388586</v>
+        <v>6388555</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3522,7 +3446,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3532,7 +3456,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3559,10 +3483,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128835448</v>
+        <v>128835449</v>
       </c>
       <c r="B29" t="n">
-        <v>86796</v>
+        <v>87146</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3594,10 +3518,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>700817</v>
+        <v>700916</v>
       </c>
       <c r="R29" t="n">
-        <v>6388555</v>
+        <v>6388577</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3629,7 +3553,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3639,7 +3563,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3666,32 +3590,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128835442</v>
+        <v>128835450</v>
       </c>
       <c r="B30" t="n">
-        <v>87040</v>
+        <v>87146</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3767</v>
+        <v>3762</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3701,10 +3625,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>700952</v>
+        <v>700914</v>
       </c>
       <c r="R30" t="n">
-        <v>6388607</v>
+        <v>6388586</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3736,7 +3660,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3746,7 +3670,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3773,10 +3697,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128835471</v>
+        <v>128835441</v>
       </c>
       <c r="B31" t="n">
-        <v>86794</v>
+        <v>87391</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3784,21 +3708,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1985</v>
+        <v>3767</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3808,10 +3732,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>700792</v>
+        <v>700883</v>
       </c>
       <c r="R31" t="n">
-        <v>6388508</v>
+        <v>6388583</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3843,7 +3767,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3853,7 +3777,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3880,32 +3804,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128835455</v>
+        <v>128835442</v>
       </c>
       <c r="B32" t="n">
-        <v>91022</v>
+        <v>87391</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5735</v>
+        <v>3767</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Svartnande fingersvamp</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phaeoclavulina macrospora</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Brinkmann</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3915,10 +3839,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>700897</v>
+        <v>700952</v>
       </c>
       <c r="R32" t="n">
-        <v>6388579</v>
+        <v>6388607</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3950,7 +3874,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3960,7 +3884,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3969,7 +3893,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3988,10 +3911,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128833061</v>
+        <v>128835443</v>
       </c>
       <c r="B33" t="n">
-        <v>86911</v>
+        <v>87391</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3999,34 +3922,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>248956</v>
+        <v>3767</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Follingbo Rosendal, Gtl</t>
+          <t>Follingsbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>700935</v>
+        <v>700956</v>
       </c>
       <c r="R33" t="n">
-        <v>6388458</v>
+        <v>6388619</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4056,9 +3979,19 @@
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4073,22 +4006,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128835461</v>
+        <v>128835444</v>
       </c>
       <c r="B34" t="n">
-        <v>91078</v>
+        <v>87391</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4096,37 +4029,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5747</v>
+        <v>3767</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Follingsbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>700816</v>
+        <v>700957</v>
       </c>
       <c r="R34" t="n">
-        <v>6388491</v>
+        <v>6388621</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4158,7 +4088,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4168,7 +4098,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4177,7 +4107,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4196,32 +4125,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128835476</v>
+        <v>128835454</v>
       </c>
       <c r="B35" t="n">
-        <v>87194</v>
+        <v>91382</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>451</v>
+        <v>5735</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sotbandad spindling</t>
+          <t>Svartnande fingersvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cortinarius fuscoperonatus</t>
+          <t>Phaeoclavulina macrospora</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Kühner</t>
+          <t>Brinkmann</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4234,10 +4163,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>700801</v>
+        <v>700887</v>
       </c>
       <c r="R35" t="n">
-        <v>6388492</v>
+        <v>6388572</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4269,7 +4198,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4279,19 +4208,19 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Kollekt.</t>
+          <t>Riklig förekomst, Minst 47 fk i en 13 Linje!! Undr En 7-8 meter hög en</t>
         </is>
       </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
@@ -4308,49 +4237,53 @@
           <t>Martin Axegård</t>
         </is>
       </c>
-      <c r="AY35" t="inlineStr"/>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>Fynd med DNA-sekvens - extern</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128833054</v>
+        <v>128835455</v>
       </c>
       <c r="B36" t="n">
-        <v>86995</v>
+        <v>91382</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6003295</v>
+        <v>5735</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartnande fingersvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Phaeoclavulina macrospora</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brinkmann</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Follingbo Rosendal, Gtl</t>
+          <t>Follingsbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>700966</v>
+        <v>700897</v>
       </c>
       <c r="R36" t="n">
-        <v>6388444</v>
+        <v>6388579</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4380,9 +4313,19 @@
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4398,57 +4341,60 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128833066</v>
+        <v>128835461</v>
       </c>
       <c r="B37" t="n">
-        <v>86958</v>
+        <v>91435</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>3674</v>
+        <v>5747</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Follingbo Rosendal, Gtl</t>
+          <t>Follingsbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>701012</v>
+        <v>700816</v>
       </c>
       <c r="R37" t="n">
-        <v>6388573</v>
+        <v>6388491</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4478,61 +4424,72 @@
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>16:59</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>16:59</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128833053</v>
+        <v>128833059</v>
       </c>
       <c r="B38" t="n">
-        <v>86995</v>
+        <v>8455</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6003295</v>
+        <v>106545</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4542,10 +4499,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>700979</v>
+        <v>700942</v>
       </c>
       <c r="R38" t="n">
-        <v>6388550</v>
+        <v>6388538</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4586,7 +4543,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4605,45 +4561,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128833052</v>
+        <v>128835492</v>
       </c>
       <c r="B39" t="n">
-        <v>86995</v>
+        <v>106812</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6003295</v>
+        <v>220785</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Follingbo Rosendal, Gtl</t>
+          <t>Follingsbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>701151</v>
+        <v>700799</v>
       </c>
       <c r="R39" t="n">
-        <v>6388524</v>
+        <v>6388520</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4673,40 +4629,54 @@
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Mycket hlgvuxen 12+ Meter</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128835474</v>
+        <v>105104386</v>
       </c>
       <c r="B40" t="n">
-        <v>86794</v>
+        <v>106650</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4714,37 +4684,30 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1985</v>
+        <v>225197</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Äkta ljungsnärja</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Kalchbr.</t>
-        </is>
-      </c>
+          <t>Cuscuta epithymum var. epithymum</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Follingsbo Rosendal, Gtl</t>
+          <t>Follingbomasten 300 m V, Gtl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>700966</v>
+        <v>701144</v>
       </c>
       <c r="R40" t="n">
-        <v>6388635</v>
+        <v>6388381</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4771,22 +4734,17 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>14:32</t>
+          <t>1992-01-01</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>14:32</t>
+          <t>1996-12-31</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Rosendal 1:17</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4795,64 +4753,72 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>Alvarlik kalkhällmark, parasit på Gulmåra, Ögontröst, Praktbrunört</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr"/>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>Projekt Gotlands Flora</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128833057</v>
+        <v>128835480</v>
       </c>
       <c r="B41" t="n">
-        <v>86995</v>
+        <v>92688</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6003295</v>
+        <v>232138</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gul lammticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Albatrellus citrinus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Ryman</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Follingbo Rosendal, Gtl</t>
+          <t>Follingsbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>701053</v>
+        <v>700814</v>
       </c>
       <c r="R41" t="n">
-        <v>6388488</v>
+        <v>6388491</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4882,62 +4848,71 @@
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>16:59</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>16:59</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128833070</v>
+        <v>128833061</v>
       </c>
       <c r="B42" t="n">
-        <v>86958</v>
+        <v>87262</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3674</v>
+        <v>248956</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4947,10 +4922,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>701026</v>
+        <v>700935</v>
       </c>
       <c r="R42" t="n">
-        <v>6388477</v>
+        <v>6388458</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5009,10 +4984,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128833055</v>
+        <v>128833052</v>
       </c>
       <c r="B43" t="n">
-        <v>86995</v>
+        <v>87346</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5044,10 +5019,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>700996</v>
+        <v>701151</v>
       </c>
       <c r="R43" t="n">
-        <v>6388473</v>
+        <v>6388524</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5107,10 +5082,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128833056</v>
+        <v>128833053</v>
       </c>
       <c r="B44" t="n">
-        <v>86995</v>
+        <v>87346</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5142,10 +5117,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>701017</v>
+        <v>700979</v>
       </c>
       <c r="R44" t="n">
-        <v>6388485</v>
+        <v>6388550</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5205,32 +5180,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128833069</v>
+        <v>128833054</v>
       </c>
       <c r="B45" t="n">
-        <v>86958</v>
+        <v>87346</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5240,10 +5215,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>700967</v>
+        <v>700966</v>
       </c>
       <c r="R45" t="n">
-        <v>6388445</v>
+        <v>6388444</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5284,6 +5259,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5302,32 +5278,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128833065</v>
+        <v>128833055</v>
       </c>
       <c r="B46" t="n">
-        <v>86820</v>
+        <v>87346</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5337,10 +5313,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>701142</v>
+        <v>700996</v>
       </c>
       <c r="R46" t="n">
-        <v>6388527</v>
+        <v>6388473</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5381,6 +5357,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5399,32 +5376,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128833064</v>
+        <v>128833056</v>
       </c>
       <c r="B47" t="n">
-        <v>86820</v>
+        <v>87346</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5434,10 +5411,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>701018</v>
+        <v>701017</v>
       </c>
       <c r="R47" t="n">
-        <v>6388486</v>
+        <v>6388485</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5478,6 +5455,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5496,32 +5474,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128833071</v>
+        <v>128833057</v>
       </c>
       <c r="B48" t="n">
-        <v>86958</v>
+        <v>87346</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5531,10 +5509,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>701130</v>
+        <v>701053</v>
       </c>
       <c r="R48" t="n">
-        <v>6388509</v>
+        <v>6388488</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5575,6 +5553,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5593,45 +5572,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128833067</v>
+        <v>128835465</v>
       </c>
       <c r="B49" t="n">
-        <v>86958</v>
+        <v>87346</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Follingbo Rosendal, Gtl</t>
+          <t>Follingsbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>700982</v>
+        <v>700869</v>
       </c>
       <c r="R49" t="n">
-        <v>6388557</v>
+        <v>6388563</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5661,32 +5640,151 @@
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>128835466</v>
+      </c>
+      <c r="B50" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Follingsbo Rosendal, Gtl</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>700824</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6388554</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Follingbo</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 6153-2024 artfynd.xlsx
+++ b/artfynd/A 6153-2024 artfynd.xlsx
@@ -6037,7 +6037,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Jan Henriksson, Tobias Ivarsson</t>
+          <t>Tobias Ivarsson, Jan Henriksson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -6134,7 +6134,7 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Jan Henriksson, Tobias Ivarsson</t>
+          <t>Tobias Ivarsson, Jan Henriksson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -6231,7 +6231,7 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Jan Henriksson, Tobias Ivarsson</t>
+          <t>Tobias Ivarsson, Jan Henriksson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>

--- a/artfynd/A 6153-2024 artfynd.xlsx
+++ b/artfynd/A 6153-2024 artfynd.xlsx
@@ -6037,7 +6037,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Tobias Ivarsson, Jan Henriksson</t>
+          <t>Jan Henriksson, Tobias Ivarsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -6134,7 +6134,7 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Tobias Ivarsson, Jan Henriksson</t>
+          <t>Jan Henriksson, Tobias Ivarsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -6231,7 +6231,7 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Tobias Ivarsson, Jan Henriksson</t>
+          <t>Jan Henriksson, Tobias Ivarsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>

--- a/artfynd/A 6153-2024 artfynd.xlsx
+++ b/artfynd/A 6153-2024 artfynd.xlsx
@@ -5145,7 +5145,7 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Jan Henriksson, Tobias Ivarsson</t>
+          <t>Tobias Ivarsson, Jan Henriksson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Jan Henriksson, Tobias Ivarsson</t>
+          <t>Tobias Ivarsson, Jan Henriksson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5440,7 +5440,7 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Jan Henriksson, Tobias Ivarsson</t>
+          <t>Tobias Ivarsson, Jan Henriksson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Jan Henriksson, Tobias Ivarsson</t>
+          <t>Tobias Ivarsson, Jan Henriksson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -5731,7 +5731,7 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Jan Henriksson, Tobias Ivarsson</t>
+          <t>Tobias Ivarsson, Jan Henriksson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Jan Henriksson, Tobias Ivarsson</t>
+          <t>Tobias Ivarsson, Jan Henriksson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>

--- a/artfynd/A 6153-2024 artfynd.xlsx
+++ b/artfynd/A 6153-2024 artfynd.xlsx
@@ -5145,7 +5145,7 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Tobias Ivarsson, Jan Henriksson</t>
+          <t>Jan Henriksson, Tobias Ivarsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Tobias Ivarsson, Jan Henriksson</t>
+          <t>Jan Henriksson, Tobias Ivarsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5440,7 +5440,7 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Tobias Ivarsson, Jan Henriksson</t>
+          <t>Jan Henriksson, Tobias Ivarsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Tobias Ivarsson, Jan Henriksson</t>
+          <t>Jan Henriksson, Tobias Ivarsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -5731,7 +5731,7 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Tobias Ivarsson, Jan Henriksson</t>
+          <t>Jan Henriksson, Tobias Ivarsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Tobias Ivarsson, Jan Henriksson</t>
+          <t>Jan Henriksson, Tobias Ivarsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>

--- a/artfynd/A 6153-2024 artfynd.xlsx
+++ b/artfynd/A 6153-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY69"/>
+  <dimension ref="A1:AZ69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128835490</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128835471</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128835472</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128835473</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1211,6 +1236,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128835474</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1318,6 +1348,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128835475</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1425,6 +1460,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128835462</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1532,6 +1572,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128835463</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1639,6 +1684,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128835464</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1751,6 +1801,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128835469</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1858,6 +1913,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128835470</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1955,6 +2015,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128833066</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2052,6 +2117,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128833067</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2149,6 +2219,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128833068</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2246,6 +2321,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128833069</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2343,6 +2423,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128833070</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2440,6 +2525,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128833071</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2547,6 +2637,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128835493</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2654,6 +2749,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128835494</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2761,6 +2861,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128835495</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2868,6 +2973,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128835497</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2975,6 +3085,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128835498</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3082,6 +3197,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128835499</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3179,6 +3299,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128833063</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3276,6 +3401,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128833064</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3373,6 +3503,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128833065</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3480,6 +3615,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128835448</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3587,6 +3727,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128835449</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3694,6 +3839,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128835450</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3801,6 +3951,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128835441</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3908,6 +4063,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128835442</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4015,6 +4175,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128835443</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4122,6 +4287,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128835444</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4242,6 +4412,11 @@
           <t>Fynd med DNA-sekvens - extern</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128835454</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4350,6 +4525,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128835455</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4461,6 +4641,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128835461</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4562,6 +4747,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135045765</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4663,6 +4853,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135045766</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4760,6 +4955,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135046035</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4858,6 +5058,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135046042</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4955,6 +5160,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135045810</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5052,6 +5262,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128833059</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5149,6 +5364,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135045850</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5246,6 +5466,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135045821</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5347,6 +5572,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135046025</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5444,6 +5674,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135045846</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5541,6 +5776,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135045938</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5638,6 +5878,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135045818</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5735,6 +5980,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135045819</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5832,6 +6082,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135045757</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5944,6 +6199,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128835492</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6041,6 +6301,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135046113</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6138,6 +6403,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135046114</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6235,6 +6505,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135046115</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6328,6 +6603,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135045855</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6421,6 +6701,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135045887</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6514,6 +6799,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135045888</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6621,6 +6911,11 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105104386</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6728,6 +7023,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128835480</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6825,6 +7125,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128833061</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6923,6 +7228,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128833052</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7021,6 +7331,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128833053</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7119,6 +7434,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128833054</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7217,6 +7537,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128833055</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7315,6 +7640,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128833056</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7413,6 +7743,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128833057</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7521,6 +7856,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128835465</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7629,8 +7969,83 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128835466</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 6153-2024 artfynd.xlsx
+++ b/artfynd/A 6153-2024 artfynd.xlsx
@@ -4652,7 +4652,7 @@
         <v>135045765</v>
       </c>
       <c r="B38" t="n">
-        <v>43304</v>
+        <v>43309</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4758,7 +4758,7 @@
         <v>135045766</v>
       </c>
       <c r="B39" t="n">
-        <v>43304</v>
+        <v>43309</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4864,7 +4864,7 @@
         <v>135046035</v>
       </c>
       <c r="B40" t="n">
-        <v>45050</v>
+        <v>45055</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4966,7 +4966,7 @@
         <v>135046042</v>
       </c>
       <c r="B41" t="n">
-        <v>45050</v>
+        <v>45055</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5069,7 +5069,7 @@
         <v>135045810</v>
       </c>
       <c r="B42" t="n">
-        <v>40521</v>
+        <v>40525</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5273,7 +5273,7 @@
         <v>135045850</v>
       </c>
       <c r="B44" t="n">
-        <v>43224</v>
+        <v>43229</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5375,7 +5375,7 @@
         <v>135045821</v>
       </c>
       <c r="B45" t="n">
-        <v>45048</v>
+        <v>45053</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5477,7 +5477,7 @@
         <v>135046025</v>
       </c>
       <c r="B46" t="n">
-        <v>43986</v>
+        <v>43991</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5583,7 +5583,7 @@
         <v>135045846</v>
       </c>
       <c r="B47" t="n">
-        <v>111257</v>
+        <v>111315</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5685,7 +5685,7 @@
         <v>135045938</v>
       </c>
       <c r="B48" t="n">
-        <v>108197</v>
+        <v>108252</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
         <v>135045818</v>
       </c>
       <c r="B49" t="n">
-        <v>109896</v>
+        <v>109952</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5889,7 +5889,7 @@
         <v>135045819</v>
       </c>
       <c r="B50" t="n">
-        <v>109896</v>
+        <v>109952</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5991,7 +5991,7 @@
         <v>135045757</v>
       </c>
       <c r="B51" t="n">
-        <v>110159</v>
+        <v>110215</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6210,7 +6210,7 @@
         <v>135046113</v>
       </c>
       <c r="B53" t="n">
-        <v>107598</v>
+        <v>107653</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6312,7 +6312,7 @@
         <v>135046114</v>
       </c>
       <c r="B54" t="n">
-        <v>107598</v>
+        <v>107653</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6414,7 +6414,7 @@
         <v>135046115</v>
       </c>
       <c r="B55" t="n">
-        <v>107598</v>
+        <v>107653</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6516,7 +6516,7 @@
         <v>135045855</v>
       </c>
       <c r="B56" t="n">
-        <v>104720</v>
+        <v>104774</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6614,7 +6614,7 @@
         <v>135045887</v>
       </c>
       <c r="B57" t="n">
-        <v>104720</v>
+        <v>104774</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6712,7 +6712,7 @@
         <v>135045888</v>
       </c>
       <c r="B58" t="n">
-        <v>104720</v>
+        <v>104774</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 6153-2024 artfynd.xlsx
+++ b/artfynd/A 6153-2024 artfynd.xlsx
@@ -5583,7 +5583,7 @@
         <v>135045846</v>
       </c>
       <c r="B47" t="n">
-        <v>111315</v>
+        <v>111342</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5685,7 +5685,7 @@
         <v>135045938</v>
       </c>
       <c r="B48" t="n">
-        <v>108252</v>
+        <v>108279</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
         <v>135045818</v>
       </c>
       <c r="B49" t="n">
-        <v>109952</v>
+        <v>109979</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5889,7 +5889,7 @@
         <v>135045819</v>
       </c>
       <c r="B50" t="n">
-        <v>109952</v>
+        <v>109979</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5991,7 +5991,7 @@
         <v>135045757</v>
       </c>
       <c r="B51" t="n">
-        <v>110215</v>
+        <v>110242</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6210,7 +6210,7 @@
         <v>135046113</v>
       </c>
       <c r="B53" t="n">
-        <v>107653</v>
+        <v>107680</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6312,7 +6312,7 @@
         <v>135046114</v>
       </c>
       <c r="B54" t="n">
-        <v>107653</v>
+        <v>107680</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6414,7 +6414,7 @@
         <v>135046115</v>
       </c>
       <c r="B55" t="n">
-        <v>107653</v>
+        <v>107680</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6516,7 +6516,7 @@
         <v>135045855</v>
       </c>
       <c r="B56" t="n">
-        <v>104774</v>
+        <v>104801</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6614,7 +6614,7 @@
         <v>135045887</v>
       </c>
       <c r="B57" t="n">
-        <v>104774</v>
+        <v>104801</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6712,7 +6712,7 @@
         <v>135045888</v>
       </c>
       <c r="B58" t="n">
-        <v>104774</v>
+        <v>104801</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
